--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,369 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123253165</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>513623</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6733230</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123252664</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513616</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6733249</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123252821</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513598</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6733234</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123253165</v>
+        <v>123252821</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513623</v>
+        <v>513598</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733234</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252821</v>
+        <v>123253165</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513598</v>
+        <v>513623</v>
       </c>
       <c r="R5" t="n">
-        <v>6733234</v>
+        <v>6733230</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252821</v>
+        <v>123253165</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513598</v>
+        <v>513623</v>
       </c>
       <c r="R3" t="n">
-        <v>6733234</v>
+        <v>6733230</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123253165</v>
+        <v>123252821</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513623</v>
+        <v>513598</v>
       </c>
       <c r="R5" t="n">
-        <v>6733230</v>
+        <v>6733234</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123253272</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>123253165</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252664</v>
+        <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,12 +948,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513616</v>
+        <v>513598</v>
       </c>
       <c r="R4" t="n">
-        <v>6733249</v>
+        <v>6733234</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252821</v>
+        <v>123252664</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513598</v>
+        <v>513616</v>
       </c>
       <c r="R5" t="n">
-        <v>6733234</v>
+        <v>6733249</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123253165</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>123252664</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
         <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252664</v>
+        <v>123253165</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513616</v>
+        <v>513623</v>
       </c>
       <c r="R5" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652219</v>
+        <v>123652201</v>
       </c>
       <c r="B31" t="n">
         <v>98379</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513609</v>
+        <v>513640</v>
       </c>
       <c r="R31" t="n">
-        <v>6733267</v>
+        <v>6733246</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,7 +4327,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652201</v>
+        <v>123652219</v>
       </c>
       <c r="B32" t="n">
         <v>98379</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513640</v>
+        <v>513609</v>
       </c>
       <c r="R32" t="n">
-        <v>6733246</v>
+        <v>6733267</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4815,10 +4815,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123656499</v>
+        <v>123652178</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>98379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4827,25 +4827,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513625</v>
+        <v>513605</v>
       </c>
       <c r="R36" t="n">
-        <v>6733311</v>
+        <v>6733242</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4904,7 +4904,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4932,10 +4937,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652178</v>
+        <v>123656505</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>57497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4944,31 +4949,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4976,10 +4985,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513605</v>
+        <v>513624</v>
       </c>
       <c r="R37" t="n">
-        <v>6733242</v>
+        <v>6733235</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5011,7 +5020,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5021,12 +5030,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5035,7 +5044,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5054,10 +5062,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123656505</v>
+        <v>123656499</v>
       </c>
       <c r="B38" t="n">
-        <v>57497</v>
+        <v>97333</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5066,35 +5074,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5102,13 +5106,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513624</v>
+        <v>513625</v>
       </c>
       <c r="R38" t="n">
-        <v>6733235</v>
+        <v>6733311</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5137,7 +5141,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5147,12 +5151,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5161,6 +5160,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652168</v>
+        <v>123652212</v>
       </c>
       <c r="B39" t="n">
         <v>98379</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513593</v>
+        <v>513623</v>
       </c>
       <c r="R39" t="n">
-        <v>6733228</v>
+        <v>6733260</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5301,7 +5301,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652212</v>
+        <v>123652205</v>
       </c>
       <c r="B40" t="n">
         <v>98379</v>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513623</v>
+        <v>513635</v>
       </c>
       <c r="R40" t="n">
-        <v>6733260</v>
+        <v>6733245</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5423,7 +5423,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652205</v>
+        <v>123652190</v>
       </c>
       <c r="B41" t="n">
         <v>98379</v>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513635</v>
+        <v>513627</v>
       </c>
       <c r="R41" t="n">
-        <v>6733245</v>
+        <v>6733227</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5545,7 +5545,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652190</v>
+        <v>123652168</v>
       </c>
       <c r="B42" t="n">
         <v>98379</v>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513627</v>
+        <v>513593</v>
       </c>
       <c r="R42" t="n">
-        <v>6733227</v>
+        <v>6733228</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6277,10 +6277,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123650526</v>
+        <v>123652204</v>
       </c>
       <c r="B48" t="n">
-        <v>56683</v>
+        <v>98379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6289,35 +6289,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6325,10 +6321,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513627</v>
+        <v>513632</v>
       </c>
       <c r="R48" t="n">
-        <v>6733250</v>
+        <v>6733247</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6360,7 +6356,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6370,12 +6366,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,6 +6380,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6402,7 +6399,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652204</v>
+        <v>123652226</v>
       </c>
       <c r="B49" t="n">
         <v>98379</v>
@@ -6446,10 +6443,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513632</v>
+        <v>513622</v>
       </c>
       <c r="R49" t="n">
-        <v>6733247</v>
+        <v>6733236</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6481,7 +6478,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6491,12 +6488,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6524,10 +6521,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652226</v>
+        <v>123650526</v>
       </c>
       <c r="B50" t="n">
-        <v>98379</v>
+        <v>56683</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6536,31 +6533,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6568,10 +6569,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513622</v>
+        <v>513627</v>
       </c>
       <c r="R50" t="n">
-        <v>6733236</v>
+        <v>6733250</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6603,7 +6604,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6613,12 +6614,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6627,7 +6628,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123253272</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252664</v>
+        <v>123253165</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513616</v>
+        <v>513623</v>
       </c>
       <c r="R3" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
         <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R5" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123656504</v>
+        <v>123652209</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,35 +1167,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513643</v>
+        <v>513620</v>
       </c>
       <c r="R6" t="n">
-        <v>6733240</v>
+        <v>6733253</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1258,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652214</v>
+        <v>123652226</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513615</v>
+        <v>513622</v>
       </c>
       <c r="R7" t="n">
-        <v>6733271</v>
+        <v>6733236</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652206</v>
+        <v>123652189</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513623</v>
+        <v>513629</v>
       </c>
       <c r="R8" t="n">
-        <v>6733237</v>
+        <v>6733228</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1481,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652164</v>
+        <v>123656504</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,31 +1533,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1568,7 +1569,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513617</v>
+        <v>513643</v>
       </c>
       <c r="R9" t="n">
         <v>6733240</v>
@@ -1603,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1614,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,7 +1628,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123650528</v>
+        <v>123652185</v>
       </c>
       <c r="B10" t="n">
-        <v>56683</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,35 +1658,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1694,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513632</v>
+        <v>513619</v>
       </c>
       <c r="R10" t="n">
-        <v>6733214</v>
+        <v>6733240</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1729,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1739,7 +1735,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,6 +1749,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1759,17 +1761,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652207</v>
+        <v>123652194</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513629</v>
+        <v>513642</v>
       </c>
       <c r="R11" t="n">
-        <v>6733245</v>
+        <v>6733220</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1845,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1855,12 +1857,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652211</v>
+        <v>123652219</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513625</v>
+        <v>513609</v>
       </c>
       <c r="R12" t="n">
-        <v>6733258</v>
+        <v>6733267</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1967,7 +1969,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1977,12 +1979,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652182</v>
+        <v>123652163</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2054,13 +2056,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513620</v>
+        <v>513621</v>
       </c>
       <c r="R13" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2089,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2099,7 +2101,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2132,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652210</v>
+        <v>123652186</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2176,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513625</v>
+        <v>513623</v>
       </c>
       <c r="R14" t="n">
-        <v>6733251</v>
+        <v>6733238</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2211,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2221,12 +2223,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652213</v>
+        <v>123652218</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2298,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513617</v>
+        <v>513613</v>
       </c>
       <c r="R15" t="n">
-        <v>6733269</v>
+        <v>6733273</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2333,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652193</v>
+        <v>123652221</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513631</v>
+        <v>513613</v>
       </c>
       <c r="R16" t="n">
-        <v>6733221</v>
+        <v>6733269</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2455,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2498,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652160</v>
+        <v>123652201</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2542,7 +2544,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513608</v>
+        <v>513640</v>
       </c>
       <c r="R17" t="n">
         <v>6733246</v>
@@ -2577,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2587,12 +2589,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,10 +2622,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123656503</v>
+        <v>123652205</v>
       </c>
       <c r="B18" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,35 +2634,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2668,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513619</v>
+        <v>513635</v>
       </c>
       <c r="R18" t="n">
-        <v>6733230</v>
+        <v>6733245</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2703,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2713,12 +2711,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,6 +2725,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2745,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123656502</v>
+        <v>123652184</v>
       </c>
       <c r="B19" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2757,35 +2756,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2793,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513623</v>
+        <v>513618</v>
       </c>
       <c r="R19" t="n">
-        <v>6733240</v>
+        <v>6733235</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2828,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2838,12 +2833,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2852,6 +2847,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2870,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652208</v>
+        <v>123652161</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513626</v>
+        <v>513597</v>
       </c>
       <c r="R20" t="n">
-        <v>6733254</v>
+        <v>6733265</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2949,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2959,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2985,17 +2981,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652203</v>
+        <v>123652160</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3036,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513639</v>
+        <v>513608</v>
       </c>
       <c r="R21" t="n">
-        <v>6733252</v>
+        <v>6733246</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3071,7 +3067,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3081,12 +3077,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3114,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652179</v>
+        <v>123652210</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3158,10 +3154,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513611</v>
+        <v>513625</v>
       </c>
       <c r="R22" t="n">
-        <v>6733236</v>
+        <v>6733251</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3193,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3203,12 +3199,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3236,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652186</v>
+        <v>123652178</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3280,10 +3276,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513623</v>
+        <v>513605</v>
       </c>
       <c r="R23" t="n">
-        <v>6733238</v>
+        <v>6733242</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3315,7 +3311,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3321,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3358,10 +3354,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652195</v>
+        <v>123652174</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3402,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513645</v>
+        <v>513606</v>
       </c>
       <c r="R24" t="n">
-        <v>6733241</v>
+        <v>6733257</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3437,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3447,12 +3443,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3480,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652175</v>
+        <v>123650528</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>56689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3492,31 +3488,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513606</v>
+        <v>513632</v>
       </c>
       <c r="R25" t="n">
-        <v>6733254</v>
+        <v>6733214</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3569,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3583,7 +3578,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3595,17 +3589,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123650527</v>
+        <v>123652192</v>
       </c>
       <c r="B26" t="n">
-        <v>56683</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3614,35 +3608,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3650,10 +3640,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513634</v>
+        <v>513630</v>
       </c>
       <c r="R26" t="n">
-        <v>6733215</v>
+        <v>6733221</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3683,14 +3673,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3699,6 +3699,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3717,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652217</v>
+        <v>123650526</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>56689</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3729,31 +3730,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3761,10 +3766,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513612</v>
+        <v>513627</v>
       </c>
       <c r="R27" t="n">
-        <v>6733277</v>
+        <v>6733250</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3796,7 +3801,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3806,12 +3811,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3820,7 +3825,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3839,10 +3843,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652221</v>
+        <v>123652182</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,10 +3887,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513613</v>
+        <v>513620</v>
       </c>
       <c r="R28" t="n">
-        <v>6733269</v>
+        <v>6733241</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3918,7 +3922,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3928,12 +3932,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3961,10 +3965,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652188</v>
+        <v>123652217</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4005,10 +4009,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513629</v>
+        <v>513612</v>
       </c>
       <c r="R29" t="n">
-        <v>6733239</v>
+        <v>6733277</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4040,7 +4044,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4050,12 +4054,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4083,10 +4087,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652189</v>
+        <v>123652162</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4127,10 +4131,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513629</v>
+        <v>513604</v>
       </c>
       <c r="R30" t="n">
-        <v>6733228</v>
+        <v>6733250</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4172,12 +4176,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4205,10 +4209,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652201</v>
+        <v>123652197</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4249,10 +4253,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513640</v>
+        <v>513644</v>
       </c>
       <c r="R31" t="n">
-        <v>6733246</v>
+        <v>6733242</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4284,7 +4288,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4294,7 +4298,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4327,10 +4331,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652219</v>
+        <v>123652169</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4371,10 +4375,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513609</v>
+        <v>513603</v>
       </c>
       <c r="R32" t="n">
-        <v>6733267</v>
+        <v>6733229</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4416,12 +4420,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4449,10 +4453,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652209</v>
+        <v>123656505</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4461,31 +4465,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4493,10 +4501,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513620</v>
+        <v>513624</v>
       </c>
       <c r="R33" t="n">
-        <v>6733253</v>
+        <v>6733235</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4528,7 +4536,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4538,12 +4546,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,7 +4560,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4571,10 +4578,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652173</v>
+        <v>123652180</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4615,10 +4622,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513600</v>
+        <v>513623</v>
       </c>
       <c r="R34" t="n">
-        <v>6733258</v>
+        <v>6733239</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4650,7 +4657,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4660,7 +4667,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4693,10 +4700,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652202</v>
+        <v>123652222</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4737,10 +4744,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513640</v>
+        <v>513612</v>
       </c>
       <c r="R35" t="n">
-        <v>6733250</v>
+        <v>6733260</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4772,7 +4779,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4782,7 +4789,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4815,10 +4822,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652178</v>
+        <v>123652220</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4859,10 +4866,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513605</v>
+        <v>513609</v>
       </c>
       <c r="R36" t="n">
-        <v>6733242</v>
+        <v>6733266</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4894,7 +4901,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4904,12 +4911,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4937,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123656505</v>
+        <v>123652175</v>
       </c>
       <c r="B37" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4949,35 +4956,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4985,10 +4988,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513624</v>
+        <v>513606</v>
       </c>
       <c r="R37" t="n">
-        <v>6733235</v>
+        <v>6733254</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5020,7 +5023,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5030,12 +5033,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5044,6 +5047,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5062,10 +5066,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123656499</v>
+        <v>123652207</v>
       </c>
       <c r="B38" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5074,25 +5078,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5106,13 +5110,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513625</v>
+        <v>513629</v>
       </c>
       <c r="R38" t="n">
-        <v>6733311</v>
+        <v>6733245</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5141,7 +5145,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5151,7 +5155,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5179,10 +5188,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652212</v>
+        <v>123652181</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5223,10 +5232,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513623</v>
+        <v>513619</v>
       </c>
       <c r="R39" t="n">
-        <v>6733260</v>
+        <v>6733234</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5258,7 +5267,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5268,12 +5277,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5301,10 +5310,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652205</v>
+        <v>123652195</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5345,10 +5354,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513635</v>
+        <v>513645</v>
       </c>
       <c r="R40" t="n">
-        <v>6733245</v>
+        <v>6733241</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5380,7 +5389,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5390,12 +5399,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5423,10 +5432,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652190</v>
+        <v>123650523</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>56689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5435,31 +5444,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5467,10 +5484,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513627</v>
+        <v>513585</v>
       </c>
       <c r="R41" t="n">
-        <v>6733227</v>
+        <v>6733249</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5502,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5512,12 +5529,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5526,7 +5543,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5545,10 +5561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652168</v>
+        <v>123652211</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5589,10 +5605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513593</v>
+        <v>513625</v>
       </c>
       <c r="R42" t="n">
-        <v>6733228</v>
+        <v>6733258</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5624,7 +5640,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5634,12 +5650,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5667,10 +5683,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652225</v>
+        <v>123652214</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5711,10 +5727,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513617</v>
+        <v>513615</v>
       </c>
       <c r="R43" t="n">
-        <v>6733234</v>
+        <v>6733271</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5746,7 +5762,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5756,12 +5772,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5789,10 +5805,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652216</v>
+        <v>123652164</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5833,10 +5849,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513614</v>
+        <v>513617</v>
       </c>
       <c r="R44" t="n">
-        <v>6733272</v>
+        <v>6733240</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5868,7 +5884,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5878,12 +5894,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5911,10 +5927,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652197</v>
+        <v>123652213</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5955,10 +5971,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513644</v>
+        <v>513617</v>
       </c>
       <c r="R45" t="n">
-        <v>6733242</v>
+        <v>6733269</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5990,7 +6006,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6000,7 +6016,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6033,10 +6049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652191</v>
+        <v>123652204</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6077,10 +6093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513628</v>
+        <v>513632</v>
       </c>
       <c r="R46" t="n">
-        <v>6733228</v>
+        <v>6733247</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6112,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6122,12 +6138,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6155,10 +6171,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652177</v>
+        <v>123652173</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6199,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513615</v>
+        <v>513600</v>
       </c>
       <c r="R47" t="n">
-        <v>6733245</v>
+        <v>6733258</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6244,7 +6260,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6277,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652204</v>
+        <v>123656502</v>
       </c>
       <c r="B48" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6289,31 +6305,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6321,10 +6341,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513632</v>
+        <v>513623</v>
       </c>
       <c r="R48" t="n">
-        <v>6733247</v>
+        <v>6733240</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6356,7 +6376,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6366,12 +6386,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6380,7 +6400,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6399,10 +6418,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652226</v>
+        <v>123656503</v>
       </c>
       <c r="B49" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6411,31 +6430,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6443,10 +6466,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513622</v>
+        <v>513619</v>
       </c>
       <c r="R49" t="n">
-        <v>6733236</v>
+        <v>6733230</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6478,7 +6501,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6488,12 +6511,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6502,7 +6525,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6521,10 +6543,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123650526</v>
+        <v>123652187</v>
       </c>
       <c r="B50" t="n">
-        <v>56683</v>
+        <v>98396</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6533,35 +6555,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6572,7 +6590,7 @@
         <v>513627</v>
       </c>
       <c r="R50" t="n">
-        <v>6733250</v>
+        <v>6733241</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6604,7 +6622,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6614,12 +6632,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6628,6 +6646,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6646,10 +6665,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652224</v>
+        <v>123652206</v>
       </c>
       <c r="B51" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6690,10 +6709,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513610</v>
+        <v>513623</v>
       </c>
       <c r="R51" t="n">
-        <v>6733242</v>
+        <v>6733237</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6725,7 +6744,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6735,12 +6754,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6768,10 +6787,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652181</v>
+        <v>123652223</v>
       </c>
       <c r="B52" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6812,10 +6831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513619</v>
+        <v>513611</v>
       </c>
       <c r="R52" t="n">
-        <v>6733234</v>
+        <v>6733249</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6847,7 +6866,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6857,12 +6876,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6890,10 +6909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652185</v>
+        <v>123652203</v>
       </c>
       <c r="B53" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6934,10 +6953,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513619</v>
+        <v>513639</v>
       </c>
       <c r="R53" t="n">
-        <v>6733240</v>
+        <v>6733252</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6969,7 +6988,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6979,12 +6998,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7012,10 +7031,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652169</v>
+        <v>123652168</v>
       </c>
       <c r="B54" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7056,10 +7075,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513603</v>
+        <v>513593</v>
       </c>
       <c r="R54" t="n">
-        <v>6733229</v>
+        <v>6733228</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7091,7 +7110,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7101,7 +7120,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7134,10 +7153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652170</v>
+        <v>123650524</v>
       </c>
       <c r="B55" t="n">
-        <v>98379</v>
+        <v>56689</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7146,31 +7165,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7178,10 +7205,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513607</v>
+        <v>513595</v>
       </c>
       <c r="R55" t="n">
-        <v>6733239</v>
+        <v>6733257</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7213,7 +7240,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7223,12 +7250,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7237,7 +7259,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7256,10 +7277,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652174</v>
+        <v>123652202</v>
       </c>
       <c r="B56" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7300,10 +7321,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513606</v>
+        <v>513640</v>
       </c>
       <c r="R56" t="n">
-        <v>6733257</v>
+        <v>6733250</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7335,7 +7356,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7345,12 +7366,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7378,10 +7399,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652184</v>
+        <v>123652179</v>
       </c>
       <c r="B57" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7422,10 +7443,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513618</v>
+        <v>513611</v>
       </c>
       <c r="R57" t="n">
-        <v>6733235</v>
+        <v>6733236</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7457,7 +7478,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7467,12 +7488,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7500,10 +7521,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652187</v>
+        <v>123652208</v>
       </c>
       <c r="B58" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7544,10 +7565,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513627</v>
+        <v>513626</v>
       </c>
       <c r="R58" t="n">
-        <v>6733241</v>
+        <v>6733254</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7579,7 +7600,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7589,12 +7610,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7622,10 +7643,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652192</v>
+        <v>123652190</v>
       </c>
       <c r="B59" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7666,10 +7687,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513630</v>
+        <v>513627</v>
       </c>
       <c r="R59" t="n">
-        <v>6733221</v>
+        <v>6733227</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7701,7 +7722,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7711,7 +7732,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7744,10 +7765,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123650523</v>
+        <v>123656499</v>
       </c>
       <c r="B60" t="n">
-        <v>56683</v>
+        <v>97350</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7756,39 +7777,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7796,13 +7809,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513585</v>
+        <v>513625</v>
       </c>
       <c r="R60" t="n">
-        <v>6733249</v>
+        <v>6733311</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7831,7 +7844,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7841,12 +7854,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7855,6 +7863,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7873,10 +7882,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652220</v>
+        <v>123652224</v>
       </c>
       <c r="B61" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7917,10 +7926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513609</v>
+        <v>513610</v>
       </c>
       <c r="R61" t="n">
-        <v>6733266</v>
+        <v>6733242</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7952,7 +7961,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7962,12 +7971,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7995,10 +8004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652200</v>
+        <v>123652225</v>
       </c>
       <c r="B62" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8039,10 +8048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513638</v>
+        <v>513617</v>
       </c>
       <c r="R62" t="n">
-        <v>6733248</v>
+        <v>6733234</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8074,7 +8083,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8084,7 +8093,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8117,10 +8126,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652199</v>
+        <v>123652212</v>
       </c>
       <c r="B63" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8161,10 +8170,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513642</v>
+        <v>513623</v>
       </c>
       <c r="R63" t="n">
-        <v>6733246</v>
+        <v>6733260</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8196,7 +8205,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8206,12 +8215,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8239,10 +8248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652161</v>
+        <v>123652177</v>
       </c>
       <c r="B64" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8283,10 +8292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513597</v>
+        <v>513615</v>
       </c>
       <c r="R64" t="n">
-        <v>6733265</v>
+        <v>6733245</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8318,7 +8327,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8328,12 +8337,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8354,17 +8363,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652176</v>
+        <v>123652199</v>
       </c>
       <c r="B65" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8405,10 +8414,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513605</v>
+        <v>513642</v>
       </c>
       <c r="R65" t="n">
-        <v>6733249</v>
+        <v>6733246</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8440,7 +8449,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8450,12 +8459,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8483,10 +8492,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652222</v>
+        <v>123656500</v>
       </c>
       <c r="B66" t="n">
-        <v>98379</v>
+        <v>5174</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8495,31 +8504,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8527,13 +8537,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513612</v>
+        <v>513668</v>
       </c>
       <c r="R66" t="n">
-        <v>6733260</v>
+        <v>6733244</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8557,27 +8567,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8598,17 +8603,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652218</v>
+        <v>123652188</v>
       </c>
       <c r="B67" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8649,10 +8654,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513613</v>
+        <v>513629</v>
       </c>
       <c r="R67" t="n">
-        <v>6733273</v>
+        <v>6733239</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8684,7 +8689,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8694,12 +8699,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8727,10 +8732,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652194</v>
+        <v>123652200</v>
       </c>
       <c r="B68" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8771,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513642</v>
+        <v>513638</v>
       </c>
       <c r="R68" t="n">
-        <v>6733220</v>
+        <v>6733248</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8806,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8816,12 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8849,10 +8854,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652162</v>
+        <v>123652191</v>
       </c>
       <c r="B69" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8893,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513604</v>
+        <v>513628</v>
       </c>
       <c r="R69" t="n">
-        <v>6733250</v>
+        <v>6733228</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8928,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8938,7 +8943,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8971,10 +8976,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123650524</v>
+        <v>123650527</v>
       </c>
       <c r="B70" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9006,14 +9011,10 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9023,10 +9024,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513595</v>
+        <v>513634</v>
       </c>
       <c r="R70" t="n">
-        <v>6733257</v>
+        <v>6733215</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9056,19 +9057,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:52</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9095,10 +9091,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652180</v>
+        <v>123652170</v>
       </c>
       <c r="B71" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9139,7 +9135,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513623</v>
+        <v>513607</v>
       </c>
       <c r="R71" t="n">
         <v>6733239</v>
@@ -9174,7 +9170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9184,7 +9180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -9217,10 +9213,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652171</v>
+        <v>123652193</v>
       </c>
       <c r="B72" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9261,10 +9257,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513608</v>
+        <v>513631</v>
       </c>
       <c r="R72" t="n">
-        <v>6733238</v>
+        <v>6733221</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9296,7 +9292,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9306,12 +9302,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9339,10 +9335,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652163</v>
+        <v>123652171</v>
       </c>
       <c r="B73" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9383,13 +9379,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513621</v>
+        <v>513608</v>
       </c>
       <c r="R73" t="n">
-        <v>6733235</v>
+        <v>6733238</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9418,7 +9414,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9428,7 +9424,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -9461,10 +9457,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652223</v>
+        <v>123652216</v>
       </c>
       <c r="B74" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9505,10 +9501,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513611</v>
+        <v>513614</v>
       </c>
       <c r="R74" t="n">
-        <v>6733249</v>
+        <v>6733272</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9540,7 +9536,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9550,12 +9546,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9583,10 +9579,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123656500</v>
+        <v>123652176</v>
       </c>
       <c r="B75" t="n">
-        <v>5173</v>
+        <v>98396</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9595,32 +9591,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9628,13 +9623,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513668</v>
+        <v>513605</v>
       </c>
       <c r="R75" t="n">
-        <v>6733244</v>
+        <v>6733249</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9658,22 +9653,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1768,7 +1768,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652194</v>
+        <v>123652163</v>
       </c>
       <c r="B11" t="n">
         <v>98396</v>
@@ -1812,13 +1812,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513642</v>
+        <v>513621</v>
       </c>
       <c r="R11" t="n">
-        <v>6733220</v>
+        <v>6733235</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1890,7 +1890,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652219</v>
+        <v>123652194</v>
       </c>
       <c r="B12" t="n">
         <v>98396</v>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513609</v>
+        <v>513642</v>
       </c>
       <c r="R12" t="n">
-        <v>6733267</v>
+        <v>6733220</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,7 +2012,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652163</v>
+        <v>123652219</v>
       </c>
       <c r="B13" t="n">
         <v>98396</v>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513621</v>
+        <v>513609</v>
       </c>
       <c r="R13" t="n">
-        <v>6733235</v>
+        <v>6733267</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2378,7 +2378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652221</v>
+        <v>123652201</v>
       </c>
       <c r="B16" t="n">
         <v>98396</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513613</v>
+        <v>513640</v>
       </c>
       <c r="R16" t="n">
-        <v>6733269</v>
+        <v>6733246</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2500,7 +2500,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652201</v>
+        <v>123652205</v>
       </c>
       <c r="B17" t="n">
         <v>98396</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513640</v>
+        <v>513635</v>
       </c>
       <c r="R17" t="n">
-        <v>6733246</v>
+        <v>6733245</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2622,7 +2622,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652205</v>
+        <v>123652184</v>
       </c>
       <c r="B18" t="n">
         <v>98396</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513635</v>
+        <v>513618</v>
       </c>
       <c r="R18" t="n">
-        <v>6733245</v>
+        <v>6733235</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,7 +2744,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652184</v>
+        <v>123652161</v>
       </c>
       <c r="B19" t="n">
         <v>98396</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513618</v>
+        <v>513597</v>
       </c>
       <c r="R19" t="n">
-        <v>6733235</v>
+        <v>6733265</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652161</v>
+        <v>123652221</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513597</v>
+        <v>513613</v>
       </c>
       <c r="R20" t="n">
-        <v>6733265</v>
+        <v>6733269</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652162</v>
+        <v>123652197</v>
       </c>
       <c r="B30" t="n">
         <v>98396</v>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513604</v>
+        <v>513644</v>
       </c>
       <c r="R30" t="n">
-        <v>6733250</v>
+        <v>6733242</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652197</v>
+        <v>123652162</v>
       </c>
       <c r="B31" t="n">
         <v>98396</v>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513644</v>
+        <v>513604</v>
       </c>
       <c r="R31" t="n">
-        <v>6733242</v>
+        <v>6733250</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6049,7 +6049,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652204</v>
+        <v>123652173</v>
       </c>
       <c r="B46" t="n">
         <v>98396</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513632</v>
+        <v>513600</v>
       </c>
       <c r="R46" t="n">
-        <v>6733247</v>
+        <v>6733258</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6171,7 +6171,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652173</v>
+        <v>123652204</v>
       </c>
       <c r="B47" t="n">
         <v>98396</v>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513600</v>
+        <v>513632</v>
       </c>
       <c r="R47" t="n">
-        <v>6733258</v>
+        <v>6733247</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123656502</v>
+        <v>123652187</v>
       </c>
       <c r="B48" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,35 +6305,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6341,10 +6337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R48" t="n">
-        <v>6733240</v>
+        <v>6733241</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6376,7 +6372,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6386,12 +6382,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6400,6 +6396,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6418,10 +6415,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123656503</v>
+        <v>123652206</v>
       </c>
       <c r="B49" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6430,35 +6427,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6466,10 +6459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513619</v>
+        <v>513623</v>
       </c>
       <c r="R49" t="n">
-        <v>6733230</v>
+        <v>6733237</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6501,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6511,12 +6504,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6525,6 +6518,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6543,7 +6537,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652187</v>
+        <v>123652223</v>
       </c>
       <c r="B50" t="n">
         <v>98396</v>
@@ -6587,10 +6581,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513627</v>
+        <v>513611</v>
       </c>
       <c r="R50" t="n">
-        <v>6733241</v>
+        <v>6733249</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6622,7 +6616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6632,12 +6626,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6665,7 +6659,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652206</v>
+        <v>123652203</v>
       </c>
       <c r="B51" t="n">
         <v>98396</v>
@@ -6709,10 +6703,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513623</v>
+        <v>513639</v>
       </c>
       <c r="R51" t="n">
-        <v>6733237</v>
+        <v>6733252</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6744,7 +6738,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6754,12 +6748,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6787,7 +6781,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652223</v>
+        <v>123652168</v>
       </c>
       <c r="B52" t="n">
         <v>98396</v>
@@ -6831,10 +6825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513611</v>
+        <v>513593</v>
       </c>
       <c r="R52" t="n">
-        <v>6733249</v>
+        <v>6733228</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6866,7 +6860,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6876,12 +6870,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6909,10 +6903,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652203</v>
+        <v>123656502</v>
       </c>
       <c r="B53" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6921,31 +6915,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6953,10 +6951,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513639</v>
+        <v>513623</v>
       </c>
       <c r="R53" t="n">
-        <v>6733252</v>
+        <v>6733240</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6988,7 +6986,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6998,12 +6996,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7012,7 +7010,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7031,10 +7028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652168</v>
+        <v>123656503</v>
       </c>
       <c r="B54" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7043,31 +7040,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7075,10 +7076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513593</v>
+        <v>513619</v>
       </c>
       <c r="R54" t="n">
-        <v>6733228</v>
+        <v>6733230</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7110,7 +7111,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7120,12 +7121,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7134,7 +7135,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -8492,10 +8492,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123656500</v>
+        <v>123652191</v>
       </c>
       <c r="B66" t="n">
-        <v>5174</v>
+        <v>98396</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8504,32 +8504,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8537,13 +8536,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513668</v>
+        <v>513628</v>
       </c>
       <c r="R66" t="n">
-        <v>6733244</v>
+        <v>6733228</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8567,22 +8566,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8603,17 +8607,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652188</v>
+        <v>123656500</v>
       </c>
       <c r="B67" t="n">
-        <v>98396</v>
+        <v>5174</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8622,31 +8626,32 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8654,13 +8659,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513629</v>
+        <v>513668</v>
       </c>
       <c r="R67" t="n">
-        <v>6733239</v>
+        <v>6733244</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8684,27 +8689,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652200</v>
+        <v>123650527</v>
       </c>
       <c r="B68" t="n">
-        <v>98396</v>
+        <v>56689</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8744,31 +8744,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8776,10 +8780,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513638</v>
+        <v>513634</v>
       </c>
       <c r="R68" t="n">
-        <v>6733248</v>
+        <v>6733215</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8809,24 +8813,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8835,7 +8829,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8854,7 +8847,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652191</v>
+        <v>123652188</v>
       </c>
       <c r="B69" t="n">
         <v>98396</v>
@@ -8898,10 +8891,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513628</v>
+        <v>513629</v>
       </c>
       <c r="R69" t="n">
-        <v>6733228</v>
+        <v>6733239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8933,7 +8926,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,7 +8936,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8976,10 +8969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123650527</v>
+        <v>123652200</v>
       </c>
       <c r="B70" t="n">
-        <v>56689</v>
+        <v>98396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8988,35 +8981,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9024,10 +9013,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513634</v>
+        <v>513638</v>
       </c>
       <c r="R70" t="n">
-        <v>6733215</v>
+        <v>6733248</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9057,14 +9046,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9073,6 +9072,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9091,7 +9091,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652170</v>
+        <v>123652193</v>
       </c>
       <c r="B71" t="n">
         <v>98396</v>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513607</v>
+        <v>513631</v>
       </c>
       <c r="R71" t="n">
-        <v>6733239</v>
+        <v>6733221</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9213,7 +9213,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652193</v>
+        <v>123652171</v>
       </c>
       <c r="B72" t="n">
         <v>98396</v>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513631</v>
+        <v>513608</v>
       </c>
       <c r="R72" t="n">
-        <v>6733221</v>
+        <v>6733238</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9302,12 +9302,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9335,7 +9335,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652171</v>
+        <v>123652170</v>
       </c>
       <c r="B73" t="n">
         <v>98396</v>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513608</v>
+        <v>513607</v>
       </c>
       <c r="R73" t="n">
-        <v>6733238</v>
+        <v>6733239</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -2378,7 +2378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652201</v>
+        <v>123652221</v>
       </c>
       <c r="B16" t="n">
         <v>98396</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513640</v>
+        <v>513613</v>
       </c>
       <c r="R16" t="n">
-        <v>6733246</v>
+        <v>6733269</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2500,7 +2500,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652205</v>
+        <v>123652201</v>
       </c>
       <c r="B17" t="n">
         <v>98396</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513635</v>
+        <v>513640</v>
       </c>
       <c r="R17" t="n">
-        <v>6733245</v>
+        <v>6733246</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2622,7 +2622,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652184</v>
+        <v>123652205</v>
       </c>
       <c r="B18" t="n">
         <v>98396</v>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513618</v>
+        <v>513635</v>
       </c>
       <c r="R18" t="n">
-        <v>6733235</v>
+        <v>6733245</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,7 +2744,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652161</v>
+        <v>123652184</v>
       </c>
       <c r="B19" t="n">
         <v>98396</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513597</v>
+        <v>513618</v>
       </c>
       <c r="R19" t="n">
-        <v>6733265</v>
+        <v>6733235</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652221</v>
+        <v>123652161</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513613</v>
+        <v>513597</v>
       </c>
       <c r="R20" t="n">
-        <v>6733269</v>
+        <v>6733265</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652173</v>
+        <v>123652204</v>
       </c>
       <c r="B46" t="n">
         <v>98396</v>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513600</v>
+        <v>513632</v>
       </c>
       <c r="R46" t="n">
-        <v>6733258</v>
+        <v>6733247</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6171,7 +6171,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652204</v>
+        <v>123652173</v>
       </c>
       <c r="B47" t="n">
         <v>98396</v>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513632</v>
+        <v>513600</v>
       </c>
       <c r="R47" t="n">
-        <v>6733247</v>
+        <v>6733258</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652187</v>
+        <v>123656502</v>
       </c>
       <c r="B48" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,31 +6305,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6337,10 +6341,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513627</v>
+        <v>513623</v>
       </c>
       <c r="R48" t="n">
-        <v>6733241</v>
+        <v>6733240</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6372,7 +6376,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6382,12 +6386,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6396,7 +6400,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6415,10 +6418,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652206</v>
+        <v>123656503</v>
       </c>
       <c r="B49" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6427,31 +6430,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6459,10 +6466,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513623</v>
+        <v>513619</v>
       </c>
       <c r="R49" t="n">
-        <v>6733237</v>
+        <v>6733230</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6494,7 +6501,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,12 +6511,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6518,7 +6525,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6537,7 +6543,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652223</v>
+        <v>123652187</v>
       </c>
       <c r="B50" t="n">
         <v>98396</v>
@@ -6581,10 +6587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513611</v>
+        <v>513627</v>
       </c>
       <c r="R50" t="n">
-        <v>6733249</v>
+        <v>6733241</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6616,7 +6622,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6626,12 +6632,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6659,7 +6665,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652203</v>
+        <v>123652206</v>
       </c>
       <c r="B51" t="n">
         <v>98396</v>
@@ -6703,10 +6709,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513639</v>
+        <v>513623</v>
       </c>
       <c r="R51" t="n">
-        <v>6733252</v>
+        <v>6733237</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6738,7 +6744,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6748,12 +6754,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6781,7 +6787,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652168</v>
+        <v>123652223</v>
       </c>
       <c r="B52" t="n">
         <v>98396</v>
@@ -6825,10 +6831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513593</v>
+        <v>513611</v>
       </c>
       <c r="R52" t="n">
-        <v>6733228</v>
+        <v>6733249</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6860,7 +6866,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6870,12 +6876,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6903,10 +6909,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123656502</v>
+        <v>123652203</v>
       </c>
       <c r="B53" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6915,35 +6921,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6951,10 +6953,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513623</v>
+        <v>513639</v>
       </c>
       <c r="R53" t="n">
-        <v>6733240</v>
+        <v>6733252</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6986,7 +6988,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6996,12 +6998,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7010,6 +7012,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7028,10 +7031,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123656503</v>
+        <v>123652168</v>
       </c>
       <c r="B54" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7040,35 +7043,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7076,10 +7075,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513619</v>
+        <v>513593</v>
       </c>
       <c r="R54" t="n">
-        <v>6733230</v>
+        <v>6733228</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7111,7 +7110,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7121,12 +7120,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7135,6 +7134,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -8492,10 +8492,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652191</v>
+        <v>123656500</v>
       </c>
       <c r="B66" t="n">
-        <v>98396</v>
+        <v>5174</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8504,31 +8504,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8536,13 +8537,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513628</v>
+        <v>513668</v>
       </c>
       <c r="R66" t="n">
-        <v>6733228</v>
+        <v>6733244</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8566,27 +8567,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8607,17 +8603,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123656500</v>
+        <v>123652188</v>
       </c>
       <c r="B67" t="n">
-        <v>5174</v>
+        <v>98396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8626,32 +8622,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8659,13 +8654,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513668</v>
+        <v>513629</v>
       </c>
       <c r="R67" t="n">
-        <v>6733244</v>
+        <v>6733239</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8689,22 +8684,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8725,17 +8725,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123650527</v>
+        <v>123652200</v>
       </c>
       <c r="B68" t="n">
-        <v>56689</v>
+        <v>98396</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8744,35 +8744,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8780,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513634</v>
+        <v>513638</v>
       </c>
       <c r="R68" t="n">
-        <v>6733215</v>
+        <v>6733248</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8813,14 +8809,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8829,6 +8835,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8847,7 +8854,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652188</v>
+        <v>123652191</v>
       </c>
       <c r="B69" t="n">
         <v>98396</v>
@@ -8891,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513629</v>
+        <v>513628</v>
       </c>
       <c r="R69" t="n">
-        <v>6733239</v>
+        <v>6733228</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8926,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8936,7 +8943,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8969,10 +8976,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652200</v>
+        <v>123650527</v>
       </c>
       <c r="B70" t="n">
-        <v>98396</v>
+        <v>56689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8981,31 +8988,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9013,10 +9024,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513638</v>
+        <v>513634</v>
       </c>
       <c r="R70" t="n">
-        <v>6733248</v>
+        <v>6733215</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9046,24 +9057,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9072,7 +9073,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123656504</v>
+        <v>123652185</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,35 +1533,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1569,7 +1565,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513643</v>
+        <v>513619</v>
       </c>
       <c r="R9" t="n">
         <v>6733240</v>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,6 +1624,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1646,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652185</v>
+        <v>123656504</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,31 +1655,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1690,7 +1691,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513619</v>
+        <v>513643</v>
       </c>
       <c r="R10" t="n">
         <v>6733240</v>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,12 +1736,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,7 +1750,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652197</v>
+        <v>123652162</v>
       </c>
       <c r="B30" t="n">
         <v>98396</v>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513644</v>
+        <v>513604</v>
       </c>
       <c r="R30" t="n">
-        <v>6733242</v>
+        <v>6733250</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652162</v>
+        <v>123652197</v>
       </c>
       <c r="B31" t="n">
         <v>98396</v>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513604</v>
+        <v>513644</v>
       </c>
       <c r="R31" t="n">
-        <v>6733250</v>
+        <v>6733242</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6293,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123656502</v>
+        <v>123652187</v>
       </c>
       <c r="B48" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,35 +6305,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6341,10 +6337,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R48" t="n">
-        <v>6733240</v>
+        <v>6733241</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6376,7 +6372,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6386,12 +6382,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6400,6 +6396,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6418,10 +6415,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123656503</v>
+        <v>123652206</v>
       </c>
       <c r="B49" t="n">
-        <v>57503</v>
+        <v>98396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6430,35 +6427,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6466,10 +6459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513619</v>
+        <v>513623</v>
       </c>
       <c r="R49" t="n">
-        <v>6733230</v>
+        <v>6733237</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6501,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6511,12 +6504,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6525,6 +6518,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6543,7 +6537,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652187</v>
+        <v>123652223</v>
       </c>
       <c r="B50" t="n">
         <v>98396</v>
@@ -6587,10 +6581,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513627</v>
+        <v>513611</v>
       </c>
       <c r="R50" t="n">
-        <v>6733241</v>
+        <v>6733249</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6622,7 +6616,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6632,12 +6626,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6665,7 +6659,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652206</v>
+        <v>123652203</v>
       </c>
       <c r="B51" t="n">
         <v>98396</v>
@@ -6709,10 +6703,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513623</v>
+        <v>513639</v>
       </c>
       <c r="R51" t="n">
-        <v>6733237</v>
+        <v>6733252</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6744,7 +6738,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6754,12 +6748,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6787,7 +6781,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652223</v>
+        <v>123652168</v>
       </c>
       <c r="B52" t="n">
         <v>98396</v>
@@ -6831,10 +6825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513611</v>
+        <v>513593</v>
       </c>
       <c r="R52" t="n">
-        <v>6733249</v>
+        <v>6733228</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6866,7 +6860,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6876,12 +6870,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6909,10 +6903,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652203</v>
+        <v>123656502</v>
       </c>
       <c r="B53" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6921,31 +6915,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6953,10 +6951,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513639</v>
+        <v>513623</v>
       </c>
       <c r="R53" t="n">
-        <v>6733252</v>
+        <v>6733240</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6988,7 +6986,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6998,12 +6996,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7012,7 +7010,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7031,10 +7028,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652168</v>
+        <v>123656503</v>
       </c>
       <c r="B54" t="n">
-        <v>98396</v>
+        <v>57503</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7043,31 +7040,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7075,10 +7076,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513593</v>
+        <v>513619</v>
       </c>
       <c r="R54" t="n">
-        <v>6733228</v>
+        <v>6733230</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7110,7 +7111,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7120,12 +7121,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7134,7 +7135,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123253272</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252821</v>
+        <v>123253165</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513598</v>
+        <v>513623</v>
       </c>
       <c r="R4" t="n">
-        <v>6733234</v>
+        <v>6733230</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252664</v>
+        <v>123252821</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513616</v>
+        <v>513598</v>
       </c>
       <c r="R5" t="n">
-        <v>6733249</v>
+        <v>6733234</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652209</v>
+        <v>123652216</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513620</v>
+        <v>513614</v>
       </c>
       <c r="R6" t="n">
-        <v>6733253</v>
+        <v>6733272</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652226</v>
+        <v>123652224</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513622</v>
+        <v>513610</v>
       </c>
       <c r="R7" t="n">
-        <v>6733236</v>
+        <v>6733242</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652189</v>
+        <v>123652175</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513629</v>
+        <v>513606</v>
       </c>
       <c r="R8" t="n">
-        <v>6733228</v>
+        <v>6733254</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652185</v>
+        <v>123652178</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513619</v>
+        <v>513605</v>
       </c>
       <c r="R9" t="n">
-        <v>6733240</v>
+        <v>6733242</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123656504</v>
+        <v>123652188</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,35 +1655,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513643</v>
+        <v>513629</v>
       </c>
       <c r="R10" t="n">
-        <v>6733240</v>
+        <v>6733239</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1726,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,12 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,6 +1746,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652163</v>
+        <v>123652205</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,13 +1809,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513621</v>
+        <v>513635</v>
       </c>
       <c r="R11" t="n">
-        <v>6733235</v>
+        <v>6733245</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1847,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,12 +1854,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652194</v>
+        <v>123652212</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513642</v>
+        <v>513623</v>
       </c>
       <c r="R12" t="n">
-        <v>6733220</v>
+        <v>6733260</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1969,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,12 +1976,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652219</v>
+        <v>123652197</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2056,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513609</v>
+        <v>513644</v>
       </c>
       <c r="R13" t="n">
-        <v>6733267</v>
+        <v>6733242</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2091,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,12 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652186</v>
+        <v>123652192</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2178,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513623</v>
+        <v>513630</v>
       </c>
       <c r="R14" t="n">
-        <v>6733238</v>
+        <v>6733221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2213,7 +2210,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,7 +2220,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2256,10 +2253,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652218</v>
+        <v>123652176</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,10 +2297,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513613</v>
+        <v>513605</v>
       </c>
       <c r="R15" t="n">
-        <v>6733273</v>
+        <v>6733249</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2335,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,12 +2342,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,10 +2375,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652221</v>
+        <v>123652203</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2422,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513613</v>
+        <v>513639</v>
       </c>
       <c r="R16" t="n">
-        <v>6733269</v>
+        <v>6733252</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2454,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2464,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652201</v>
+        <v>123652185</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2544,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513640</v>
+        <v>513619</v>
       </c>
       <c r="R17" t="n">
-        <v>6733246</v>
+        <v>6733240</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,12 +2586,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652205</v>
+        <v>123652162</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513635</v>
+        <v>513604</v>
       </c>
       <c r="R18" t="n">
-        <v>6733245</v>
+        <v>6733250</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2701,7 +2698,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,12 +2708,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2741,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652184</v>
+        <v>123656504</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,31 +2753,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2788,10 +2789,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513618</v>
+        <v>513643</v>
       </c>
       <c r="R19" t="n">
-        <v>6733235</v>
+        <v>6733240</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2823,7 +2824,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2833,12 +2834,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2847,7 +2848,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2866,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652161</v>
+        <v>123652208</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513597</v>
+        <v>513626</v>
       </c>
       <c r="R20" t="n">
-        <v>6733265</v>
+        <v>6733254</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652160</v>
+        <v>123652213</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513608</v>
+        <v>513617</v>
       </c>
       <c r="R21" t="n">
-        <v>6733246</v>
+        <v>6733269</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652210</v>
+        <v>123652200</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513625</v>
+        <v>513638</v>
       </c>
       <c r="R22" t="n">
-        <v>6733251</v>
+        <v>6733248</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3232,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652178</v>
+        <v>123652174</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513605</v>
+        <v>513606</v>
       </c>
       <c r="R23" t="n">
-        <v>6733242</v>
+        <v>6733257</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652174</v>
+        <v>123652219</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513606</v>
+        <v>513609</v>
       </c>
       <c r="R24" t="n">
-        <v>6733257</v>
+        <v>6733267</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123650528</v>
+        <v>123652223</v>
       </c>
       <c r="B25" t="n">
-        <v>56689</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3488,35 +3488,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3524,10 +3520,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513632</v>
+        <v>513611</v>
       </c>
       <c r="R25" t="n">
-        <v>6733214</v>
+        <v>6733249</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3559,7 +3555,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,7 +3565,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3578,6 +3579,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3589,17 +3591,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652192</v>
+        <v>123652221</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3640,10 +3642,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513630</v>
+        <v>513613</v>
       </c>
       <c r="R26" t="n">
-        <v>6733221</v>
+        <v>6733269</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3675,7 +3677,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3685,12 +3687,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123650526</v>
+        <v>123656502</v>
       </c>
       <c r="B27" t="n">
-        <v>56689</v>
+        <v>57506</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3734,16 +3736,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3756,7 +3758,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3766,10 +3768,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513627</v>
+        <v>513623</v>
       </c>
       <c r="R27" t="n">
-        <v>6733250</v>
+        <v>6733240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3801,7 +3803,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3811,12 +3813,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,10 +3845,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652182</v>
+        <v>123656505</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3855,31 +3857,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3887,10 +3893,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513620</v>
+        <v>513624</v>
       </c>
       <c r="R28" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3922,7 +3928,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3932,12 +3938,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3946,7 +3952,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3965,10 +3970,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652217</v>
+        <v>123652170</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4009,10 +4014,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513612</v>
+        <v>513607</v>
       </c>
       <c r="R29" t="n">
-        <v>6733277</v>
+        <v>6733239</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4044,7 +4049,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4054,12 +4059,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4087,10 +4092,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652162</v>
+        <v>123652209</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4131,10 +4136,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513604</v>
+        <v>513620</v>
       </c>
       <c r="R30" t="n">
-        <v>6733250</v>
+        <v>6733253</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4166,7 +4171,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4176,12 +4181,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4209,10 +4214,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652197</v>
+        <v>123652202</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513644</v>
+        <v>513640</v>
       </c>
       <c r="R31" t="n">
-        <v>6733242</v>
+        <v>6733250</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4288,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4298,7 +4303,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4331,10 +4336,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652169</v>
+        <v>123652189</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4375,10 +4380,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513603</v>
+        <v>513629</v>
       </c>
       <c r="R32" t="n">
-        <v>6733229</v>
+        <v>6733228</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4410,7 +4415,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4420,12 +4425,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4453,10 +4458,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123656505</v>
+        <v>123650524</v>
       </c>
       <c r="B33" t="n">
-        <v>57503</v>
+        <v>56692</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4469,16 +4474,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4488,10 +4493,14 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4501,10 +4510,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513624</v>
+        <v>513595</v>
       </c>
       <c r="R33" t="n">
-        <v>6733235</v>
+        <v>6733257</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4536,7 +4545,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4546,12 +4555,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4578,10 +4582,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652180</v>
+        <v>123652186</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4625,7 +4629,7 @@
         <v>513623</v>
       </c>
       <c r="R34" t="n">
-        <v>6733239</v>
+        <v>6733238</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4657,7 +4661,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4667,7 +4671,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4700,10 +4704,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652222</v>
+        <v>123652195</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4744,10 +4748,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513612</v>
+        <v>513645</v>
       </c>
       <c r="R35" t="n">
-        <v>6733260</v>
+        <v>6733241</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4779,7 +4783,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4789,12 +4793,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4822,10 +4826,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652220</v>
+        <v>123650527</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>56692</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4834,31 +4838,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4866,10 +4874,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513609</v>
+        <v>513634</v>
       </c>
       <c r="R36" t="n">
-        <v>6733266</v>
+        <v>6733215</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4899,24 +4907,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4925,7 +4923,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4944,10 +4941,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652175</v>
+        <v>123650528</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>56692</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4956,31 +4953,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4988,10 +4989,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513606</v>
+        <v>513632</v>
       </c>
       <c r="R37" t="n">
-        <v>6733254</v>
+        <v>6733214</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5023,7 +5024,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5033,12 +5034,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5047,7 +5043,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5059,17 +5054,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652207</v>
+        <v>123652187</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513629</v>
+        <v>513627</v>
       </c>
       <c r="R38" t="n">
-        <v>6733245</v>
+        <v>6733241</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5145,7 +5140,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5155,12 +5150,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5188,10 +5183,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652181</v>
+        <v>123652182</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5232,10 +5227,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513619</v>
+        <v>513620</v>
       </c>
       <c r="R39" t="n">
-        <v>6733234</v>
+        <v>6733241</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5267,7 +5262,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5277,7 +5272,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5310,10 +5305,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652195</v>
+        <v>123652181</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5354,10 +5349,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513645</v>
+        <v>513619</v>
       </c>
       <c r="R40" t="n">
-        <v>6733241</v>
+        <v>6733234</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5389,7 +5384,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5399,12 +5394,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,10 +5427,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123650523</v>
+        <v>123652210</v>
       </c>
       <c r="B41" t="n">
-        <v>56689</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5444,39 +5439,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5484,10 +5471,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513585</v>
+        <v>513625</v>
       </c>
       <c r="R41" t="n">
-        <v>6733249</v>
+        <v>6733251</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5519,7 +5506,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5529,12 +5516,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5543,6 +5530,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5561,10 +5549,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652211</v>
+        <v>123652199</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5605,10 +5593,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513625</v>
+        <v>513642</v>
       </c>
       <c r="R42" t="n">
-        <v>6733258</v>
+        <v>6733246</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5640,7 +5628,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5650,12 +5638,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5683,10 +5671,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652214</v>
+        <v>123652164</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5727,10 +5715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513615</v>
+        <v>513617</v>
       </c>
       <c r="R43" t="n">
-        <v>6733271</v>
+        <v>6733240</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5762,7 +5750,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5772,12 +5760,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5805,10 +5793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652164</v>
+        <v>123650526</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
+        <v>56692</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5817,31 +5805,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5849,10 +5841,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513617</v>
+        <v>513627</v>
       </c>
       <c r="R44" t="n">
-        <v>6733240</v>
+        <v>6733250</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5884,7 +5876,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5894,12 +5886,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5908,7 +5900,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5927,10 +5918,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652213</v>
+        <v>123656503</v>
       </c>
       <c r="B45" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5939,31 +5930,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5971,10 +5966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513617</v>
+        <v>513619</v>
       </c>
       <c r="R45" t="n">
-        <v>6733269</v>
+        <v>6733230</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6006,7 +6001,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6016,12 +6011,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6030,7 +6025,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6049,10 +6043,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652204</v>
+        <v>123652206</v>
       </c>
       <c r="B46" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6093,10 +6087,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513632</v>
+        <v>513623</v>
       </c>
       <c r="R46" t="n">
-        <v>6733247</v>
+        <v>6733237</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6128,7 +6122,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,7 +6132,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6171,10 +6165,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652173</v>
+        <v>123652222</v>
       </c>
       <c r="B47" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6215,10 +6209,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513600</v>
+        <v>513612</v>
       </c>
       <c r="R47" t="n">
-        <v>6733258</v>
+        <v>6733260</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6250,7 +6244,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6260,12 +6254,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652187</v>
+        <v>123652217</v>
       </c>
       <c r="B48" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6337,10 +6331,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513627</v>
+        <v>513612</v>
       </c>
       <c r="R48" t="n">
-        <v>6733241</v>
+        <v>6733277</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6372,7 +6366,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6382,12 +6376,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6415,10 +6409,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652206</v>
+        <v>123650523</v>
       </c>
       <c r="B49" t="n">
-        <v>98396</v>
+        <v>56692</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6427,31 +6421,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6459,10 +6461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513623</v>
+        <v>513585</v>
       </c>
       <c r="R49" t="n">
-        <v>6733237</v>
+        <v>6733249</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6494,7 +6496,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,12 +6506,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6518,7 +6520,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6537,10 +6538,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652223</v>
+        <v>123652180</v>
       </c>
       <c r="B50" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6581,10 +6582,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513611</v>
+        <v>513623</v>
       </c>
       <c r="R50" t="n">
-        <v>6733249</v>
+        <v>6733239</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6616,7 +6617,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6626,12 +6627,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6659,10 +6660,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652203</v>
+        <v>123652204</v>
       </c>
       <c r="B51" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6703,10 +6704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513639</v>
+        <v>513632</v>
       </c>
       <c r="R51" t="n">
-        <v>6733252</v>
+        <v>6733247</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6738,7 +6739,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6748,12 +6749,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6781,10 +6782,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652168</v>
+        <v>123652171</v>
       </c>
       <c r="B52" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6825,10 +6826,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513593</v>
+        <v>513608</v>
       </c>
       <c r="R52" t="n">
-        <v>6733228</v>
+        <v>6733238</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6860,7 +6861,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6870,7 +6871,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6903,10 +6904,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123656502</v>
+        <v>123652190</v>
       </c>
       <c r="B53" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6915,35 +6916,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6951,10 +6948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R53" t="n">
-        <v>6733240</v>
+        <v>6733227</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6986,7 +6983,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6996,12 +6993,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7010,6 +7007,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7028,10 +7026,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123656503</v>
+        <v>123656499</v>
       </c>
       <c r="B54" t="n">
-        <v>57503</v>
+        <v>97367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7040,35 +7038,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7076,13 +7070,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513619</v>
+        <v>513625</v>
       </c>
       <c r="R54" t="n">
-        <v>6733230</v>
+        <v>6733311</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7111,7 +7105,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7121,12 +7115,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7135,6 +7124,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7153,10 +7143,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123650524</v>
+        <v>123652177</v>
       </c>
       <c r="B55" t="n">
-        <v>56689</v>
+        <v>98502</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7165,39 +7155,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7205,10 +7187,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513595</v>
+        <v>513615</v>
       </c>
       <c r="R55" t="n">
-        <v>6733257</v>
+        <v>6733245</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7240,7 +7222,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7250,7 +7232,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7259,6 +7246,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7277,10 +7265,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652202</v>
+        <v>123652179</v>
       </c>
       <c r="B56" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7321,10 +7309,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513640</v>
+        <v>513611</v>
       </c>
       <c r="R56" t="n">
-        <v>6733250</v>
+        <v>6733236</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7356,7 +7344,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7366,12 +7354,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7399,10 +7387,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652179</v>
+        <v>123652211</v>
       </c>
       <c r="B57" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7443,10 +7431,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513611</v>
+        <v>513625</v>
       </c>
       <c r="R57" t="n">
-        <v>6733236</v>
+        <v>6733258</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7478,7 +7466,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7488,12 +7476,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7521,10 +7509,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652208</v>
+        <v>123652161</v>
       </c>
       <c r="B58" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7565,10 +7553,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513626</v>
+        <v>513597</v>
       </c>
       <c r="R58" t="n">
-        <v>6733254</v>
+        <v>6733265</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7600,7 +7588,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7610,12 +7598,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7636,17 +7624,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652190</v>
+        <v>123652193</v>
       </c>
       <c r="B59" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7687,10 +7675,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513627</v>
+        <v>513631</v>
       </c>
       <c r="R59" t="n">
-        <v>6733227</v>
+        <v>6733221</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7722,7 +7710,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7732,12 +7720,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7765,10 +7753,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123656499</v>
+        <v>123652169</v>
       </c>
       <c r="B60" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7777,25 +7765,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7809,13 +7797,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513625</v>
+        <v>513603</v>
       </c>
       <c r="R60" t="n">
-        <v>6733311</v>
+        <v>6733229</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7844,7 +7832,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7854,7 +7842,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7882,10 +7875,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652224</v>
+        <v>123652191</v>
       </c>
       <c r="B61" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7926,10 +7919,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513610</v>
+        <v>513628</v>
       </c>
       <c r="R61" t="n">
-        <v>6733242</v>
+        <v>6733228</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7961,7 +7954,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7971,12 +7964,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8004,10 +7997,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652225</v>
+        <v>123652168</v>
       </c>
       <c r="B62" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8048,10 +8041,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513617</v>
+        <v>513593</v>
       </c>
       <c r="R62" t="n">
-        <v>6733234</v>
+        <v>6733228</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8083,7 +8076,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8093,12 +8086,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8126,10 +8119,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652212</v>
+        <v>123652201</v>
       </c>
       <c r="B63" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8170,10 +8163,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513623</v>
+        <v>513640</v>
       </c>
       <c r="R63" t="n">
-        <v>6733260</v>
+        <v>6733246</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8205,7 +8198,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8215,12 +8208,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8248,10 +8241,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652177</v>
+        <v>123652194</v>
       </c>
       <c r="B64" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8292,10 +8285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513615</v>
+        <v>513642</v>
       </c>
       <c r="R64" t="n">
-        <v>6733245</v>
+        <v>6733220</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8327,7 +8320,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8337,7 +8330,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8370,10 +8363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652199</v>
+        <v>123652160</v>
       </c>
       <c r="B65" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8414,7 +8407,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513642</v>
+        <v>513608</v>
       </c>
       <c r="R65" t="n">
         <v>6733246</v>
@@ -8449,7 +8442,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8459,12 +8452,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8492,10 +8485,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123656500</v>
+        <v>123652173</v>
       </c>
       <c r="B66" t="n">
-        <v>5174</v>
+        <v>98502</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8504,32 +8497,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8537,13 +8529,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513668</v>
+        <v>513600</v>
       </c>
       <c r="R66" t="n">
-        <v>6733244</v>
+        <v>6733258</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8567,22 +8559,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8603,17 +8600,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652188</v>
+        <v>123652225</v>
       </c>
       <c r="B67" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8654,10 +8651,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513629</v>
+        <v>513617</v>
       </c>
       <c r="R67" t="n">
-        <v>6733239</v>
+        <v>6733234</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8689,7 +8686,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8699,12 +8696,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8732,10 +8729,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652200</v>
+        <v>123652184</v>
       </c>
       <c r="B68" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8776,10 +8773,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513638</v>
+        <v>513618</v>
       </c>
       <c r="R68" t="n">
-        <v>6733248</v>
+        <v>6733235</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8808,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,12 +8818,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8854,10 +8851,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652191</v>
+        <v>123652163</v>
       </c>
       <c r="B69" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8898,13 +8895,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513628</v>
+        <v>513621</v>
       </c>
       <c r="R69" t="n">
-        <v>6733228</v>
+        <v>6733235</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8933,7 +8930,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,7 +8940,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8976,10 +8973,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123650527</v>
+        <v>123652220</v>
       </c>
       <c r="B70" t="n">
-        <v>56689</v>
+        <v>98502</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8988,35 +8985,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9024,10 +9017,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513634</v>
+        <v>513609</v>
       </c>
       <c r="R70" t="n">
-        <v>6733215</v>
+        <v>6733266</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9057,14 +9050,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9073,6 +9076,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9091,10 +9095,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652193</v>
+        <v>123652214</v>
       </c>
       <c r="B71" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9135,10 +9139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513631</v>
+        <v>513615</v>
       </c>
       <c r="R71" t="n">
-        <v>6733221</v>
+        <v>6733271</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9170,7 +9174,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9180,12 +9184,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9213,10 +9217,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652171</v>
+        <v>123652226</v>
       </c>
       <c r="B72" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9257,10 +9261,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513608</v>
+        <v>513622</v>
       </c>
       <c r="R72" t="n">
-        <v>6733238</v>
+        <v>6733236</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9292,7 +9296,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9302,12 +9306,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9335,10 +9339,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652170</v>
+        <v>123652207</v>
       </c>
       <c r="B73" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9379,10 +9383,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513607</v>
+        <v>513629</v>
       </c>
       <c r="R73" t="n">
-        <v>6733239</v>
+        <v>6733245</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9414,7 +9418,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9424,12 +9428,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9457,10 +9461,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652216</v>
+        <v>123652218</v>
       </c>
       <c r="B74" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9501,10 +9505,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513614</v>
+        <v>513613</v>
       </c>
       <c r="R74" t="n">
-        <v>6733272</v>
+        <v>6733273</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9536,7 +9540,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9546,7 +9550,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -9579,10 +9583,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123652176</v>
+        <v>123656500</v>
       </c>
       <c r="B75" t="n">
-        <v>98396</v>
+        <v>5176</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9591,31 +9595,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9623,13 +9628,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513605</v>
+        <v>513668</v>
       </c>
       <c r="R75" t="n">
-        <v>6733249</v>
+        <v>6733244</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9653,27 +9658,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252664</v>
+        <v>123253165</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513616</v>
+        <v>513623</v>
       </c>
       <c r="R3" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123253165</v>
+        <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513623</v>
+        <v>513598</v>
       </c>
       <c r="R4" t="n">
-        <v>6733230</v>
+        <v>6733234</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252821</v>
+        <v>123252664</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513598</v>
+        <v>513616</v>
       </c>
       <c r="R5" t="n">
-        <v>6733234</v>
+        <v>6733249</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652216</v>
+        <v>123652171</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513614</v>
+        <v>513608</v>
       </c>
       <c r="R6" t="n">
-        <v>6733272</v>
+        <v>6733238</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652224</v>
+        <v>123652223</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513610</v>
+        <v>513611</v>
       </c>
       <c r="R7" t="n">
-        <v>6733242</v>
+        <v>6733249</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652175</v>
+        <v>123652204</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513606</v>
+        <v>513632</v>
       </c>
       <c r="R8" t="n">
-        <v>6733254</v>
+        <v>6733247</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652178</v>
+        <v>123652200</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513605</v>
+        <v>513638</v>
       </c>
       <c r="R9" t="n">
-        <v>6733242</v>
+        <v>6733248</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652188</v>
+        <v>123652206</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513629</v>
+        <v>513623</v>
       </c>
       <c r="R10" t="n">
-        <v>6733239</v>
+        <v>6733237</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652205</v>
+        <v>123652163</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513635</v>
+        <v>513621</v>
       </c>
       <c r="R11" t="n">
-        <v>6733245</v>
+        <v>6733235</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652212</v>
+        <v>123652195</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513623</v>
+        <v>513645</v>
       </c>
       <c r="R12" t="n">
-        <v>6733260</v>
+        <v>6733241</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2009,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652197</v>
+        <v>123656503</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2021,31 +2021,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513644</v>
+        <v>513619</v>
       </c>
       <c r="R13" t="n">
-        <v>6733242</v>
+        <v>6733230</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,7 +2116,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652192</v>
+        <v>123652164</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2175,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513630</v>
+        <v>513617</v>
       </c>
       <c r="R14" t="n">
-        <v>6733221</v>
+        <v>6733240</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2210,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2220,7 +2223,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2253,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652176</v>
+        <v>123652207</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513605</v>
+        <v>513629</v>
       </c>
       <c r="R15" t="n">
-        <v>6733249</v>
+        <v>6733245</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2332,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652203</v>
+        <v>123652184</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2419,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513639</v>
+        <v>513618</v>
       </c>
       <c r="R16" t="n">
-        <v>6733252</v>
+        <v>6733235</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2454,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2464,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,7 +2503,7 @@
         <v>123652185</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2619,10 +2622,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652162</v>
+        <v>123652220</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2663,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513604</v>
+        <v>513609</v>
       </c>
       <c r="R18" t="n">
-        <v>6733250</v>
+        <v>6733266</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2698,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2708,12 +2711,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2741,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123656504</v>
+        <v>123652189</v>
       </c>
       <c r="B19" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2753,35 +2756,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2789,10 +2788,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513643</v>
+        <v>513629</v>
       </c>
       <c r="R19" t="n">
-        <v>6733240</v>
+        <v>6733228</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2824,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2834,12 +2833,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,6 +2847,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2866,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652208</v>
+        <v>123652176</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513626</v>
+        <v>513605</v>
       </c>
       <c r="R20" t="n">
-        <v>6733254</v>
+        <v>6733249</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,10 +2988,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652213</v>
+        <v>123652212</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513617</v>
+        <v>513623</v>
       </c>
       <c r="R21" t="n">
-        <v>6733269</v>
+        <v>6733260</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652200</v>
+        <v>123652225</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513638</v>
+        <v>513617</v>
       </c>
       <c r="R22" t="n">
-        <v>6733248</v>
+        <v>6733234</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3232,10 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652174</v>
+        <v>123652173</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3276,10 +3276,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513606</v>
+        <v>513600</v>
       </c>
       <c r="R23" t="n">
-        <v>6733257</v>
+        <v>6733258</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3357,7 +3357,7 @@
         <v>123652219</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652223</v>
+        <v>123652182</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513611</v>
+        <v>513620</v>
       </c>
       <c r="R25" t="n">
-        <v>6733249</v>
+        <v>6733241</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652221</v>
+        <v>123656502</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3610,31 +3610,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3642,10 +3646,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513613</v>
+        <v>513623</v>
       </c>
       <c r="R26" t="n">
-        <v>6733269</v>
+        <v>6733240</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3677,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3687,12 +3691,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3701,7 +3705,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3720,10 +3723,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123656502</v>
+        <v>123652221</v>
       </c>
       <c r="B27" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3732,35 +3735,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3768,10 +3767,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513623</v>
+        <v>513613</v>
       </c>
       <c r="R27" t="n">
-        <v>6733240</v>
+        <v>6733269</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3803,7 +3802,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3813,12 +3812,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,6 +3826,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3845,10 +3845,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123656505</v>
+        <v>123652209</v>
       </c>
       <c r="B28" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3857,35 +3857,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3893,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513624</v>
+        <v>513620</v>
       </c>
       <c r="R28" t="n">
-        <v>6733235</v>
+        <v>6733253</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3928,7 +3924,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3938,12 +3934,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3952,6 +3948,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3970,10 +3967,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652170</v>
+        <v>123656504</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3982,31 +3979,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4014,10 +4015,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513607</v>
+        <v>513643</v>
       </c>
       <c r="R29" t="n">
-        <v>6733239</v>
+        <v>6733240</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4049,7 +4050,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4059,12 +4060,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4073,7 +4074,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652209</v>
+        <v>123652213</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513620</v>
+        <v>513617</v>
       </c>
       <c r="R30" t="n">
-        <v>6733253</v>
+        <v>6733269</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4214,10 +4214,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652202</v>
+        <v>123652191</v>
       </c>
       <c r="B31" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513640</v>
+        <v>513628</v>
       </c>
       <c r="R31" t="n">
-        <v>6733250</v>
+        <v>6733228</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4336,10 +4336,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652189</v>
+        <v>123652177</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513629</v>
+        <v>513615</v>
       </c>
       <c r="R32" t="n">
-        <v>6733228</v>
+        <v>6733245</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4458,10 +4458,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123650524</v>
+        <v>123652224</v>
       </c>
       <c r="B33" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4470,39 +4470,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4510,10 +4502,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513595</v>
+        <v>513610</v>
       </c>
       <c r="R33" t="n">
-        <v>6733257</v>
+        <v>6733242</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4555,7 +4547,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4564,6 +4561,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4582,10 +4580,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652186</v>
+        <v>123652201</v>
       </c>
       <c r="B34" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4626,10 +4624,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513623</v>
+        <v>513640</v>
       </c>
       <c r="R34" t="n">
-        <v>6733238</v>
+        <v>6733246</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4661,7 +4659,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4671,12 +4669,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4704,10 +4702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652195</v>
+        <v>123650528</v>
       </c>
       <c r="B35" t="n">
-        <v>98502</v>
+        <v>56692</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4716,31 +4714,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4748,10 +4750,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513645</v>
+        <v>513632</v>
       </c>
       <c r="R35" t="n">
-        <v>6733241</v>
+        <v>6733214</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4783,7 +4785,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,12 +4795,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4807,7 +4804,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4819,17 +4815,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123650527</v>
+        <v>123656505</v>
       </c>
       <c r="B36" t="n">
-        <v>56692</v>
+        <v>57507</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4842,16 +4838,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4864,7 +4860,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4874,10 +4870,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513634</v>
+        <v>513624</v>
       </c>
       <c r="R36" t="n">
-        <v>6733215</v>
+        <v>6733235</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4907,14 +4903,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4941,7 +4947,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123650528</v>
+        <v>123650524</v>
       </c>
       <c r="B37" t="n">
         <v>56692</v>
@@ -4976,10 +4982,14 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4989,10 +4999,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513632</v>
+        <v>513595</v>
       </c>
       <c r="R37" t="n">
-        <v>6733214</v>
+        <v>6733257</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5024,7 +5034,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5034,7 +5044,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5054,17 +5064,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652187</v>
+        <v>123652170</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513627</v>
+        <v>513607</v>
       </c>
       <c r="R38" t="n">
-        <v>6733241</v>
+        <v>6733239</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5140,7 +5150,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5150,7 +5160,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5183,10 +5193,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652182</v>
+        <v>123652174</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5227,10 +5237,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513620</v>
+        <v>513606</v>
       </c>
       <c r="R39" t="n">
-        <v>6733241</v>
+        <v>6733257</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5262,7 +5272,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5272,7 +5282,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5305,10 +5315,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652181</v>
+        <v>123652169</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5349,10 +5359,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513619</v>
+        <v>513603</v>
       </c>
       <c r="R40" t="n">
-        <v>6733234</v>
+        <v>6733229</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5384,7 +5394,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5394,7 +5404,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5427,10 +5437,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652210</v>
+        <v>123652187</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5471,10 +5481,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513625</v>
+        <v>513627</v>
       </c>
       <c r="R41" t="n">
-        <v>6733251</v>
+        <v>6733241</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5506,7 +5516,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5516,12 +5526,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5549,10 +5559,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652199</v>
+        <v>123652211</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5593,10 +5603,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513642</v>
+        <v>513625</v>
       </c>
       <c r="R42" t="n">
-        <v>6733246</v>
+        <v>6733258</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5628,7 +5638,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5638,12 +5648,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5671,10 +5681,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652164</v>
+        <v>123652178</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5715,10 +5725,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513617</v>
+        <v>513605</v>
       </c>
       <c r="R43" t="n">
-        <v>6733240</v>
+        <v>6733242</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5750,7 +5760,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5760,7 +5770,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5793,10 +5803,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123650526</v>
+        <v>123652216</v>
       </c>
       <c r="B44" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5805,35 +5815,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5841,10 +5847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513627</v>
+        <v>513614</v>
       </c>
       <c r="R44" t="n">
-        <v>6733250</v>
+        <v>6733272</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5876,7 +5882,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5886,12 +5892,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5900,6 +5906,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5918,10 +5925,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123656503</v>
+        <v>123656499</v>
       </c>
       <c r="B45" t="n">
-        <v>57506</v>
+        <v>97369</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5930,35 +5937,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5966,13 +5969,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513619</v>
+        <v>513625</v>
       </c>
       <c r="R45" t="n">
-        <v>6733230</v>
+        <v>6733311</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6001,7 +6004,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6011,12 +6014,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6025,6 +6023,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6043,10 +6042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652206</v>
+        <v>123656500</v>
       </c>
       <c r="B46" t="n">
-        <v>98502</v>
+        <v>5176</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6055,31 +6054,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513623</v>
+        <v>513668</v>
       </c>
       <c r="R46" t="n">
-        <v>6733237</v>
+        <v>6733244</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6117,27 +6117,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6158,17 +6153,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652222</v>
+        <v>123652214</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6209,10 +6204,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513612</v>
+        <v>513615</v>
       </c>
       <c r="R47" t="n">
-        <v>6733260</v>
+        <v>6733271</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6244,7 +6239,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6254,12 +6249,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6287,10 +6282,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652217</v>
+        <v>123652175</v>
       </c>
       <c r="B48" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513612</v>
+        <v>513606</v>
       </c>
       <c r="R48" t="n">
-        <v>6733277</v>
+        <v>6733254</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6366,7 +6361,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6376,12 +6371,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6409,10 +6404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123650523</v>
+        <v>123652186</v>
       </c>
       <c r="B49" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6421,39 +6416,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6461,10 +6448,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513585</v>
+        <v>513623</v>
       </c>
       <c r="R49" t="n">
-        <v>6733249</v>
+        <v>6733238</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6496,7 +6483,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6506,12 +6493,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6520,6 +6507,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6538,10 +6526,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652180</v>
+        <v>123650527</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>56692</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6550,31 +6538,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6582,10 +6574,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513623</v>
+        <v>513634</v>
       </c>
       <c r="R50" t="n">
-        <v>6733239</v>
+        <v>6733215</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6615,24 +6607,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6641,7 +6623,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6660,10 +6641,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652204</v>
+        <v>123650526</v>
       </c>
       <c r="B51" t="n">
-        <v>98502</v>
+        <v>56692</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6672,31 +6653,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6704,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513632</v>
+        <v>513627</v>
       </c>
       <c r="R51" t="n">
-        <v>6733247</v>
+        <v>6733250</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6739,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6749,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6763,7 +6748,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6782,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652171</v>
+        <v>123652226</v>
       </c>
       <c r="B52" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6826,10 +6810,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513608</v>
+        <v>513622</v>
       </c>
       <c r="R52" t="n">
-        <v>6733238</v>
+        <v>6733236</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6861,7 +6845,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6871,12 +6855,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6904,10 +6888,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652190</v>
+        <v>123652202</v>
       </c>
       <c r="B53" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6948,10 +6932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513627</v>
+        <v>513640</v>
       </c>
       <c r="R53" t="n">
-        <v>6733227</v>
+        <v>6733250</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6983,7 +6967,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6993,12 +6977,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7026,10 +7010,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123656499</v>
+        <v>123652199</v>
       </c>
       <c r="B54" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7038,25 +7022,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7070,13 +7054,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513625</v>
+        <v>513642</v>
       </c>
       <c r="R54" t="n">
-        <v>6733311</v>
+        <v>6733246</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7105,7 +7089,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7115,7 +7099,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7143,10 +7132,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652177</v>
+        <v>123652179</v>
       </c>
       <c r="B55" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7187,10 +7176,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513615</v>
+        <v>513611</v>
       </c>
       <c r="R55" t="n">
-        <v>6733245</v>
+        <v>6733236</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7222,7 +7211,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7232,12 +7221,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7265,10 +7254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652179</v>
+        <v>123652168</v>
       </c>
       <c r="B56" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7309,10 +7298,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513611</v>
+        <v>513593</v>
       </c>
       <c r="R56" t="n">
-        <v>6733236</v>
+        <v>6733228</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7344,7 +7333,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7354,12 +7343,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7387,10 +7376,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652211</v>
+        <v>123652161</v>
       </c>
       <c r="B57" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7431,10 +7420,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513625</v>
+        <v>513597</v>
       </c>
       <c r="R57" t="n">
-        <v>6733258</v>
+        <v>6733265</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7466,7 +7455,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7476,12 +7465,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7502,17 +7491,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652161</v>
+        <v>123652162</v>
       </c>
       <c r="B58" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7553,10 +7542,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513597</v>
+        <v>513604</v>
       </c>
       <c r="R58" t="n">
-        <v>6733265</v>
+        <v>6733250</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7588,7 +7577,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7598,12 +7587,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7624,17 +7613,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652193</v>
+        <v>123652192</v>
       </c>
       <c r="B59" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7675,7 +7664,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513631</v>
+        <v>513630</v>
       </c>
       <c r="R59" t="n">
         <v>6733221</v>
@@ -7710,7 +7699,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7720,12 +7709,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7753,10 +7742,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652169</v>
+        <v>123652181</v>
       </c>
       <c r="B60" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7797,10 +7786,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513603</v>
+        <v>513619</v>
       </c>
       <c r="R60" t="n">
-        <v>6733229</v>
+        <v>6733234</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7832,7 +7821,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7842,7 +7831,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7875,10 +7864,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652191</v>
+        <v>123652197</v>
       </c>
       <c r="B61" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7919,10 +7908,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513628</v>
+        <v>513644</v>
       </c>
       <c r="R61" t="n">
-        <v>6733228</v>
+        <v>6733242</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7954,7 +7943,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7964,12 +7953,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7997,10 +7986,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652168</v>
+        <v>123652203</v>
       </c>
       <c r="B62" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8041,10 +8030,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513593</v>
+        <v>513639</v>
       </c>
       <c r="R62" t="n">
-        <v>6733228</v>
+        <v>6733252</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8076,7 +8065,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8086,12 +8075,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8119,10 +8108,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652201</v>
+        <v>123652190</v>
       </c>
       <c r="B63" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8163,10 +8152,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513640</v>
+        <v>513627</v>
       </c>
       <c r="R63" t="n">
-        <v>6733246</v>
+        <v>6733227</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8198,7 +8187,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8208,12 +8197,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8241,10 +8230,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652194</v>
+        <v>123652188</v>
       </c>
       <c r="B64" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8285,10 +8274,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513642</v>
+        <v>513629</v>
       </c>
       <c r="R64" t="n">
-        <v>6733220</v>
+        <v>6733239</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8320,7 +8309,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8330,7 +8319,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -8363,10 +8352,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652160</v>
+        <v>123650523</v>
       </c>
       <c r="B65" t="n">
-        <v>98502</v>
+        <v>56692</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8375,31 +8364,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8407,10 +8404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513608</v>
+        <v>513585</v>
       </c>
       <c r="R65" t="n">
-        <v>6733246</v>
+        <v>6733249</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8442,7 +8439,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8452,12 +8449,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8466,7 +8463,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8485,10 +8481,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652173</v>
+        <v>123652210</v>
       </c>
       <c r="B66" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8529,10 +8525,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513600</v>
+        <v>513625</v>
       </c>
       <c r="R66" t="n">
-        <v>6733258</v>
+        <v>6733251</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8564,7 +8560,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8574,12 +8570,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8607,10 +8603,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652225</v>
+        <v>123652222</v>
       </c>
       <c r="B67" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8651,10 +8647,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513617</v>
+        <v>513612</v>
       </c>
       <c r="R67" t="n">
-        <v>6733234</v>
+        <v>6733260</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8686,7 +8682,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8696,7 +8692,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8729,10 +8725,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652184</v>
+        <v>123652180</v>
       </c>
       <c r="B68" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8773,10 +8769,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513618</v>
+        <v>513623</v>
       </c>
       <c r="R68" t="n">
-        <v>6733235</v>
+        <v>6733239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8808,7 +8804,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8818,7 +8814,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8851,10 +8847,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652163</v>
+        <v>123652218</v>
       </c>
       <c r="B69" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8895,13 +8891,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513621</v>
+        <v>513613</v>
       </c>
       <c r="R69" t="n">
-        <v>6733235</v>
+        <v>6733273</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8930,7 +8926,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8940,12 +8936,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8973,10 +8969,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652220</v>
+        <v>123652208</v>
       </c>
       <c r="B70" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9017,10 +9013,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513609</v>
+        <v>513626</v>
       </c>
       <c r="R70" t="n">
-        <v>6733266</v>
+        <v>6733254</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9052,7 +9048,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9062,7 +9058,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -9095,10 +9091,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652214</v>
+        <v>123652205</v>
       </c>
       <c r="B71" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9139,10 +9135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513615</v>
+        <v>513635</v>
       </c>
       <c r="R71" t="n">
-        <v>6733271</v>
+        <v>6733245</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9174,7 +9170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9184,12 +9180,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9217,10 +9213,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652226</v>
+        <v>123652193</v>
       </c>
       <c r="B72" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9261,10 +9257,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513622</v>
+        <v>513631</v>
       </c>
       <c r="R72" t="n">
-        <v>6733236</v>
+        <v>6733221</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9296,7 +9292,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9306,12 +9302,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9339,10 +9335,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652207</v>
+        <v>123652160</v>
       </c>
       <c r="B73" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9383,10 +9379,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513629</v>
+        <v>513608</v>
       </c>
       <c r="R73" t="n">
-        <v>6733245</v>
+        <v>6733246</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9418,7 +9414,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9428,12 +9424,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9461,10 +9457,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652218</v>
+        <v>123652217</v>
       </c>
       <c r="B74" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9505,10 +9501,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513613</v>
+        <v>513612</v>
       </c>
       <c r="R74" t="n">
-        <v>6733273</v>
+        <v>6733277</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9540,7 +9536,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9550,7 +9546,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -9583,10 +9579,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123656500</v>
+        <v>123652194</v>
       </c>
       <c r="B75" t="n">
-        <v>5176</v>
+        <v>98504</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9595,32 +9591,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9628,13 +9623,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513668</v>
+        <v>513642</v>
       </c>
       <c r="R75" t="n">
-        <v>6733244</v>
+        <v>6733220</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9658,22 +9653,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -2009,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123656503</v>
+        <v>123652184</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2021,35 +2021,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2057,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513619</v>
+        <v>513618</v>
       </c>
       <c r="R13" t="n">
-        <v>6733230</v>
+        <v>6733235</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2092,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2112,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2134,7 +2131,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652164</v>
+        <v>123652185</v>
       </c>
       <c r="B14" t="n">
         <v>98504</v>
@@ -2178,7 +2175,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513617</v>
+        <v>513619</v>
       </c>
       <c r="R14" t="n">
         <v>6733240</v>
@@ -2213,7 +2210,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,7 +2220,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2256,7 +2253,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652207</v>
+        <v>123652164</v>
       </c>
       <c r="B15" t="n">
         <v>98504</v>
@@ -2300,10 +2297,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513629</v>
+        <v>513617</v>
       </c>
       <c r="R15" t="n">
-        <v>6733245</v>
+        <v>6733240</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2335,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,12 +2342,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,7 +2375,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652184</v>
+        <v>123652207</v>
       </c>
       <c r="B16" t="n">
         <v>98504</v>
@@ -2422,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513618</v>
+        <v>513629</v>
       </c>
       <c r="R16" t="n">
-        <v>6733235</v>
+        <v>6733245</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2454,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2464,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652185</v>
+        <v>123656503</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,31 +2509,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2547,7 +2548,7 @@
         <v>513619</v>
       </c>
       <c r="R17" t="n">
-        <v>6733240</v>
+        <v>6733230</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,12 +2590,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,7 +2604,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652177</v>
+        <v>123650528</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4348,31 +4348,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4380,10 +4384,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513615</v>
+        <v>513632</v>
       </c>
       <c r="R32" t="n">
-        <v>6733245</v>
+        <v>6733214</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4425,12 +4429,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4439,7 +4438,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4451,14 +4449,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652224</v>
+        <v>123652177</v>
       </c>
       <c r="B33" t="n">
         <v>98504</v>
@@ -4502,10 +4500,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513610</v>
+        <v>513615</v>
       </c>
       <c r="R33" t="n">
-        <v>6733242</v>
+        <v>6733245</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4537,7 +4535,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4547,12 +4545,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4580,7 +4578,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652201</v>
+        <v>123652224</v>
       </c>
       <c r="B34" t="n">
         <v>98504</v>
@@ -4624,10 +4622,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513640</v>
+        <v>513610</v>
       </c>
       <c r="R34" t="n">
-        <v>6733246</v>
+        <v>6733242</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4659,7 +4657,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4669,12 +4667,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4702,10 +4700,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123650528</v>
+        <v>123652201</v>
       </c>
       <c r="B35" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4714,35 +4712,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4750,10 +4744,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513632</v>
+        <v>513640</v>
       </c>
       <c r="R35" t="n">
-        <v>6733214</v>
+        <v>6733246</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4785,7 +4779,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4795,7 +4789,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4804,6 +4803,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4815,17 +4815,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123656505</v>
+        <v>123652170</v>
       </c>
       <c r="B36" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4834,35 +4834,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4870,10 +4866,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513624</v>
+        <v>513607</v>
       </c>
       <c r="R36" t="n">
-        <v>6733235</v>
+        <v>6733239</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4905,7 +4901,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4915,12 +4911,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4929,6 +4925,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123650524</v>
+        <v>123652174</v>
       </c>
       <c r="B37" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4959,39 +4956,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4999,7 +4988,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513595</v>
+        <v>513606</v>
       </c>
       <c r="R37" t="n">
         <v>6733257</v>
@@ -5034,7 +5023,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5044,7 +5033,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5053,6 +5047,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5071,7 +5066,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652170</v>
+        <v>123652169</v>
       </c>
       <c r="B38" t="n">
         <v>98504</v>
@@ -5115,10 +5110,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513607</v>
+        <v>513603</v>
       </c>
       <c r="R38" t="n">
-        <v>6733239</v>
+        <v>6733229</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5150,7 +5145,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5160,7 +5155,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5193,7 +5188,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652174</v>
+        <v>123652187</v>
       </c>
       <c r="B39" t="n">
         <v>98504</v>
@@ -5237,10 +5232,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513606</v>
+        <v>513627</v>
       </c>
       <c r="R39" t="n">
-        <v>6733257</v>
+        <v>6733241</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5272,7 +5267,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5282,7 +5277,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5315,7 +5310,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652169</v>
+        <v>123652211</v>
       </c>
       <c r="B40" t="n">
         <v>98504</v>
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513603</v>
+        <v>513625</v>
       </c>
       <c r="R40" t="n">
-        <v>6733229</v>
+        <v>6733258</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5394,7 +5389,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5404,12 +5399,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5437,10 +5432,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652187</v>
+        <v>123656505</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5449,31 +5444,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5481,10 +5480,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513627</v>
+        <v>513624</v>
       </c>
       <c r="R41" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5516,7 +5515,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5526,12 +5525,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5540,7 +5539,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5559,10 +5557,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652211</v>
+        <v>123650524</v>
       </c>
       <c r="B42" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5571,31 +5569,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5603,10 +5609,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513625</v>
+        <v>513595</v>
       </c>
       <c r="R42" t="n">
-        <v>6733258</v>
+        <v>6733257</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5638,7 +5644,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5648,12 +5654,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5662,7 +5663,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652186</v>
+        <v>123650526</v>
       </c>
       <c r="B49" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6416,31 +6416,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6448,10 +6452,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R49" t="n">
-        <v>6733238</v>
+        <v>6733250</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6483,7 +6487,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6493,12 +6497,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6507,7 +6511,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6526,10 +6529,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123650527</v>
+        <v>123652186</v>
       </c>
       <c r="B50" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6538,35 +6541,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6574,10 +6573,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513634</v>
+        <v>513623</v>
       </c>
       <c r="R50" t="n">
-        <v>6733215</v>
+        <v>6733238</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6607,14 +6606,24 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6623,6 +6632,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6641,10 +6651,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123650526</v>
+        <v>123652226</v>
       </c>
       <c r="B51" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6653,35 +6663,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6689,10 +6695,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513627</v>
+        <v>513622</v>
       </c>
       <c r="R51" t="n">
-        <v>6733250</v>
+        <v>6733236</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6724,7 +6730,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6740,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6748,6 +6754,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6766,7 +6773,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652226</v>
+        <v>123652202</v>
       </c>
       <c r="B52" t="n">
         <v>98504</v>
@@ -6810,10 +6817,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513622</v>
+        <v>513640</v>
       </c>
       <c r="R52" t="n">
-        <v>6733236</v>
+        <v>6733250</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6845,7 +6852,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6855,12 +6862,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6888,7 +6895,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652202</v>
+        <v>123652199</v>
       </c>
       <c r="B53" t="n">
         <v>98504</v>
@@ -6932,10 +6939,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513640</v>
+        <v>513642</v>
       </c>
       <c r="R53" t="n">
-        <v>6733250</v>
+        <v>6733246</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6967,7 +6974,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6977,7 +6984,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7010,7 +7017,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652199</v>
+        <v>123652179</v>
       </c>
       <c r="B54" t="n">
         <v>98504</v>
@@ -7054,10 +7061,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513642</v>
+        <v>513611</v>
       </c>
       <c r="R54" t="n">
-        <v>6733246</v>
+        <v>6733236</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7089,7 +7096,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7099,12 +7106,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7132,7 +7139,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652179</v>
+        <v>123652168</v>
       </c>
       <c r="B55" t="n">
         <v>98504</v>
@@ -7176,10 +7183,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513611</v>
+        <v>513593</v>
       </c>
       <c r="R55" t="n">
-        <v>6733236</v>
+        <v>6733228</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7211,7 +7218,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7221,12 +7228,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7254,7 +7261,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652168</v>
+        <v>123652161</v>
       </c>
       <c r="B56" t="n">
         <v>98504</v>
@@ -7298,10 +7305,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513593</v>
+        <v>513597</v>
       </c>
       <c r="R56" t="n">
-        <v>6733228</v>
+        <v>6733265</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7333,7 +7340,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7343,12 +7350,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7369,14 +7376,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652161</v>
+        <v>123652162</v>
       </c>
       <c r="B57" t="n">
         <v>98504</v>
@@ -7420,10 +7427,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513597</v>
+        <v>513604</v>
       </c>
       <c r="R57" t="n">
-        <v>6733265</v>
+        <v>6733250</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7455,7 +7462,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7465,12 +7472,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,14 +7498,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652162</v>
+        <v>123652192</v>
       </c>
       <c r="B58" t="n">
         <v>98504</v>
@@ -7542,10 +7549,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513604</v>
+        <v>513630</v>
       </c>
       <c r="R58" t="n">
-        <v>6733250</v>
+        <v>6733221</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7577,7 +7584,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7587,7 +7594,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7620,7 +7627,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652192</v>
+        <v>123652181</v>
       </c>
       <c r="B59" t="n">
         <v>98504</v>
@@ -7664,10 +7671,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513630</v>
+        <v>513619</v>
       </c>
       <c r="R59" t="n">
-        <v>6733221</v>
+        <v>6733234</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7699,7 +7706,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7709,7 +7716,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7742,7 +7749,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652181</v>
+        <v>123652197</v>
       </c>
       <c r="B60" t="n">
         <v>98504</v>
@@ -7786,10 +7793,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513619</v>
+        <v>513644</v>
       </c>
       <c r="R60" t="n">
-        <v>6733234</v>
+        <v>6733242</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7821,7 +7828,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7831,12 +7838,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7864,7 +7871,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652197</v>
+        <v>123652203</v>
       </c>
       <c r="B61" t="n">
         <v>98504</v>
@@ -7908,10 +7915,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513644</v>
+        <v>513639</v>
       </c>
       <c r="R61" t="n">
-        <v>6733242</v>
+        <v>6733252</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7943,7 +7950,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7953,12 +7960,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7986,7 +7993,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652203</v>
+        <v>123652190</v>
       </c>
       <c r="B62" t="n">
         <v>98504</v>
@@ -8030,10 +8037,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513639</v>
+        <v>513627</v>
       </c>
       <c r="R62" t="n">
-        <v>6733252</v>
+        <v>6733227</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8065,7 +8072,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8075,12 +8082,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8108,7 +8115,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652190</v>
+        <v>123652188</v>
       </c>
       <c r="B63" t="n">
         <v>98504</v>
@@ -8152,10 +8159,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513627</v>
+        <v>513629</v>
       </c>
       <c r="R63" t="n">
-        <v>6733227</v>
+        <v>6733239</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8187,7 +8194,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8197,7 +8204,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8230,10 +8237,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652188</v>
+        <v>123650523</v>
       </c>
       <c r="B64" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8242,31 +8249,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8274,10 +8289,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513629</v>
+        <v>513585</v>
       </c>
       <c r="R64" t="n">
-        <v>6733239</v>
+        <v>6733249</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8309,7 +8324,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8319,12 +8334,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8333,7 +8348,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8352,10 +8366,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123650523</v>
+        <v>123652210</v>
       </c>
       <c r="B65" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8364,39 +8378,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8404,10 +8410,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513585</v>
+        <v>513625</v>
       </c>
       <c r="R65" t="n">
-        <v>6733249</v>
+        <v>6733251</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8439,7 +8445,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8449,12 +8455,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8463,6 +8469,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8481,7 +8488,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652210</v>
+        <v>123652222</v>
       </c>
       <c r="B66" t="n">
         <v>98504</v>
@@ -8525,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513625</v>
+        <v>513612</v>
       </c>
       <c r="R66" t="n">
-        <v>6733251</v>
+        <v>6733260</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8560,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8570,12 +8577,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8603,7 +8610,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652222</v>
+        <v>123652180</v>
       </c>
       <c r="B67" t="n">
         <v>98504</v>
@@ -8647,10 +8654,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513612</v>
+        <v>513623</v>
       </c>
       <c r="R67" t="n">
-        <v>6733260</v>
+        <v>6733239</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8682,7 +8689,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8692,12 +8699,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8725,7 +8732,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652180</v>
+        <v>123652193</v>
       </c>
       <c r="B68" t="n">
         <v>98504</v>
@@ -8769,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513623</v>
+        <v>513631</v>
       </c>
       <c r="R68" t="n">
-        <v>6733239</v>
+        <v>6733221</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8804,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8814,12 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9213,7 +9220,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652193</v>
+        <v>123652160</v>
       </c>
       <c r="B72" t="n">
         <v>98504</v>
@@ -9257,10 +9264,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513631</v>
+        <v>513608</v>
       </c>
       <c r="R72" t="n">
-        <v>6733221</v>
+        <v>6733246</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9292,7 +9299,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9302,12 +9309,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9335,7 +9342,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652160</v>
+        <v>123652217</v>
       </c>
       <c r="B73" t="n">
         <v>98504</v>
@@ -9379,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513608</v>
+        <v>513612</v>
       </c>
       <c r="R73" t="n">
-        <v>6733246</v>
+        <v>6733277</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9414,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9424,12 +9431,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9457,7 +9464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652217</v>
+        <v>123652194</v>
       </c>
       <c r="B74" t="n">
         <v>98504</v>
@@ -9501,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513612</v>
+        <v>513642</v>
       </c>
       <c r="R74" t="n">
-        <v>6733277</v>
+        <v>6733220</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9536,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9546,12 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9579,10 +9586,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123652194</v>
+        <v>123650527</v>
       </c>
       <c r="B75" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9591,31 +9598,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9623,10 +9634,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513642</v>
+        <v>513634</v>
       </c>
       <c r="R75" t="n">
-        <v>6733220</v>
+        <v>6733215</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -9656,24 +9667,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9682,7 +9683,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -2009,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652184</v>
+        <v>123656503</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2021,31 +2021,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513618</v>
+        <v>513619</v>
       </c>
       <c r="R13" t="n">
-        <v>6733235</v>
+        <v>6733230</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,7 +2116,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2131,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652185</v>
+        <v>123652164</v>
       </c>
       <c r="B14" t="n">
         <v>98504</v>
@@ -2175,7 +2178,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513619</v>
+        <v>513617</v>
       </c>
       <c r="R14" t="n">
         <v>6733240</v>
@@ -2210,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2220,7 +2223,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2253,7 +2256,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652164</v>
+        <v>123652207</v>
       </c>
       <c r="B15" t="n">
         <v>98504</v>
@@ -2297,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513617</v>
+        <v>513629</v>
       </c>
       <c r="R15" t="n">
-        <v>6733240</v>
+        <v>6733245</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2332,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,7 +2378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652207</v>
+        <v>123652184</v>
       </c>
       <c r="B16" t="n">
         <v>98504</v>
@@ -2419,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513629</v>
+        <v>513618</v>
       </c>
       <c r="R16" t="n">
-        <v>6733245</v>
+        <v>6733235</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2454,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2464,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123656503</v>
+        <v>123652185</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,35 +2512,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2548,7 +2547,7 @@
         <v>513619</v>
       </c>
       <c r="R17" t="n">
-        <v>6733230</v>
+        <v>6733240</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2580,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2590,12 +2589,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,6 +2603,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652182</v>
+        <v>123652221</v>
       </c>
       <c r="B25" t="n">
         <v>98504</v>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513620</v>
+        <v>513613</v>
       </c>
       <c r="R25" t="n">
-        <v>6733241</v>
+        <v>6733269</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3598,10 +3598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123656502</v>
+        <v>123652209</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3610,35 +3610,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3646,10 +3642,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513623</v>
+        <v>513620</v>
       </c>
       <c r="R26" t="n">
-        <v>6733240</v>
+        <v>6733253</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3681,7 +3677,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3691,12 +3687,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3705,6 +3701,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3723,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652221</v>
+        <v>123656502</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3735,31 +3732,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3767,10 +3768,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513613</v>
+        <v>513623</v>
       </c>
       <c r="R27" t="n">
-        <v>6733269</v>
+        <v>6733240</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3802,7 +3803,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3812,12 +3813,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3826,7 +3827,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3845,7 +3845,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652209</v>
+        <v>123652182</v>
       </c>
       <c r="B28" t="n">
         <v>98504</v>
@@ -3892,7 +3892,7 @@
         <v>513620</v>
       </c>
       <c r="R28" t="n">
-        <v>6733253</v>
+        <v>6733241</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -7871,10 +7871,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652203</v>
+        <v>123650523</v>
       </c>
       <c r="B61" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7883,31 +7883,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7915,10 +7923,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513639</v>
+        <v>513585</v>
       </c>
       <c r="R61" t="n">
-        <v>6733252</v>
+        <v>6733249</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7950,7 +7958,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7960,12 +7968,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7974,7 +7982,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7993,7 +8000,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652190</v>
+        <v>123652203</v>
       </c>
       <c r="B62" t="n">
         <v>98504</v>
@@ -8037,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513627</v>
+        <v>513639</v>
       </c>
       <c r="R62" t="n">
-        <v>6733227</v>
+        <v>6733252</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8072,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8082,12 +8089,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8115,7 +8122,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652188</v>
+        <v>123652190</v>
       </c>
       <c r="B63" t="n">
         <v>98504</v>
@@ -8159,10 +8166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513629</v>
+        <v>513627</v>
       </c>
       <c r="R63" t="n">
-        <v>6733239</v>
+        <v>6733227</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8194,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8204,7 +8211,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8237,10 +8244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123650523</v>
+        <v>123652188</v>
       </c>
       <c r="B64" t="n">
-        <v>56692</v>
+        <v>98504</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8249,39 +8256,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8289,10 +8288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513585</v>
+        <v>513629</v>
       </c>
       <c r="R64" t="n">
-        <v>6733249</v>
+        <v>6733239</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8324,7 +8323,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8334,12 +8333,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8348,6 +8347,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652193</v>
+        <v>123652218</v>
       </c>
       <c r="B68" t="n">
         <v>98504</v>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513631</v>
+        <v>513613</v>
       </c>
       <c r="R68" t="n">
-        <v>6733221</v>
+        <v>6733273</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8854,7 +8854,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652218</v>
+        <v>123652208</v>
       </c>
       <c r="B69" t="n">
         <v>98504</v>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513613</v>
+        <v>513626</v>
       </c>
       <c r="R69" t="n">
-        <v>6733273</v>
+        <v>6733254</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,7 +8976,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652208</v>
+        <v>123652205</v>
       </c>
       <c r="B70" t="n">
         <v>98504</v>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513626</v>
+        <v>513635</v>
       </c>
       <c r="R70" t="n">
-        <v>6733254</v>
+        <v>6733245</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -9098,7 +9098,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652205</v>
+        <v>123652193</v>
       </c>
       <c r="B71" t="n">
         <v>98504</v>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513635</v>
+        <v>513631</v>
       </c>
       <c r="R71" t="n">
-        <v>6733245</v>
+        <v>6733221</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +916,7 @@
         <v>123252821</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252664</v>
+        <v>123253165</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513616</v>
+        <v>513623</v>
       </c>
       <c r="R5" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652171</v>
+        <v>123652201</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513608</v>
+        <v>513640</v>
       </c>
       <c r="R6" t="n">
-        <v>6733238</v>
+        <v>6733246</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652223</v>
+        <v>123652214</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513611</v>
+        <v>513615</v>
       </c>
       <c r="R7" t="n">
-        <v>6733249</v>
+        <v>6733271</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652204</v>
+        <v>123652219</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513632</v>
+        <v>513609</v>
       </c>
       <c r="R8" t="n">
-        <v>6733247</v>
+        <v>6733267</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652200</v>
+        <v>123652207</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513638</v>
+        <v>513629</v>
       </c>
       <c r="R9" t="n">
-        <v>6733248</v>
+        <v>6733245</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652206</v>
+        <v>123656499</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,25 +1655,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513623</v>
+        <v>513625</v>
       </c>
       <c r="R10" t="n">
-        <v>6733237</v>
+        <v>6733311</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,12 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652163</v>
+        <v>123652199</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513621</v>
+        <v>513642</v>
       </c>
       <c r="R11" t="n">
-        <v>6733235</v>
+        <v>6733246</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,12 +1849,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652195</v>
+        <v>123652211</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,10 +1926,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513645</v>
+        <v>513625</v>
       </c>
       <c r="R12" t="n">
-        <v>6733241</v>
+        <v>6733258</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1966,7 +1961,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1971,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123656503</v>
+        <v>123652202</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2021,35 +2016,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2057,10 +2048,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513619</v>
+        <v>513640</v>
       </c>
       <c r="R13" t="n">
-        <v>6733230</v>
+        <v>6733250</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2092,7 +2083,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2093,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2116,6 +2107,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2134,10 +2126,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652164</v>
+        <v>123652206</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2178,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513617</v>
+        <v>513623</v>
       </c>
       <c r="R14" t="n">
-        <v>6733240</v>
+        <v>6733237</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2213,7 +2205,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,12 +2215,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652207</v>
+        <v>123652222</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,10 +2292,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513629</v>
+        <v>513612</v>
       </c>
       <c r="R15" t="n">
-        <v>6733245</v>
+        <v>6733260</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2335,7 +2327,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2337,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2378,10 +2370,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652184</v>
+        <v>123652226</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2422,10 +2414,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513618</v>
+        <v>513622</v>
       </c>
       <c r="R16" t="n">
-        <v>6733235</v>
+        <v>6733236</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2449,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2459,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,10 +2492,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652185</v>
+        <v>123652179</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2544,10 +2536,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513619</v>
+        <v>513611</v>
       </c>
       <c r="R17" t="n">
-        <v>6733240</v>
+        <v>6733236</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2571,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,12 +2581,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,10 +2614,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652220</v>
+        <v>123652221</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2666,10 +2658,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513609</v>
+        <v>513613</v>
       </c>
       <c r="R18" t="n">
-        <v>6733266</v>
+        <v>6733269</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2701,7 +2693,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,7 +2703,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2744,10 +2736,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652189</v>
+        <v>123656500</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,31 +2748,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2788,13 +2781,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513629</v>
+        <v>513668</v>
       </c>
       <c r="R19" t="n">
-        <v>6733228</v>
+        <v>6733244</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2818,27 +2811,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,17 +2847,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652176</v>
+        <v>123652188</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2910,10 +2898,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513605</v>
+        <v>513629</v>
       </c>
       <c r="R20" t="n">
-        <v>6733249</v>
+        <v>6733239</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2933,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,7 +2943,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2988,10 +2976,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652212</v>
+        <v>123652184</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,10 +3020,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513623</v>
+        <v>513618</v>
       </c>
       <c r="R21" t="n">
-        <v>6733260</v>
+        <v>6733235</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3067,7 +3055,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3077,12 +3065,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,10 +3098,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652225</v>
+        <v>123652213</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3157,7 +3145,7 @@
         <v>513617</v>
       </c>
       <c r="R22" t="n">
-        <v>6733234</v>
+        <v>6733269</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3189,7 +3177,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3187,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3232,10 +3220,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652173</v>
+        <v>123652186</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3276,10 +3264,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513600</v>
+        <v>513623</v>
       </c>
       <c r="R23" t="n">
-        <v>6733258</v>
+        <v>6733238</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3311,7 +3299,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3321,7 +3309,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3354,10 +3342,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652219</v>
+        <v>123652161</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3398,10 +3386,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513609</v>
+        <v>513597</v>
       </c>
       <c r="R24" t="n">
-        <v>6733267</v>
+        <v>6733265</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3433,7 +3421,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,12 +3431,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,17 +3457,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652221</v>
+        <v>123652177</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3520,10 +3508,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513613</v>
+        <v>513615</v>
       </c>
       <c r="R25" t="n">
-        <v>6733269</v>
+        <v>6733245</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3555,7 +3543,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3565,12 +3553,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3598,10 +3586,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652209</v>
+        <v>123652162</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3642,10 +3630,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513620</v>
+        <v>513604</v>
       </c>
       <c r="R26" t="n">
-        <v>6733253</v>
+        <v>6733250</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3677,7 +3665,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3687,12 +3675,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3720,10 +3708,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123656502</v>
+        <v>123652170</v>
       </c>
       <c r="B27" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3732,35 +3720,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3768,10 +3752,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513623</v>
+        <v>513607</v>
       </c>
       <c r="R27" t="n">
-        <v>6733240</v>
+        <v>6733239</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3803,7 +3787,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3813,12 +3797,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3827,6 +3811,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3845,10 +3830,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652182</v>
+        <v>123652187</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3889,7 +3874,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513620</v>
+        <v>513627</v>
       </c>
       <c r="R28" t="n">
         <v>6733241</v>
@@ -3924,7 +3909,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3934,7 +3919,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3967,10 +3952,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123656504</v>
+        <v>123652197</v>
       </c>
       <c r="B29" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3979,35 +3964,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4015,10 +3996,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513643</v>
+        <v>513644</v>
       </c>
       <c r="R29" t="n">
-        <v>6733240</v>
+        <v>6733242</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4050,7 +4031,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4060,12 +4041,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,6 +4055,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4092,10 +4074,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652213</v>
+        <v>123652176</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,10 +4118,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513617</v>
+        <v>513605</v>
       </c>
       <c r="R30" t="n">
-        <v>6733269</v>
+        <v>6733249</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4171,7 +4153,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4181,12 +4163,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4214,10 +4196,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652191</v>
+        <v>123652181</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4258,10 +4240,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513628</v>
+        <v>513619</v>
       </c>
       <c r="R31" t="n">
-        <v>6733228</v>
+        <v>6733234</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4293,7 +4275,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,7 +4285,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4336,10 +4318,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123650528</v>
+        <v>123652190</v>
       </c>
       <c r="B32" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4348,35 +4330,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4384,10 +4362,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513632</v>
+        <v>513627</v>
       </c>
       <c r="R32" t="n">
-        <v>6733214</v>
+        <v>6733227</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4419,7 +4397,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4429,7 +4407,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,6 +4421,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4449,17 +4433,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652177</v>
+        <v>123652192</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4500,10 +4484,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513615</v>
+        <v>513630</v>
       </c>
       <c r="R33" t="n">
-        <v>6733245</v>
+        <v>6733221</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4535,7 +4519,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4545,7 +4529,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4578,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652224</v>
+        <v>123652164</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4622,10 +4606,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513610</v>
+        <v>513617</v>
       </c>
       <c r="R34" t="n">
-        <v>6733242</v>
+        <v>6733240</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4657,7 +4641,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4667,12 +4651,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4700,10 +4684,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652201</v>
+        <v>123652205</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4744,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513640</v>
+        <v>513635</v>
       </c>
       <c r="R35" t="n">
-        <v>6733246</v>
+        <v>6733245</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4779,7 +4763,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4789,7 +4773,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4822,10 +4806,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652170</v>
+        <v>123652193</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4866,10 +4850,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513607</v>
+        <v>513631</v>
       </c>
       <c r="R36" t="n">
-        <v>6733239</v>
+        <v>6733221</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4901,7 +4885,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4911,12 +4895,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4944,10 +4928,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652174</v>
+        <v>123652182</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4988,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513606</v>
+        <v>513620</v>
       </c>
       <c r="R37" t="n">
-        <v>6733257</v>
+        <v>6733241</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5023,7 +5007,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5033,7 +5017,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5066,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652169</v>
+        <v>123652168</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5110,10 +5094,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513603</v>
+        <v>513593</v>
       </c>
       <c r="R38" t="n">
-        <v>6733229</v>
+        <v>6733228</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5145,7 +5129,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5155,7 +5139,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5188,10 +5172,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652187</v>
+        <v>123652200</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5232,10 +5216,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513627</v>
+        <v>513638</v>
       </c>
       <c r="R39" t="n">
-        <v>6733241</v>
+        <v>6733248</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5267,7 +5251,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5277,12 +5261,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5310,10 +5294,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652211</v>
+        <v>123652218</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5354,10 +5338,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513625</v>
+        <v>513613</v>
       </c>
       <c r="R40" t="n">
-        <v>6733258</v>
+        <v>6733273</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5389,7 +5373,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5399,12 +5383,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5432,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123656505</v>
+        <v>123652225</v>
       </c>
       <c r="B41" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5444,35 +5428,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5480,10 +5460,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513624</v>
+        <v>513617</v>
       </c>
       <c r="R41" t="n">
-        <v>6733235</v>
+        <v>6733234</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5515,7 +5495,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5525,12 +5505,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5539,6 +5519,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5557,10 +5538,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123650524</v>
+        <v>123652178</v>
       </c>
       <c r="B42" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5569,39 +5550,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5609,10 +5582,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513595</v>
+        <v>513605</v>
       </c>
       <c r="R42" t="n">
-        <v>6733257</v>
+        <v>6733242</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5644,7 +5617,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5654,7 +5627,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5663,6 +5641,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5681,10 +5660,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652178</v>
+        <v>123650523</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5693,31 +5672,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5725,10 +5712,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513605</v>
+        <v>513585</v>
       </c>
       <c r="R43" t="n">
-        <v>6733242</v>
+        <v>6733249</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5760,7 +5747,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5770,12 +5757,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5784,7 +5771,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5803,10 +5789,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652216</v>
+        <v>123652208</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5847,10 +5833,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513614</v>
+        <v>513626</v>
       </c>
       <c r="R44" t="n">
-        <v>6733272</v>
+        <v>6733254</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5882,7 +5868,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,12 +5878,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5925,10 +5911,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123656499</v>
+        <v>123652209</v>
       </c>
       <c r="B45" t="n">
-        <v>97369</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5937,25 +5923,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5969,13 +5955,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513625</v>
+        <v>513620</v>
       </c>
       <c r="R45" t="n">
-        <v>6733311</v>
+        <v>6733253</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6004,7 +5990,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6014,7 +6000,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,10 +6033,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123656500</v>
+        <v>123652204</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6054,32 +6045,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6087,13 +6077,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513668</v>
+        <v>513632</v>
       </c>
       <c r="R46" t="n">
-        <v>6733244</v>
+        <v>6733247</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6117,22 +6107,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6153,17 +6148,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652214</v>
+        <v>123652171</v>
       </c>
       <c r="B47" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6204,10 +6199,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513615</v>
+        <v>513608</v>
       </c>
       <c r="R47" t="n">
-        <v>6733271</v>
+        <v>6733238</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6239,7 +6234,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6249,12 +6244,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6282,10 +6277,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652175</v>
+        <v>123656502</v>
       </c>
       <c r="B48" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6294,31 +6289,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6326,10 +6325,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513606</v>
+        <v>513623</v>
       </c>
       <c r="R48" t="n">
-        <v>6733254</v>
+        <v>6733240</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6361,7 +6360,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6371,12 +6370,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6385,7 +6384,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6404,10 +6402,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123650526</v>
+        <v>123656505</v>
       </c>
       <c r="B49" t="n">
-        <v>56692</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6420,16 +6418,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6442,7 +6440,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6452,10 +6450,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513627</v>
+        <v>513624</v>
       </c>
       <c r="R49" t="n">
-        <v>6733250</v>
+        <v>6733235</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6502,7 +6500,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6529,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652186</v>
+        <v>123656504</v>
       </c>
       <c r="B50" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6541,31 +6539,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6573,10 +6575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513623</v>
+        <v>513643</v>
       </c>
       <c r="R50" t="n">
-        <v>6733238</v>
+        <v>6733240</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6608,7 +6610,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6618,12 +6620,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6632,7 +6634,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6651,10 +6652,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652226</v>
+        <v>123652174</v>
       </c>
       <c r="B51" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6695,10 +6696,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513622</v>
+        <v>513606</v>
       </c>
       <c r="R51" t="n">
-        <v>6733236</v>
+        <v>6733257</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6730,7 +6731,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6740,12 +6741,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6773,10 +6774,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652202</v>
+        <v>123656503</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6785,31 +6786,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6817,10 +6822,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513640</v>
+        <v>513619</v>
       </c>
       <c r="R52" t="n">
-        <v>6733250</v>
+        <v>6733230</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6852,7 +6857,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6862,12 +6867,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6876,7 +6881,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6895,10 +6899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652199</v>
+        <v>123652160</v>
       </c>
       <c r="B53" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6939,7 +6943,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513642</v>
+        <v>513608</v>
       </c>
       <c r="R53" t="n">
         <v>6733246</v>
@@ -6974,7 +6978,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6984,12 +6988,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7017,10 +7021,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652179</v>
+        <v>123652185</v>
       </c>
       <c r="B54" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7061,10 +7065,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513611</v>
+        <v>513619</v>
       </c>
       <c r="R54" t="n">
-        <v>6733236</v>
+        <v>6733240</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7096,7 +7100,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7106,12 +7110,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7139,10 +7143,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652168</v>
+        <v>123652175</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7183,10 +7187,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513593</v>
+        <v>513606</v>
       </c>
       <c r="R55" t="n">
-        <v>6733228</v>
+        <v>6733254</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7218,7 +7222,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7228,7 +7232,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7261,10 +7265,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652161</v>
+        <v>123650526</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7273,31 +7277,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7305,10 +7313,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513597</v>
+        <v>513627</v>
       </c>
       <c r="R56" t="n">
-        <v>6733265</v>
+        <v>6733250</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7340,7 +7348,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7350,12 +7358,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7364,7 +7372,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7376,17 +7383,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652162</v>
+        <v>123652216</v>
       </c>
       <c r="B57" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7427,10 +7434,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513604</v>
+        <v>513614</v>
       </c>
       <c r="R57" t="n">
-        <v>6733250</v>
+        <v>6733272</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7462,7 +7469,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7472,12 +7479,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7505,10 +7512,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652192</v>
+        <v>123652195</v>
       </c>
       <c r="B58" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7549,10 +7556,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513630</v>
+        <v>513645</v>
       </c>
       <c r="R58" t="n">
-        <v>6733221</v>
+        <v>6733241</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7584,7 +7591,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7594,12 +7601,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7627,10 +7634,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652181</v>
+        <v>123652163</v>
       </c>
       <c r="B59" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7671,13 +7678,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513619</v>
+        <v>513621</v>
       </c>
       <c r="R59" t="n">
-        <v>6733234</v>
+        <v>6733235</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7706,7 +7713,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7716,7 +7723,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7749,10 +7756,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652197</v>
+        <v>123652220</v>
       </c>
       <c r="B60" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7793,10 +7800,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513644</v>
+        <v>513609</v>
       </c>
       <c r="R60" t="n">
-        <v>6733242</v>
+        <v>6733266</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7828,7 +7835,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7838,7 +7845,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7871,10 +7878,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123650523</v>
+        <v>123652169</v>
       </c>
       <c r="B61" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7883,39 +7890,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7923,10 +7922,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513585</v>
+        <v>513603</v>
       </c>
       <c r="R61" t="n">
-        <v>6733249</v>
+        <v>6733229</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7958,7 +7957,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7968,12 +7967,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7982,6 +7981,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8000,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652203</v>
+        <v>123652191</v>
       </c>
       <c r="B62" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513639</v>
+        <v>513628</v>
       </c>
       <c r="R62" t="n">
-        <v>6733252</v>
+        <v>6733228</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8122,10 +8122,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652190</v>
+        <v>123652224</v>
       </c>
       <c r="B63" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513627</v>
+        <v>513610</v>
       </c>
       <c r="R63" t="n">
-        <v>6733227</v>
+        <v>6733242</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,10 +8244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652188</v>
+        <v>123652223</v>
       </c>
       <c r="B64" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513629</v>
+        <v>513611</v>
       </c>
       <c r="R64" t="n">
-        <v>6733239</v>
+        <v>6733249</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8366,10 +8366,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652210</v>
+        <v>123652173</v>
       </c>
       <c r="B65" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513625</v>
+        <v>513600</v>
       </c>
       <c r="R65" t="n">
-        <v>6733251</v>
+        <v>6733258</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8488,10 +8488,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652222</v>
+        <v>123652189</v>
       </c>
       <c r="B66" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513612</v>
+        <v>513629</v>
       </c>
       <c r="R66" t="n">
-        <v>6733260</v>
+        <v>6733228</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8610,10 +8610,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652180</v>
+        <v>123652194</v>
       </c>
       <c r="B67" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513623</v>
+        <v>513642</v>
       </c>
       <c r="R67" t="n">
-        <v>6733239</v>
+        <v>6733220</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8732,10 +8732,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652218</v>
+        <v>123652180</v>
       </c>
       <c r="B68" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513613</v>
+        <v>513623</v>
       </c>
       <c r="R68" t="n">
-        <v>6733273</v>
+        <v>6733239</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8854,10 +8854,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652208</v>
+        <v>123652217</v>
       </c>
       <c r="B69" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513626</v>
+        <v>513612</v>
       </c>
       <c r="R69" t="n">
-        <v>6733254</v>
+        <v>6733277</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,10 +8976,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652205</v>
+        <v>123652210</v>
       </c>
       <c r="B70" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513635</v>
+        <v>513625</v>
       </c>
       <c r="R70" t="n">
-        <v>6733245</v>
+        <v>6733251</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9098,10 +9098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652193</v>
+        <v>123650524</v>
       </c>
       <c r="B71" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9110,31 +9110,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9142,10 +9150,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513631</v>
+        <v>513595</v>
       </c>
       <c r="R71" t="n">
-        <v>6733221</v>
+        <v>6733257</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9177,7 +9185,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9187,12 +9195,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9201,7 +9204,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9220,10 +9222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652160</v>
+        <v>123652212</v>
       </c>
       <c r="B72" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9264,10 +9266,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513608</v>
+        <v>513623</v>
       </c>
       <c r="R72" t="n">
-        <v>6733246</v>
+        <v>6733260</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9299,7 +9301,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9309,12 +9311,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9342,10 +9344,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652217</v>
+        <v>123652203</v>
       </c>
       <c r="B73" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9386,10 +9388,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513612</v>
+        <v>513639</v>
       </c>
       <c r="R73" t="n">
-        <v>6733277</v>
+        <v>6733252</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9423,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,7 +9433,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -9464,10 +9466,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652194</v>
+        <v>123650528</v>
       </c>
       <c r="B74" t="n">
-        <v>98504</v>
+        <v>56692</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9476,31 +9478,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9508,10 +9514,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513642</v>
+        <v>513632</v>
       </c>
       <c r="R74" t="n">
-        <v>6733220</v>
+        <v>6733214</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9549,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9559,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9567,7 +9568,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -9222,10 +9222,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652212</v>
+        <v>123650528</v>
       </c>
       <c r="B72" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9234,31 +9234,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9266,10 +9270,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513623</v>
+        <v>513632</v>
       </c>
       <c r="R72" t="n">
-        <v>6733260</v>
+        <v>6733214</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9301,7 +9305,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9311,12 +9315,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9325,7 +9324,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9337,14 +9335,14 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652203</v>
+        <v>123652212</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9388,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513639</v>
+        <v>513623</v>
       </c>
       <c r="R73" t="n">
-        <v>6733252</v>
+        <v>6733260</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9423,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9433,7 +9431,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -9466,10 +9464,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123650528</v>
+        <v>123652203</v>
       </c>
       <c r="B74" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9478,35 +9476,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9514,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513632</v>
+        <v>513639</v>
       </c>
       <c r="R74" t="n">
-        <v>6733214</v>
+        <v>6733252</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9549,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9559,7 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9568,6 +9567,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252664</v>
+        <v>123253165</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513616</v>
+        <v>513623</v>
       </c>
       <c r="R3" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R5" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652201</v>
+        <v>123652173</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513640</v>
+        <v>513600</v>
       </c>
       <c r="R6" t="n">
-        <v>6733246</v>
+        <v>6733258</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652214</v>
+        <v>123652179</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513615</v>
+        <v>513611</v>
       </c>
       <c r="R7" t="n">
-        <v>6733271</v>
+        <v>6733236</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652219</v>
+        <v>123652186</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513609</v>
+        <v>513623</v>
       </c>
       <c r="R8" t="n">
-        <v>6733267</v>
+        <v>6733238</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652207</v>
+        <v>123652202</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513629</v>
+        <v>513640</v>
       </c>
       <c r="R9" t="n">
-        <v>6733245</v>
+        <v>6733250</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123656499</v>
+        <v>123652197</v>
       </c>
       <c r="B10" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,25 +1655,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513625</v>
+        <v>513644</v>
       </c>
       <c r="R10" t="n">
-        <v>6733311</v>
+        <v>6733242</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,7 +1765,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652199</v>
+        <v>123652217</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1804,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513642</v>
+        <v>513612</v>
       </c>
       <c r="R11" t="n">
-        <v>6733246</v>
+        <v>6733277</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1839,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,12 +1854,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652211</v>
+        <v>123656505</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1894,31 +1899,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1926,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513625</v>
+        <v>513624</v>
       </c>
       <c r="R12" t="n">
-        <v>6733258</v>
+        <v>6733235</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1961,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1971,12 +1980,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,7 +1994,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2004,7 +2012,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652202</v>
+        <v>123652195</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2048,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513640</v>
+        <v>513645</v>
       </c>
       <c r="R13" t="n">
-        <v>6733250</v>
+        <v>6733241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2083,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2093,12 +2101,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652206</v>
+        <v>123652193</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2170,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513623</v>
+        <v>513631</v>
       </c>
       <c r="R14" t="n">
-        <v>6733237</v>
+        <v>6733221</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2205,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2215,12 +2223,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,7 +2256,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652222</v>
+        <v>123652176</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2292,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513612</v>
+        <v>513605</v>
       </c>
       <c r="R15" t="n">
-        <v>6733260</v>
+        <v>6733249</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2327,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,7 +2378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652226</v>
+        <v>123652181</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2414,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513622</v>
+        <v>513619</v>
       </c>
       <c r="R16" t="n">
-        <v>6733236</v>
+        <v>6733234</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2449,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2459,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,7 +2500,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652179</v>
+        <v>123652168</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2536,10 +2544,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513611</v>
+        <v>513593</v>
       </c>
       <c r="R17" t="n">
-        <v>6733236</v>
+        <v>6733228</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2571,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2581,12 +2589,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2614,7 +2622,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652221</v>
+        <v>123652164</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2658,10 +2666,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513613</v>
+        <v>513617</v>
       </c>
       <c r="R18" t="n">
-        <v>6733269</v>
+        <v>6733240</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2693,7 +2701,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2703,12 +2711,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2736,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123656500</v>
+        <v>123652209</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2748,32 +2756,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2781,13 +2788,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513668</v>
+        <v>513620</v>
       </c>
       <c r="R19" t="n">
-        <v>6733244</v>
+        <v>6733253</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2811,22 +2818,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2847,14 +2859,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652188</v>
+        <v>123652214</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2898,10 +2910,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513629</v>
+        <v>513615</v>
       </c>
       <c r="R20" t="n">
-        <v>6733239</v>
+        <v>6733271</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2933,7 +2945,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2943,12 +2955,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,7 +2988,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652184</v>
+        <v>123652225</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3020,10 +3032,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513618</v>
+        <v>513617</v>
       </c>
       <c r="R21" t="n">
-        <v>6733235</v>
+        <v>6733234</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3055,7 +3067,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,12 +3077,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652213</v>
+        <v>123650523</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3110,31 +3122,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3142,10 +3162,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513617</v>
+        <v>513585</v>
       </c>
       <c r="R22" t="n">
-        <v>6733269</v>
+        <v>6733249</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3177,7 +3197,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3187,12 +3207,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3201,7 +3221,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3220,7 +3239,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652186</v>
+        <v>123652192</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3264,10 +3283,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513623</v>
+        <v>513630</v>
       </c>
       <c r="R23" t="n">
-        <v>6733238</v>
+        <v>6733221</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3299,7 +3318,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3309,7 +3328,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3342,7 +3361,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652161</v>
+        <v>123652207</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3386,10 +3405,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513597</v>
+        <v>513629</v>
       </c>
       <c r="R24" t="n">
-        <v>6733265</v>
+        <v>6733245</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3421,7 +3440,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3431,12 +3450,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,14 +3476,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652177</v>
+        <v>123652211</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3508,10 +3527,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513615</v>
+        <v>513625</v>
       </c>
       <c r="R25" t="n">
-        <v>6733245</v>
+        <v>6733258</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3543,7 +3562,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3553,12 +3572,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3586,7 +3605,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652162</v>
+        <v>123652187</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3630,10 +3649,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513604</v>
+        <v>513627</v>
       </c>
       <c r="R26" t="n">
-        <v>6733250</v>
+        <v>6733241</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3665,7 +3684,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3675,7 +3694,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3708,7 +3727,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652170</v>
+        <v>123652206</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3752,10 +3771,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513607</v>
+        <v>513623</v>
       </c>
       <c r="R27" t="n">
-        <v>6733239</v>
+        <v>6733237</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3787,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3797,12 +3816,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3830,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652187</v>
+        <v>123652177</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3874,10 +3893,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513627</v>
+        <v>513615</v>
       </c>
       <c r="R28" t="n">
-        <v>6733241</v>
+        <v>6733245</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3909,7 +3928,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3919,7 +3938,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3952,7 +3971,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652197</v>
+        <v>123652191</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3996,10 +4015,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513644</v>
+        <v>513628</v>
       </c>
       <c r="R29" t="n">
-        <v>6733242</v>
+        <v>6733228</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4031,7 +4050,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4041,12 +4060,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,7 +4093,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652176</v>
+        <v>123652184</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4118,10 +4137,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513605</v>
+        <v>513618</v>
       </c>
       <c r="R30" t="n">
-        <v>6733249</v>
+        <v>6733235</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4153,7 +4172,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4163,7 +4182,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4196,7 +4215,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652181</v>
+        <v>123652190</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4240,10 +4259,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513619</v>
+        <v>513627</v>
       </c>
       <c r="R31" t="n">
-        <v>6733234</v>
+        <v>6733227</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4275,7 +4294,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4285,7 +4304,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4318,10 +4337,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652190</v>
+        <v>123650526</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4330,31 +4349,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4365,7 +4388,7 @@
         <v>513627</v>
       </c>
       <c r="R32" t="n">
-        <v>6733227</v>
+        <v>6733250</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4397,7 +4420,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4407,12 +4430,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4421,7 +4444,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4440,7 +4462,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652192</v>
+        <v>123652205</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4484,10 +4506,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513630</v>
+        <v>513635</v>
       </c>
       <c r="R33" t="n">
-        <v>6733221</v>
+        <v>6733245</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4519,7 +4541,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4529,12 +4551,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4562,7 +4584,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652164</v>
+        <v>123652212</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4606,10 +4628,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513617</v>
+        <v>513623</v>
       </c>
       <c r="R34" t="n">
-        <v>6733240</v>
+        <v>6733260</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4641,7 +4663,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4651,12 +4673,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4684,7 +4706,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652205</v>
+        <v>123652213</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4728,10 +4750,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513635</v>
+        <v>513617</v>
       </c>
       <c r="R35" t="n">
-        <v>6733245</v>
+        <v>6733269</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4763,7 +4785,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4773,7 +4795,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4806,7 +4828,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652193</v>
+        <v>123652163</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4850,13 +4872,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513631</v>
+        <v>513621</v>
       </c>
       <c r="R36" t="n">
-        <v>6733221</v>
+        <v>6733235</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4885,7 +4907,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4895,12 +4917,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4928,7 +4950,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652182</v>
+        <v>123652160</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4972,10 +4994,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513620</v>
+        <v>513608</v>
       </c>
       <c r="R37" t="n">
-        <v>6733241</v>
+        <v>6733246</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5007,7 +5029,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5017,7 +5039,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5050,7 +5072,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652168</v>
+        <v>123652220</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5094,10 +5116,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513593</v>
+        <v>513609</v>
       </c>
       <c r="R38" t="n">
-        <v>6733228</v>
+        <v>6733266</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5129,7 +5151,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5139,12 +5161,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5172,7 +5194,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652200</v>
+        <v>123652203</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5216,10 +5238,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513638</v>
+        <v>513639</v>
       </c>
       <c r="R39" t="n">
-        <v>6733248</v>
+        <v>6733252</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5251,7 +5273,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5261,12 +5283,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5294,7 +5316,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652218</v>
+        <v>123652178</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5338,10 +5360,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513613</v>
+        <v>513605</v>
       </c>
       <c r="R40" t="n">
-        <v>6733273</v>
+        <v>6733242</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5373,7 +5395,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5383,12 +5405,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5416,10 +5438,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652225</v>
+        <v>123656502</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5428,31 +5450,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5460,10 +5486,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513617</v>
+        <v>513623</v>
       </c>
       <c r="R41" t="n">
-        <v>6733234</v>
+        <v>6733240</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5495,7 +5521,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5505,12 +5531,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5519,7 +5545,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5538,7 +5563,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652178</v>
+        <v>123652219</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5582,10 +5607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513605</v>
+        <v>513609</v>
       </c>
       <c r="R42" t="n">
-        <v>6733242</v>
+        <v>6733267</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5617,7 +5642,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5627,12 +5652,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5660,10 +5685,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123650523</v>
+        <v>123652194</v>
       </c>
       <c r="B43" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5672,39 +5697,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5712,10 +5729,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513585</v>
+        <v>513642</v>
       </c>
       <c r="R43" t="n">
-        <v>6733249</v>
+        <v>6733220</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5747,7 +5764,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5757,12 +5774,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5771,6 +5788,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5789,7 +5807,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652208</v>
+        <v>123652180</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5833,10 +5851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513626</v>
+        <v>513623</v>
       </c>
       <c r="R44" t="n">
-        <v>6733254</v>
+        <v>6733239</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5868,7 +5886,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5878,12 +5896,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5911,7 +5929,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652209</v>
+        <v>123652216</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5955,10 +5973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513620</v>
+        <v>513614</v>
       </c>
       <c r="R45" t="n">
-        <v>6733253</v>
+        <v>6733272</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5990,7 +6008,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6000,12 +6018,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6033,7 +6051,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652204</v>
+        <v>123652162</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6077,10 +6095,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513632</v>
+        <v>513604</v>
       </c>
       <c r="R46" t="n">
-        <v>6733247</v>
+        <v>6733250</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6112,7 +6130,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6122,12 +6140,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6155,7 +6173,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652171</v>
+        <v>123652218</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6199,10 +6217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513608</v>
+        <v>513613</v>
       </c>
       <c r="R47" t="n">
-        <v>6733238</v>
+        <v>6733273</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6234,7 +6252,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6244,12 +6262,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,10 +6295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123656502</v>
+        <v>123652226</v>
       </c>
       <c r="B48" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6289,35 +6307,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6325,10 +6339,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513623</v>
+        <v>513622</v>
       </c>
       <c r="R48" t="n">
-        <v>6733240</v>
+        <v>6733236</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6360,7 +6374,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6370,12 +6384,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,6 +6398,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6402,10 +6417,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123656505</v>
+        <v>123652223</v>
       </c>
       <c r="B49" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6414,35 +6429,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6450,10 +6461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513624</v>
+        <v>513611</v>
       </c>
       <c r="R49" t="n">
-        <v>6733235</v>
+        <v>6733249</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6485,7 +6496,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6495,12 +6506,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6509,6 +6520,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6527,10 +6539,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123656504</v>
+        <v>123652185</v>
       </c>
       <c r="B50" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6539,35 +6551,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6575,7 +6583,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513643</v>
+        <v>513619</v>
       </c>
       <c r="R50" t="n">
         <v>6733240</v>
@@ -6610,7 +6618,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6620,12 +6628,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6634,6 +6642,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6899,10 +6908,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652160</v>
+        <v>123656500</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6911,31 +6920,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6943,13 +6953,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513608</v>
+        <v>513668</v>
       </c>
       <c r="R53" t="n">
-        <v>6733246</v>
+        <v>6733244</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6973,27 +6983,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7014,17 +7019,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652185</v>
+        <v>123650528</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7033,31 +7038,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7065,10 +7074,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513619</v>
+        <v>513632</v>
       </c>
       <c r="R54" t="n">
-        <v>6733240</v>
+        <v>6733214</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7100,7 +7109,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7110,12 +7119,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7124,7 +7128,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7136,14 +7139,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652175</v>
+        <v>123652201</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -7187,10 +7190,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513606</v>
+        <v>513640</v>
       </c>
       <c r="R55" t="n">
-        <v>6733254</v>
+        <v>6733246</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7222,7 +7225,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7232,12 +7235,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7265,10 +7268,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123650526</v>
+        <v>123652200</v>
       </c>
       <c r="B56" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7277,35 +7280,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7313,10 +7312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513627</v>
+        <v>513638</v>
       </c>
       <c r="R56" t="n">
-        <v>6733250</v>
+        <v>6733248</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7348,7 +7347,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7358,12 +7357,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7372,6 +7371,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7390,7 +7390,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652216</v>
+        <v>123652204</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513614</v>
+        <v>513632</v>
       </c>
       <c r="R57" t="n">
-        <v>6733272</v>
+        <v>6733247</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7512,7 +7512,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652195</v>
+        <v>123652210</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513645</v>
+        <v>513625</v>
       </c>
       <c r="R58" t="n">
-        <v>6733241</v>
+        <v>6733251</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7634,7 +7634,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652163</v>
+        <v>123652161</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513621</v>
+        <v>513597</v>
       </c>
       <c r="R59" t="n">
-        <v>6733235</v>
+        <v>6733265</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652220</v>
+        <v>123652208</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513609</v>
+        <v>513626</v>
       </c>
       <c r="R60" t="n">
-        <v>6733266</v>
+        <v>6733254</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7878,7 +7878,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652169</v>
+        <v>123652189</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513603</v>
+        <v>513629</v>
       </c>
       <c r="R61" t="n">
-        <v>6733229</v>
+        <v>6733228</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,7 +8000,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652191</v>
+        <v>123652224</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8044,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513628</v>
+        <v>513610</v>
       </c>
       <c r="R62" t="n">
-        <v>6733228</v>
+        <v>6733242</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8122,7 +8122,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652224</v>
+        <v>123652222</v>
       </c>
       <c r="B63" t="n">
         <v>98079</v>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513610</v>
+        <v>513612</v>
       </c>
       <c r="R63" t="n">
-        <v>6733242</v>
+        <v>6733260</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,7 +8244,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652223</v>
+        <v>123652170</v>
       </c>
       <c r="B64" t="n">
         <v>98079</v>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513611</v>
+        <v>513607</v>
       </c>
       <c r="R64" t="n">
-        <v>6733249</v>
+        <v>6733239</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8366,10 +8366,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652173</v>
+        <v>123650524</v>
       </c>
       <c r="B65" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8378,31 +8378,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8410,10 +8418,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513600</v>
+        <v>513595</v>
       </c>
       <c r="R65" t="n">
-        <v>6733258</v>
+        <v>6733257</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8445,7 +8453,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8455,12 +8463,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8469,7 +8472,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8488,10 +8490,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652189</v>
+        <v>123656504</v>
       </c>
       <c r="B66" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8500,31 +8502,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8532,10 +8538,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513629</v>
+        <v>513643</v>
       </c>
       <c r="R66" t="n">
-        <v>6733228</v>
+        <v>6733240</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8567,7 +8573,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,12 +8583,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8591,7 +8597,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8610,7 +8615,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652194</v>
+        <v>123652182</v>
       </c>
       <c r="B67" t="n">
         <v>98079</v>
@@ -8654,10 +8659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513642</v>
+        <v>513620</v>
       </c>
       <c r="R67" t="n">
-        <v>6733220</v>
+        <v>6733241</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8689,7 +8694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8699,7 +8704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8732,7 +8737,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652180</v>
+        <v>123652169</v>
       </c>
       <c r="B68" t="n">
         <v>98079</v>
@@ -8776,10 +8781,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513623</v>
+        <v>513603</v>
       </c>
       <c r="R68" t="n">
-        <v>6733239</v>
+        <v>6733229</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8816,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,7 +8826,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8854,10 +8859,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652217</v>
+        <v>123656499</v>
       </c>
       <c r="B69" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8866,25 +8871,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8898,13 +8903,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513612</v>
+        <v>513625</v>
       </c>
       <c r="R69" t="n">
-        <v>6733277</v>
+        <v>6733311</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8933,7 +8938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,12 +8948,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,7 +8976,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652210</v>
+        <v>123652188</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513625</v>
+        <v>513629</v>
       </c>
       <c r="R70" t="n">
-        <v>6733251</v>
+        <v>6733239</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9098,10 +9098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123650524</v>
+        <v>123652175</v>
       </c>
       <c r="B71" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9110,39 +9110,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9150,10 +9142,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513595</v>
+        <v>513606</v>
       </c>
       <c r="R71" t="n">
-        <v>6733257</v>
+        <v>6733254</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9185,7 +9177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9195,7 +9187,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9204,6 +9201,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9222,10 +9220,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123650528</v>
+        <v>123652171</v>
       </c>
       <c r="B72" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9234,35 +9232,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9270,10 +9264,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513632</v>
+        <v>513608</v>
       </c>
       <c r="R72" t="n">
-        <v>6733214</v>
+        <v>6733238</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9305,7 +9299,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9315,7 +9309,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9324,6 +9323,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9335,14 +9335,14 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652212</v>
+        <v>123652199</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513623</v>
+        <v>513642</v>
       </c>
       <c r="R73" t="n">
-        <v>6733260</v>
+        <v>6733246</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652203</v>
+        <v>123652221</v>
       </c>
       <c r="B74" t="n">
         <v>98079</v>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513639</v>
+        <v>513613</v>
       </c>
       <c r="R74" t="n">
-        <v>6733252</v>
+        <v>6733269</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123253165</v>
+        <v>123252664</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -827,12 +827,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513623</v>
+        <v>513616</v>
       </c>
       <c r="R3" t="n">
-        <v>6733230</v>
+        <v>6733249</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252821</v>
+        <v>123253165</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513598</v>
+        <v>513623</v>
       </c>
       <c r="R4" t="n">
-        <v>6733234</v>
+        <v>6733230</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252664</v>
+        <v>123252821</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513616</v>
+        <v>513598</v>
       </c>
       <c r="R5" t="n">
-        <v>6733249</v>
+        <v>6733234</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652173</v>
+        <v>123656504</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,31 +1167,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1199,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513600</v>
+        <v>513643</v>
       </c>
       <c r="R6" t="n">
-        <v>6733258</v>
+        <v>6733240</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1262,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1277,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652179</v>
+        <v>123652205</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1321,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513611</v>
+        <v>513635</v>
       </c>
       <c r="R7" t="n">
-        <v>6733236</v>
+        <v>6733245</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652186</v>
+        <v>123652162</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1443,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513623</v>
+        <v>513604</v>
       </c>
       <c r="R8" t="n">
-        <v>6733238</v>
+        <v>6733250</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1521,7 +1524,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652202</v>
+        <v>123652161</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1565,10 +1568,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513640</v>
+        <v>513597</v>
       </c>
       <c r="R9" t="n">
-        <v>6733250</v>
+        <v>6733265</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1613,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,17 +1639,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652197</v>
+        <v>123656500</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,31 +1658,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1687,13 +1691,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513644</v>
+        <v>513668</v>
       </c>
       <c r="R10" t="n">
-        <v>6733242</v>
+        <v>6733244</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,27 +1721,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,14 +1757,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652217</v>
+        <v>123652214</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1809,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513612</v>
+        <v>513615</v>
       </c>
       <c r="R11" t="n">
-        <v>6733277</v>
+        <v>6733271</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1844,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,12 +1853,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1886,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123656505</v>
+        <v>123652191</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,35 +1898,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1935,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513624</v>
+        <v>513628</v>
       </c>
       <c r="R12" t="n">
-        <v>6733235</v>
+        <v>6733228</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1970,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,12 +1975,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,6 +1989,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2012,7 +2008,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652195</v>
+        <v>123652175</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2056,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513645</v>
+        <v>513606</v>
       </c>
       <c r="R13" t="n">
-        <v>6733241</v>
+        <v>6733254</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2091,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,12 +2097,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652193</v>
+        <v>123650528</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,31 +2142,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513631</v>
+        <v>513632</v>
       </c>
       <c r="R14" t="n">
-        <v>6733221</v>
+        <v>6733214</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,12 +2223,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,7 +2232,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2249,17 +2243,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652176</v>
+        <v>123656499</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,25 +2262,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2300,13 +2294,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513605</v>
+        <v>513625</v>
       </c>
       <c r="R15" t="n">
-        <v>6733249</v>
+        <v>6733311</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2335,7 +2329,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,12 +2339,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,7 +2367,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652181</v>
+        <v>123652186</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2422,10 +2411,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513619</v>
+        <v>513623</v>
       </c>
       <c r="R16" t="n">
-        <v>6733234</v>
+        <v>6733238</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,7 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2500,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652168</v>
+        <v>123652170</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2544,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513593</v>
+        <v>513607</v>
       </c>
       <c r="R17" t="n">
-        <v>6733228</v>
+        <v>6733239</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2622,7 +2611,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652164</v>
+        <v>123652201</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2666,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513617</v>
+        <v>513640</v>
       </c>
       <c r="R18" t="n">
-        <v>6733240</v>
+        <v>6733246</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2701,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,12 +2700,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,7 +2733,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652209</v>
+        <v>123652195</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2788,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513620</v>
+        <v>513645</v>
       </c>
       <c r="R19" t="n">
-        <v>6733253</v>
+        <v>6733241</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2823,7 +2812,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2833,12 +2822,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2866,7 +2855,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652214</v>
+        <v>123652193</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2910,10 +2899,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513615</v>
+        <v>513631</v>
       </c>
       <c r="R20" t="n">
-        <v>6733271</v>
+        <v>6733221</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2945,7 +2934,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2955,12 +2944,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,7 +2977,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652225</v>
+        <v>123652177</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3032,10 +3021,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513617</v>
+        <v>513615</v>
       </c>
       <c r="R21" t="n">
-        <v>6733234</v>
+        <v>6733245</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3067,7 +3056,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3077,12 +3066,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,10 +3099,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123650523</v>
+        <v>123652220</v>
       </c>
       <c r="B22" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3122,39 +3111,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3162,10 +3143,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513585</v>
+        <v>513609</v>
       </c>
       <c r="R22" t="n">
-        <v>6733249</v>
+        <v>6733266</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3197,7 +3178,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3207,12 +3188,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,6 +3202,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3239,7 +3221,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652192</v>
+        <v>123652185</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3283,10 +3265,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513630</v>
+        <v>513619</v>
       </c>
       <c r="R23" t="n">
-        <v>6733221</v>
+        <v>6733240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3318,7 +3300,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3328,7 +3310,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3361,7 +3343,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652207</v>
+        <v>123652180</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3405,10 +3387,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513629</v>
+        <v>513623</v>
       </c>
       <c r="R24" t="n">
-        <v>6733245</v>
+        <v>6733239</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3440,7 +3422,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3450,12 +3432,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3483,7 +3465,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652211</v>
+        <v>123652212</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3527,10 +3509,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513625</v>
+        <v>513623</v>
       </c>
       <c r="R25" t="n">
-        <v>6733258</v>
+        <v>6733260</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3562,7 +3544,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3572,12 +3554,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3605,7 +3587,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652187</v>
+        <v>123652218</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3649,10 +3631,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513627</v>
+        <v>513613</v>
       </c>
       <c r="R26" t="n">
-        <v>6733241</v>
+        <v>6733273</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3684,7 +3666,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3694,12 +3676,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3727,7 +3709,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652206</v>
+        <v>123652178</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3771,10 +3753,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513623</v>
+        <v>513605</v>
       </c>
       <c r="R27" t="n">
-        <v>6733237</v>
+        <v>6733242</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3806,7 +3788,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,12 +3798,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,7 +3831,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652177</v>
+        <v>123652208</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3893,10 +3875,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513615</v>
+        <v>513626</v>
       </c>
       <c r="R28" t="n">
-        <v>6733245</v>
+        <v>6733254</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3928,7 +3910,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3938,12 +3920,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3971,7 +3953,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652191</v>
+        <v>123652197</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -4015,10 +3997,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513628</v>
+        <v>513644</v>
       </c>
       <c r="R29" t="n">
-        <v>6733228</v>
+        <v>6733242</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4050,7 +4032,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4060,12 +4042,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4093,7 +4075,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652184</v>
+        <v>123652179</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4137,10 +4119,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513618</v>
+        <v>513611</v>
       </c>
       <c r="R30" t="n">
-        <v>6733235</v>
+        <v>6733236</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4172,7 +4154,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4182,12 +4164,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4215,7 +4197,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652190</v>
+        <v>123652189</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4259,10 +4241,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513627</v>
+        <v>513629</v>
       </c>
       <c r="R31" t="n">
-        <v>6733227</v>
+        <v>6733228</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4309,7 +4291,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4337,10 +4319,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123650526</v>
+        <v>123652181</v>
       </c>
       <c r="B32" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4349,35 +4331,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4385,10 +4363,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513627</v>
+        <v>513619</v>
       </c>
       <c r="R32" t="n">
-        <v>6733250</v>
+        <v>6733234</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4420,7 +4398,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4430,12 +4408,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4444,6 +4422,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4462,10 +4441,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652205</v>
+        <v>123650523</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4474,31 +4453,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4506,10 +4493,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513635</v>
+        <v>513585</v>
       </c>
       <c r="R33" t="n">
-        <v>6733245</v>
+        <v>6733249</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4541,7 +4528,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4551,12 +4538,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4565,7 +4552,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4584,10 +4570,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652212</v>
+        <v>123650526</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4596,31 +4582,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4628,10 +4618,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R34" t="n">
-        <v>6733260</v>
+        <v>6733250</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4663,7 +4653,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4673,12 +4663,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4687,7 +4677,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4706,10 +4695,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652213</v>
+        <v>123656503</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4718,31 +4707,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4750,10 +4743,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513617</v>
+        <v>513619</v>
       </c>
       <c r="R35" t="n">
-        <v>6733269</v>
+        <v>6733230</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4785,7 +4778,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4795,12 +4788,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4809,7 +4802,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4828,7 +4820,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652163</v>
+        <v>123652187</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4872,13 +4864,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513621</v>
+        <v>513627</v>
       </c>
       <c r="R36" t="n">
-        <v>6733235</v>
+        <v>6733241</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4907,7 +4899,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4917,7 +4909,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4950,7 +4942,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652160</v>
+        <v>123652190</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4994,10 +4986,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513608</v>
+        <v>513627</v>
       </c>
       <c r="R37" t="n">
-        <v>6733246</v>
+        <v>6733227</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5029,7 +5021,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5039,7 +5031,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5072,7 +5064,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652220</v>
+        <v>123652200</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5116,10 +5108,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513609</v>
+        <v>513638</v>
       </c>
       <c r="R38" t="n">
-        <v>6733266</v>
+        <v>6733248</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5151,7 +5143,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5161,7 +5153,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5194,7 +5186,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652203</v>
+        <v>123652174</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5238,10 +5230,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513639</v>
+        <v>513606</v>
       </c>
       <c r="R39" t="n">
-        <v>6733252</v>
+        <v>6733257</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5273,7 +5265,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5283,12 +5275,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5316,7 +5308,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652178</v>
+        <v>123652219</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5360,10 +5352,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513605</v>
+        <v>513609</v>
       </c>
       <c r="R40" t="n">
-        <v>6733242</v>
+        <v>6733267</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5395,7 +5387,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5405,12 +5397,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5438,10 +5430,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123656502</v>
+        <v>123652204</v>
       </c>
       <c r="B41" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5450,35 +5442,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5486,10 +5474,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513623</v>
+        <v>513632</v>
       </c>
       <c r="R41" t="n">
-        <v>6733240</v>
+        <v>6733247</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5521,7 +5509,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5531,12 +5519,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5545,6 +5533,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5563,7 +5552,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652219</v>
+        <v>123652210</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5607,10 +5596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513609</v>
+        <v>513625</v>
       </c>
       <c r="R42" t="n">
-        <v>6733267</v>
+        <v>6733251</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5642,7 +5631,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5652,12 +5641,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5685,10 +5674,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652194</v>
+        <v>123650524</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5697,31 +5686,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5729,10 +5726,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513642</v>
+        <v>513595</v>
       </c>
       <c r="R43" t="n">
-        <v>6733220</v>
+        <v>6733257</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5764,7 +5761,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5774,12 +5771,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5788,7 +5780,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5807,10 +5798,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652180</v>
+        <v>123656505</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5819,31 +5810,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5851,10 +5846,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513623</v>
+        <v>513624</v>
       </c>
       <c r="R44" t="n">
-        <v>6733239</v>
+        <v>6733235</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5886,7 +5881,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5896,12 +5891,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5910,7 +5905,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5929,7 +5923,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652216</v>
+        <v>123652222</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5973,10 +5967,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513614</v>
+        <v>513612</v>
       </c>
       <c r="R45" t="n">
-        <v>6733272</v>
+        <v>6733260</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6008,7 +6002,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6018,12 +6012,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6051,7 +6045,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652162</v>
+        <v>123652164</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6095,10 +6089,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513604</v>
+        <v>513617</v>
       </c>
       <c r="R46" t="n">
-        <v>6733250</v>
+        <v>6733240</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6130,7 +6124,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6140,7 +6134,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6173,7 +6167,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652218</v>
+        <v>123652160</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6217,10 +6211,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513613</v>
+        <v>513608</v>
       </c>
       <c r="R47" t="n">
-        <v>6733273</v>
+        <v>6733246</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6252,7 +6246,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6262,12 +6256,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6295,7 +6289,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652226</v>
+        <v>123652203</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6339,10 +6333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513622</v>
+        <v>513639</v>
       </c>
       <c r="R48" t="n">
-        <v>6733236</v>
+        <v>6733252</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6374,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6384,12 +6378,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6417,7 +6411,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652223</v>
+        <v>123652202</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6461,10 +6455,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513611</v>
+        <v>513640</v>
       </c>
       <c r="R49" t="n">
-        <v>6733249</v>
+        <v>6733250</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6496,7 +6490,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6506,12 +6500,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6539,7 +6533,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652185</v>
+        <v>123652224</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6583,10 +6577,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513619</v>
+        <v>513610</v>
       </c>
       <c r="R50" t="n">
-        <v>6733240</v>
+        <v>6733242</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6618,7 +6612,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6628,12 +6622,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6661,7 +6655,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652174</v>
+        <v>123652199</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6705,10 +6699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513606</v>
+        <v>513642</v>
       </c>
       <c r="R51" t="n">
-        <v>6733257</v>
+        <v>6733246</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6740,7 +6734,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6750,12 +6744,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6783,10 +6777,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123656503</v>
+        <v>123652168</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6795,35 +6789,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6831,10 +6821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513619</v>
+        <v>513593</v>
       </c>
       <c r="R52" t="n">
-        <v>6733230</v>
+        <v>6733228</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6866,7 +6856,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6876,12 +6866,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6890,6 +6880,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6908,10 +6899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123656500</v>
+        <v>123652206</v>
       </c>
       <c r="B53" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6920,32 +6911,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6953,13 +6943,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513668</v>
+        <v>513623</v>
       </c>
       <c r="R53" t="n">
-        <v>6733244</v>
+        <v>6733237</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6983,22 +6973,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7019,17 +7014,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123650528</v>
+        <v>123652216</v>
       </c>
       <c r="B54" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7038,35 +7033,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7074,10 +7065,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513632</v>
+        <v>513614</v>
       </c>
       <c r="R54" t="n">
-        <v>6733214</v>
+        <v>6733272</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7109,7 +7100,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7119,7 +7110,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7128,6 +7124,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7139,14 +7136,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652201</v>
+        <v>123652163</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -7190,13 +7187,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513640</v>
+        <v>513621</v>
       </c>
       <c r="R55" t="n">
-        <v>6733246</v>
+        <v>6733235</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7225,7 +7222,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7235,12 +7232,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7268,7 +7265,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652200</v>
+        <v>123652188</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -7312,10 +7309,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513638</v>
+        <v>513629</v>
       </c>
       <c r="R56" t="n">
-        <v>6733248</v>
+        <v>6733239</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7347,7 +7344,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7357,12 +7354,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7390,7 +7387,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652204</v>
+        <v>123652184</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7434,10 +7431,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513632</v>
+        <v>513618</v>
       </c>
       <c r="R57" t="n">
-        <v>6733247</v>
+        <v>6733235</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7469,7 +7466,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7479,12 +7476,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7512,7 +7509,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652210</v>
+        <v>123652171</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7556,10 +7553,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513625</v>
+        <v>513608</v>
       </c>
       <c r="R58" t="n">
-        <v>6733251</v>
+        <v>6733238</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7591,7 +7588,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7601,12 +7598,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7634,7 +7631,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652161</v>
+        <v>123652209</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7678,10 +7675,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513597</v>
+        <v>513620</v>
       </c>
       <c r="R59" t="n">
-        <v>6733265</v>
+        <v>6733253</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7713,7 +7710,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7723,12 +7720,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7749,14 +7746,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652208</v>
+        <v>123652207</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -7800,10 +7797,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513626</v>
+        <v>513629</v>
       </c>
       <c r="R60" t="n">
-        <v>6733254</v>
+        <v>6733245</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7835,7 +7832,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7845,7 +7842,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7878,7 +7875,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652189</v>
+        <v>123652169</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -7922,10 +7919,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513629</v>
+        <v>513603</v>
       </c>
       <c r="R61" t="n">
-        <v>6733228</v>
+        <v>6733229</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7957,7 +7954,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7967,12 +7964,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,7 +7997,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652224</v>
+        <v>123652225</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8044,10 +8041,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513610</v>
+        <v>513617</v>
       </c>
       <c r="R62" t="n">
-        <v>6733242</v>
+        <v>6733234</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8079,7 +8076,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,12 +8086,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8122,7 +8119,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652222</v>
+        <v>123652213</v>
       </c>
       <c r="B63" t="n">
         <v>98079</v>
@@ -8166,10 +8163,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513612</v>
+        <v>513617</v>
       </c>
       <c r="R63" t="n">
-        <v>6733260</v>
+        <v>6733269</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8201,7 +8198,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,7 +8208,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8244,7 +8241,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652170</v>
+        <v>123652223</v>
       </c>
       <c r="B64" t="n">
         <v>98079</v>
@@ -8288,10 +8285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513607</v>
+        <v>513611</v>
       </c>
       <c r="R64" t="n">
-        <v>6733239</v>
+        <v>6733249</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8323,7 +8320,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8333,12 +8330,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8366,10 +8363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123650524</v>
+        <v>123652173</v>
       </c>
       <c r="B65" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8378,39 +8375,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8418,10 +8407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513595</v>
+        <v>513600</v>
       </c>
       <c r="R65" t="n">
-        <v>6733257</v>
+        <v>6733258</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8453,7 +8442,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8463,7 +8452,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8472,6 +8466,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8490,10 +8485,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123656504</v>
+        <v>123652217</v>
       </c>
       <c r="B66" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8502,35 +8497,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8538,10 +8529,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513643</v>
+        <v>513612</v>
       </c>
       <c r="R66" t="n">
-        <v>6733240</v>
+        <v>6733277</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8573,7 +8564,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8583,12 +8574,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8597,6 +8588,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8615,7 +8607,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652182</v>
+        <v>123652194</v>
       </c>
       <c r="B67" t="n">
         <v>98079</v>
@@ -8659,10 +8651,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513620</v>
+        <v>513642</v>
       </c>
       <c r="R67" t="n">
-        <v>6733241</v>
+        <v>6733220</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8694,7 +8686,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8704,7 +8696,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8737,7 +8729,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652169</v>
+        <v>123652221</v>
       </c>
       <c r="B68" t="n">
         <v>98079</v>
@@ -8781,10 +8773,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513603</v>
+        <v>513613</v>
       </c>
       <c r="R68" t="n">
-        <v>6733229</v>
+        <v>6733269</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8816,7 +8808,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8826,12 +8818,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8859,10 +8851,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123656499</v>
+        <v>123652192</v>
       </c>
       <c r="B69" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8871,25 +8863,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8903,13 +8895,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513625</v>
+        <v>513630</v>
       </c>
       <c r="R69" t="n">
-        <v>6733311</v>
+        <v>6733221</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8938,7 +8930,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8948,7 +8940,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,7 +8973,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652188</v>
+        <v>123652211</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9020,10 +9017,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513629</v>
+        <v>513625</v>
       </c>
       <c r="R70" t="n">
-        <v>6733239</v>
+        <v>6733258</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +9052,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,12 +9062,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9098,10 +9095,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652175</v>
+        <v>123656502</v>
       </c>
       <c r="B71" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9110,31 +9107,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9142,10 +9143,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513606</v>
+        <v>513623</v>
       </c>
       <c r="R71" t="n">
-        <v>6733254</v>
+        <v>6733240</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9177,7 +9178,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9187,12 +9188,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9201,7 +9202,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652171</v>
+        <v>123652176</v>
       </c>
       <c r="B72" t="n">
         <v>98079</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513608</v>
+        <v>513605</v>
       </c>
       <c r="R72" t="n">
-        <v>6733238</v>
+        <v>6733249</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -9342,7 +9342,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652199</v>
+        <v>123652226</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513642</v>
+        <v>513622</v>
       </c>
       <c r="R73" t="n">
-        <v>6733246</v>
+        <v>6733236</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652221</v>
+        <v>123652182</v>
       </c>
       <c r="B74" t="n">
         <v>98079</v>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513613</v>
+        <v>513620</v>
       </c>
       <c r="R74" t="n">
-        <v>6733269</v>
+        <v>6733241</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123656504</v>
+        <v>123650526</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513643</v>
+        <v>513627</v>
       </c>
       <c r="R6" t="n">
-        <v>6733240</v>
+        <v>6733250</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652205</v>
+        <v>123652226</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513635</v>
+        <v>513622</v>
       </c>
       <c r="R7" t="n">
-        <v>6733245</v>
+        <v>6733236</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652162</v>
+        <v>123652177</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513604</v>
+        <v>513615</v>
       </c>
       <c r="R8" t="n">
-        <v>6733250</v>
+        <v>6733245</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652161</v>
+        <v>123652217</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513597</v>
+        <v>513612</v>
       </c>
       <c r="R9" t="n">
-        <v>6733265</v>
+        <v>6733277</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123656500</v>
+        <v>123652168</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,32 +1658,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,13 +1690,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513668</v>
+        <v>513593</v>
       </c>
       <c r="R10" t="n">
-        <v>6733244</v>
+        <v>6733228</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,22 +1720,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,14 +1761,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652214</v>
+        <v>123652221</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1808,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513615</v>
+        <v>513613</v>
       </c>
       <c r="R11" t="n">
-        <v>6733271</v>
+        <v>6733269</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1853,12 +1857,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,7 +1890,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652191</v>
+        <v>123652174</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1930,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513628</v>
+        <v>513606</v>
       </c>
       <c r="R12" t="n">
-        <v>6733228</v>
+        <v>6733257</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1965,7 +1969,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1979,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2008,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652175</v>
+        <v>123656505</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2020,31 +2024,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2052,10 +2060,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513606</v>
+        <v>513624</v>
       </c>
       <c r="R13" t="n">
-        <v>6733254</v>
+        <v>6733235</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2087,7 +2095,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,12 +2105,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,7 +2119,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2137,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123650528</v>
+        <v>123652190</v>
       </c>
       <c r="B14" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2142,35 +2149,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2178,10 +2181,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513632</v>
+        <v>513627</v>
       </c>
       <c r="R14" t="n">
-        <v>6733214</v>
+        <v>6733227</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2213,7 +2216,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,7 +2226,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2232,6 +2240,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2243,17 +2252,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123656499</v>
+        <v>123652176</v>
       </c>
       <c r="B15" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,25 +2271,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2294,13 +2303,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513625</v>
+        <v>513605</v>
       </c>
       <c r="R15" t="n">
-        <v>6733311</v>
+        <v>6733249</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2338,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,7 +2348,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2367,7 +2381,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652186</v>
+        <v>123652200</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2411,10 +2425,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513623</v>
+        <v>513638</v>
       </c>
       <c r="R16" t="n">
-        <v>6733238</v>
+        <v>6733248</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2446,7 +2460,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2456,12 +2470,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,7 +2503,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652170</v>
+        <v>123652185</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2533,10 +2547,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513607</v>
+        <v>513619</v>
       </c>
       <c r="R17" t="n">
-        <v>6733239</v>
+        <v>6733240</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2568,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2592,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2611,7 +2625,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652201</v>
+        <v>123652164</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2655,10 +2669,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513640</v>
+        <v>513617</v>
       </c>
       <c r="R18" t="n">
-        <v>6733246</v>
+        <v>6733240</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2690,7 +2704,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,12 +2714,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652195</v>
+        <v>123656502</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2745,31 +2759,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2777,10 +2795,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513645</v>
+        <v>513623</v>
       </c>
       <c r="R19" t="n">
-        <v>6733241</v>
+        <v>6733240</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2812,7 +2830,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2822,12 +2840,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2836,7 +2854,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2855,7 +2872,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652193</v>
+        <v>123652186</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2899,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513631</v>
+        <v>513623</v>
       </c>
       <c r="R20" t="n">
-        <v>6733221</v>
+        <v>6733238</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2934,7 +2951,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2944,12 +2961,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,7 +2994,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652177</v>
+        <v>123652182</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3021,10 +3038,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513615</v>
+        <v>513620</v>
       </c>
       <c r="R21" t="n">
-        <v>6733245</v>
+        <v>6733241</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3056,7 +3073,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3066,7 +3083,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3099,7 +3116,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652220</v>
+        <v>123652162</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3143,10 +3160,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513609</v>
+        <v>513604</v>
       </c>
       <c r="R22" t="n">
-        <v>6733266</v>
+        <v>6733250</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3178,7 +3195,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3188,12 +3205,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,7 +3238,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652185</v>
+        <v>123652197</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3265,10 +3282,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513619</v>
+        <v>513644</v>
       </c>
       <c r="R23" t="n">
-        <v>6733240</v>
+        <v>6733242</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3300,7 +3317,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3310,12 +3327,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3343,7 +3360,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652180</v>
+        <v>123652213</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3387,10 +3404,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513623</v>
+        <v>513617</v>
       </c>
       <c r="R24" t="n">
-        <v>6733239</v>
+        <v>6733269</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3422,7 +3439,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3432,12 +3449,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3465,7 +3482,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652212</v>
+        <v>123652225</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3509,10 +3526,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513623</v>
+        <v>513617</v>
       </c>
       <c r="R25" t="n">
-        <v>6733260</v>
+        <v>6733234</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3544,7 +3561,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3554,12 +3571,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3587,7 +3604,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652218</v>
+        <v>123652208</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3631,10 +3648,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513613</v>
+        <v>513626</v>
       </c>
       <c r="R26" t="n">
-        <v>6733273</v>
+        <v>6733254</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3666,7 +3683,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3676,12 +3693,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3709,7 +3726,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652178</v>
+        <v>123652187</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3753,10 +3770,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513605</v>
+        <v>513627</v>
       </c>
       <c r="R27" t="n">
-        <v>6733242</v>
+        <v>6733241</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3788,7 +3805,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3798,7 +3815,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3831,7 +3848,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652208</v>
+        <v>123652212</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3875,10 +3892,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513626</v>
+        <v>513623</v>
       </c>
       <c r="R28" t="n">
-        <v>6733254</v>
+        <v>6733260</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3910,7 +3927,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3920,12 +3937,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3953,7 +3970,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652197</v>
+        <v>123652216</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3997,10 +4014,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513644</v>
+        <v>513614</v>
       </c>
       <c r="R29" t="n">
-        <v>6733242</v>
+        <v>6733272</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4032,7 +4049,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4042,12 +4059,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4075,7 +4092,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652179</v>
+        <v>123652173</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4119,10 +4136,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513611</v>
+        <v>513600</v>
       </c>
       <c r="R30" t="n">
-        <v>6733236</v>
+        <v>6733258</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4154,7 +4171,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4164,12 +4181,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4197,7 +4214,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652189</v>
+        <v>123652204</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4241,10 +4258,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513629</v>
+        <v>513632</v>
       </c>
       <c r="R31" t="n">
-        <v>6733228</v>
+        <v>6733247</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4276,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4286,12 +4303,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4319,7 +4336,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652181</v>
+        <v>123652189</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4363,10 +4380,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513619</v>
+        <v>513629</v>
       </c>
       <c r="R32" t="n">
-        <v>6733234</v>
+        <v>6733228</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4398,7 +4415,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4408,12 +4425,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4441,10 +4458,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123650523</v>
+        <v>123652178</v>
       </c>
       <c r="B33" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4453,39 +4470,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4493,10 +4502,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513585</v>
+        <v>513605</v>
       </c>
       <c r="R33" t="n">
-        <v>6733249</v>
+        <v>6733242</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4528,7 +4537,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4538,12 +4547,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,6 +4561,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4570,10 +4580,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123650526</v>
+        <v>123656503</v>
       </c>
       <c r="B34" t="n">
-        <v>56692</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4586,16 +4596,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4608,7 +4618,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4618,10 +4628,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513627</v>
+        <v>513619</v>
       </c>
       <c r="R34" t="n">
-        <v>6733250</v>
+        <v>6733230</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4653,7 +4663,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4663,12 +4673,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4695,10 +4705,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123656503</v>
+        <v>123652205</v>
       </c>
       <c r="B35" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4707,35 +4717,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4743,10 +4749,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513619</v>
+        <v>513635</v>
       </c>
       <c r="R35" t="n">
-        <v>6733230</v>
+        <v>6733245</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4778,7 +4784,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4788,12 +4794,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4802,6 +4808,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4820,7 +4827,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652187</v>
+        <v>123652223</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4864,10 +4871,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513627</v>
+        <v>513611</v>
       </c>
       <c r="R36" t="n">
-        <v>6733241</v>
+        <v>6733249</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4899,7 +4906,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4909,12 +4916,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4942,7 +4949,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652190</v>
+        <v>123652199</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4986,10 +4993,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513627</v>
+        <v>513642</v>
       </c>
       <c r="R37" t="n">
-        <v>6733227</v>
+        <v>6733246</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5021,7 +5028,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5031,12 +5038,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5064,7 +5071,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652200</v>
+        <v>123652201</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5108,10 +5115,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513638</v>
+        <v>513640</v>
       </c>
       <c r="R38" t="n">
-        <v>6733248</v>
+        <v>6733246</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5186,7 +5193,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652174</v>
+        <v>123652192</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5230,10 +5237,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513606</v>
+        <v>513630</v>
       </c>
       <c r="R39" t="n">
-        <v>6733257</v>
+        <v>6733221</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5265,7 +5272,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5275,7 +5282,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5308,7 +5315,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652219</v>
+        <v>123652220</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5355,7 +5362,7 @@
         <v>513609</v>
       </c>
       <c r="R40" t="n">
-        <v>6733267</v>
+        <v>6733266</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5402,7 +5409,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5430,7 +5437,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652204</v>
+        <v>123652209</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5474,10 +5481,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513632</v>
+        <v>513620</v>
       </c>
       <c r="R41" t="n">
-        <v>6733247</v>
+        <v>6733253</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5509,7 +5516,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5519,7 +5526,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5552,7 +5559,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652210</v>
+        <v>123652180</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5596,10 +5603,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513625</v>
+        <v>513623</v>
       </c>
       <c r="R42" t="n">
-        <v>6733251</v>
+        <v>6733239</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5631,7 +5638,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5641,12 +5648,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,10 +5681,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123650524</v>
+        <v>123652194</v>
       </c>
       <c r="B43" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5686,39 +5693,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5726,10 +5725,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513595</v>
+        <v>513642</v>
       </c>
       <c r="R43" t="n">
-        <v>6733257</v>
+        <v>6733220</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5761,7 +5760,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5771,7 +5770,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5780,6 +5784,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5798,10 +5803,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123656505</v>
+        <v>123650528</v>
       </c>
       <c r="B44" t="n">
-        <v>57507</v>
+        <v>56692</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5814,16 +5819,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5836,7 +5841,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5846,10 +5851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513624</v>
+        <v>513632</v>
       </c>
       <c r="R44" t="n">
-        <v>6733235</v>
+        <v>6733214</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5881,7 +5886,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5891,12 +5896,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5916,14 +5916,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652222</v>
+        <v>123652202</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513612</v>
+        <v>513640</v>
       </c>
       <c r="R45" t="n">
-        <v>6733260</v>
+        <v>6733250</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6045,7 +6045,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652164</v>
+        <v>123652179</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513617</v>
+        <v>513611</v>
       </c>
       <c r="R46" t="n">
-        <v>6733240</v>
+        <v>6733236</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6167,7 +6167,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652160</v>
+        <v>123652203</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513608</v>
+        <v>513639</v>
       </c>
       <c r="R47" t="n">
-        <v>6733246</v>
+        <v>6733252</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,7 +6289,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652203</v>
+        <v>123652191</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513639</v>
+        <v>513628</v>
       </c>
       <c r="R48" t="n">
-        <v>6733252</v>
+        <v>6733228</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6411,10 +6411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652202</v>
+        <v>123656504</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6423,31 +6423,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6455,10 +6459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513640</v>
+        <v>513643</v>
       </c>
       <c r="R49" t="n">
-        <v>6733250</v>
+        <v>6733240</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6490,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,12 +6504,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6514,7 +6518,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6533,7 +6536,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652224</v>
+        <v>123652222</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6577,10 +6580,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513610</v>
+        <v>513612</v>
       </c>
       <c r="R50" t="n">
-        <v>6733242</v>
+        <v>6733260</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6612,7 +6615,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6622,12 +6625,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6655,7 +6658,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652199</v>
+        <v>123652210</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6699,10 +6702,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513642</v>
+        <v>513625</v>
       </c>
       <c r="R51" t="n">
-        <v>6733246</v>
+        <v>6733251</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6734,7 +6737,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6744,12 +6747,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6777,7 +6780,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652168</v>
+        <v>123652211</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -6821,10 +6824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513593</v>
+        <v>513625</v>
       </c>
       <c r="R52" t="n">
-        <v>6733228</v>
+        <v>6733258</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6856,7 +6859,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6866,12 +6869,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6899,7 +6902,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652206</v>
+        <v>123652175</v>
       </c>
       <c r="B53" t="n">
         <v>98079</v>
@@ -6943,10 +6946,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513623</v>
+        <v>513606</v>
       </c>
       <c r="R53" t="n">
-        <v>6733237</v>
+        <v>6733254</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6978,7 +6981,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6988,12 +6991,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7021,10 +7024,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652216</v>
+        <v>123656499</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7033,25 +7036,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7065,13 +7068,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513614</v>
+        <v>513625</v>
       </c>
       <c r="R54" t="n">
-        <v>6733272</v>
+        <v>6733311</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7100,7 +7103,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7110,12 +7113,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7265,7 +7263,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652188</v>
+        <v>123652169</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -7309,10 +7307,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513629</v>
+        <v>513603</v>
       </c>
       <c r="R56" t="n">
-        <v>6733239</v>
+        <v>6733229</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7344,7 +7342,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7354,7 +7352,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7387,7 +7385,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652184</v>
+        <v>123652161</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7431,10 +7429,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513618</v>
+        <v>513597</v>
       </c>
       <c r="R57" t="n">
-        <v>6733235</v>
+        <v>6733265</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7466,7 +7464,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7476,12 +7474,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7502,14 +7500,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652171</v>
+        <v>123652170</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7553,10 +7551,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513608</v>
+        <v>513607</v>
       </c>
       <c r="R58" t="n">
-        <v>6733238</v>
+        <v>6733239</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7588,7 +7586,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7598,7 +7596,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7631,7 +7629,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652209</v>
+        <v>123652160</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7675,10 +7673,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513620</v>
+        <v>513608</v>
       </c>
       <c r="R59" t="n">
-        <v>6733253</v>
+        <v>6733246</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7710,7 +7708,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7720,12 +7718,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7753,10 +7751,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652207</v>
+        <v>123656500</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7765,31 +7763,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7797,13 +7796,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513629</v>
+        <v>513668</v>
       </c>
       <c r="R60" t="n">
-        <v>6733245</v>
+        <v>6733244</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7827,27 +7826,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7868,17 +7862,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652169</v>
+        <v>123650523</v>
       </c>
       <c r="B61" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7887,31 +7881,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7919,10 +7921,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513603</v>
+        <v>513585</v>
       </c>
       <c r="R61" t="n">
-        <v>6733229</v>
+        <v>6733249</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7954,7 +7956,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7964,12 +7966,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7978,7 +7980,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7997,7 +7998,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652225</v>
+        <v>123652219</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8041,10 +8042,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513617</v>
+        <v>513609</v>
       </c>
       <c r="R62" t="n">
-        <v>6733234</v>
+        <v>6733267</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8076,7 +8077,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8086,12 +8087,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8119,7 +8120,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652213</v>
+        <v>123652195</v>
       </c>
       <c r="B63" t="n">
         <v>98079</v>
@@ -8163,10 +8164,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513617</v>
+        <v>513645</v>
       </c>
       <c r="R63" t="n">
-        <v>6733269</v>
+        <v>6733241</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8198,7 +8199,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8208,12 +8209,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8241,7 +8242,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652223</v>
+        <v>123652171</v>
       </c>
       <c r="B64" t="n">
         <v>98079</v>
@@ -8285,10 +8286,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513611</v>
+        <v>513608</v>
       </c>
       <c r="R64" t="n">
-        <v>6733249</v>
+        <v>6733238</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8320,7 +8321,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8330,12 +8331,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8363,7 +8364,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652173</v>
+        <v>123652207</v>
       </c>
       <c r="B65" t="n">
         <v>98079</v>
@@ -8407,10 +8408,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513600</v>
+        <v>513629</v>
       </c>
       <c r="R65" t="n">
-        <v>6733258</v>
+        <v>6733245</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8442,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8452,12 +8453,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8485,7 +8486,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652217</v>
+        <v>123652214</v>
       </c>
       <c r="B66" t="n">
         <v>98079</v>
@@ -8529,10 +8530,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513612</v>
+        <v>513615</v>
       </c>
       <c r="R66" t="n">
-        <v>6733277</v>
+        <v>6733271</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8564,7 +8565,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8574,12 +8575,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8607,7 +8608,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652194</v>
+        <v>123652224</v>
       </c>
       <c r="B67" t="n">
         <v>98079</v>
@@ -8651,10 +8652,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513642</v>
+        <v>513610</v>
       </c>
       <c r="R67" t="n">
-        <v>6733220</v>
+        <v>6733242</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8686,7 +8687,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8696,12 +8697,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8729,10 +8730,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652221</v>
+        <v>123650524</v>
       </c>
       <c r="B68" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8741,31 +8742,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8773,10 +8782,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513613</v>
+        <v>513595</v>
       </c>
       <c r="R68" t="n">
-        <v>6733269</v>
+        <v>6733257</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8808,7 +8817,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8818,12 +8827,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8832,7 +8836,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8851,7 +8854,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652192</v>
+        <v>123652188</v>
       </c>
       <c r="B69" t="n">
         <v>98079</v>
@@ -8895,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513630</v>
+        <v>513629</v>
       </c>
       <c r="R69" t="n">
-        <v>6733221</v>
+        <v>6733239</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8930,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8940,7 +8943,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8973,7 +8976,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652211</v>
+        <v>123652184</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9017,10 +9020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513625</v>
+        <v>513618</v>
       </c>
       <c r="R70" t="n">
-        <v>6733258</v>
+        <v>6733235</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9052,7 +9055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9062,12 +9065,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9095,10 +9098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123656502</v>
+        <v>123652206</v>
       </c>
       <c r="B71" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9107,35 +9110,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9146,7 +9145,7 @@
         <v>513623</v>
       </c>
       <c r="R71" t="n">
-        <v>6733240</v>
+        <v>6733237</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9178,7 +9177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9188,12 +9187,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9202,6 +9201,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652176</v>
+        <v>123652193</v>
       </c>
       <c r="B72" t="n">
         <v>98079</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513605</v>
+        <v>513631</v>
       </c>
       <c r="R72" t="n">
-        <v>6733249</v>
+        <v>6733221</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9342,7 +9342,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652226</v>
+        <v>123652181</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513622</v>
+        <v>513619</v>
       </c>
       <c r="R73" t="n">
-        <v>6733236</v>
+        <v>6733234</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652182</v>
+        <v>123652218</v>
       </c>
       <c r="B74" t="n">
         <v>98079</v>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513620</v>
+        <v>513613</v>
       </c>
       <c r="R74" t="n">
-        <v>6733241</v>
+        <v>6733273</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123650526</v>
+        <v>123652226</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,35 +1167,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1203,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513627</v>
+        <v>513622</v>
       </c>
       <c r="R6" t="n">
-        <v>6733250</v>
+        <v>6733236</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,6 +1258,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1280,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652226</v>
+        <v>123652177</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1324,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513622</v>
+        <v>513615</v>
       </c>
       <c r="R7" t="n">
-        <v>6733236</v>
+        <v>6733245</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1359,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1399,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652177</v>
+        <v>123652217</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1446,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513615</v>
+        <v>513612</v>
       </c>
       <c r="R8" t="n">
-        <v>6733245</v>
+        <v>6733277</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1481,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,7 +1521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652217</v>
+        <v>123652168</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1568,10 +1565,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513612</v>
+        <v>513593</v>
       </c>
       <c r="R9" t="n">
-        <v>6733277</v>
+        <v>6733228</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1603,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,7 +1643,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652168</v>
+        <v>123652221</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1690,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513593</v>
+        <v>513613</v>
       </c>
       <c r="R10" t="n">
-        <v>6733228</v>
+        <v>6733269</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1725,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,12 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,7 +1765,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652221</v>
+        <v>123652174</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1812,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513613</v>
+        <v>513606</v>
       </c>
       <c r="R11" t="n">
-        <v>6733269</v>
+        <v>6733257</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1847,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,12 +1854,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652174</v>
+        <v>123650526</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,31 +1899,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1934,10 +1935,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513606</v>
+        <v>513627</v>
       </c>
       <c r="R12" t="n">
-        <v>6733257</v>
+        <v>6733250</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1969,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1979,12 +1980,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,7 +1994,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123656505</v>
+        <v>123652190</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,35 +2024,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2060,10 +2056,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513624</v>
+        <v>513627</v>
       </c>
       <c r="R13" t="n">
-        <v>6733235</v>
+        <v>6733227</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2095,7 +2091,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2105,12 +2101,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,6 +2115,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2137,7 +2134,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652190</v>
+        <v>123652176</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2181,10 +2178,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513627</v>
+        <v>513605</v>
       </c>
       <c r="R14" t="n">
-        <v>6733227</v>
+        <v>6733249</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2216,7 +2213,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2226,7 +2223,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2259,7 +2256,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652176</v>
+        <v>123652200</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2303,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513605</v>
+        <v>513638</v>
       </c>
       <c r="R15" t="n">
-        <v>6733249</v>
+        <v>6733248</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2338,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2348,12 +2345,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,7 +2378,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652200</v>
+        <v>123652185</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2425,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513638</v>
+        <v>513619</v>
       </c>
       <c r="R16" t="n">
-        <v>6733248</v>
+        <v>6733240</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2460,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2470,12 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,7 +2500,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652185</v>
+        <v>123652164</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2547,7 +2544,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513619</v>
+        <v>513617</v>
       </c>
       <c r="R17" t="n">
         <v>6733240</v>
@@ -2582,7 +2579,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,7 +2589,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2625,10 +2622,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652164</v>
+        <v>123656505</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2637,31 +2634,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2669,10 +2670,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513617</v>
+        <v>513624</v>
       </c>
       <c r="R18" t="n">
-        <v>6733240</v>
+        <v>6733235</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2704,7 +2705,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2714,12 +2715,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,7 +2729,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652189</v>
+        <v>123656503</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4348,31 +4348,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4380,10 +4384,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513629</v>
+        <v>513619</v>
       </c>
       <c r="R32" t="n">
-        <v>6733228</v>
+        <v>6733230</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4425,12 +4429,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4439,7 +4443,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4458,7 +4461,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652178</v>
+        <v>123652189</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4502,10 +4505,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513605</v>
+        <v>513629</v>
       </c>
       <c r="R33" t="n">
-        <v>6733242</v>
+        <v>6733228</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4537,7 +4540,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4547,12 +4550,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4580,10 +4583,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123656503</v>
+        <v>123652178</v>
       </c>
       <c r="B34" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4592,35 +4595,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4628,10 +4627,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513619</v>
+        <v>513605</v>
       </c>
       <c r="R34" t="n">
-        <v>6733230</v>
+        <v>6733242</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4663,7 +4662,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4673,12 +4672,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4687,6 +4686,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -6411,10 +6411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123656504</v>
+        <v>123652222</v>
       </c>
       <c r="B49" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6423,35 +6423,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6459,10 +6455,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513643</v>
+        <v>513612</v>
       </c>
       <c r="R49" t="n">
-        <v>6733240</v>
+        <v>6733260</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6494,7 +6490,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,12 +6500,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6518,6 +6514,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6536,7 +6533,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652222</v>
+        <v>123652210</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6580,10 +6577,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513612</v>
+        <v>513625</v>
       </c>
       <c r="R50" t="n">
-        <v>6733260</v>
+        <v>6733251</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6615,7 +6612,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6625,12 +6622,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6658,7 +6655,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652210</v>
+        <v>123652211</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6705,7 +6702,7 @@
         <v>513625</v>
       </c>
       <c r="R51" t="n">
-        <v>6733251</v>
+        <v>6733258</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6737,7 +6734,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6747,12 +6744,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6780,7 +6777,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652211</v>
+        <v>123652175</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -6824,10 +6821,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513625</v>
+        <v>513606</v>
       </c>
       <c r="R52" t="n">
-        <v>6733258</v>
+        <v>6733254</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6859,7 +6856,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6869,12 +6866,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6902,10 +6899,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652175</v>
+        <v>123656504</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6914,31 +6911,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6946,10 +6947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513606</v>
+        <v>513643</v>
       </c>
       <c r="R53" t="n">
-        <v>6733254</v>
+        <v>6733240</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6981,7 +6982,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6991,12 +6992,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7005,7 +7006,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -8364,10 +8364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652207</v>
+        <v>123650524</v>
       </c>
       <c r="B65" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,31 +8376,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8408,10 +8416,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513629</v>
+        <v>513595</v>
       </c>
       <c r="R65" t="n">
-        <v>6733245</v>
+        <v>6733257</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8443,7 +8451,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,12 +8461,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8467,7 +8470,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8486,7 +8488,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652214</v>
+        <v>123652207</v>
       </c>
       <c r="B66" t="n">
         <v>98079</v>
@@ -8530,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513615</v>
+        <v>513629</v>
       </c>
       <c r="R66" t="n">
-        <v>6733271</v>
+        <v>6733245</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8565,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8575,12 +8577,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8608,7 +8610,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652224</v>
+        <v>123652214</v>
       </c>
       <c r="B67" t="n">
         <v>98079</v>
@@ -8652,10 +8654,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513610</v>
+        <v>513615</v>
       </c>
       <c r="R67" t="n">
-        <v>6733242</v>
+        <v>6733271</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8687,7 +8689,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8697,12 +8699,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8730,10 +8732,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123650524</v>
+        <v>123652224</v>
       </c>
       <c r="B68" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8742,39 +8744,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8782,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513595</v>
+        <v>513610</v>
       </c>
       <c r="R68" t="n">
-        <v>6733257</v>
+        <v>6733242</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8817,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8827,7 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,6 +8835,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123652226</v>
+        <v>123652188</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513622</v>
+        <v>513629</v>
       </c>
       <c r="R6" t="n">
-        <v>6733236</v>
+        <v>6733239</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652177</v>
+        <v>123652202</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513615</v>
+        <v>513640</v>
       </c>
       <c r="R7" t="n">
-        <v>6733245</v>
+        <v>6733250</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652217</v>
+        <v>123652162</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513612</v>
+        <v>513604</v>
       </c>
       <c r="R8" t="n">
-        <v>6733277</v>
+        <v>6733250</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652168</v>
+        <v>123650526</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,31 +1533,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1565,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513593</v>
+        <v>513627</v>
       </c>
       <c r="R9" t="n">
-        <v>6733228</v>
+        <v>6733250</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1600,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1614,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,7 +1628,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1643,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652221</v>
+        <v>123656500</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,31 +1658,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1687,13 +1691,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513613</v>
+        <v>513668</v>
       </c>
       <c r="R10" t="n">
-        <v>6733269</v>
+        <v>6733244</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,27 +1721,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,17 +1757,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123652174</v>
+        <v>123650524</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1777,31 +1776,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1809,7 +1816,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513606</v>
+        <v>513595</v>
       </c>
       <c r="R11" t="n">
         <v>6733257</v>
@@ -1844,7 +1851,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,12 +1861,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,7 +1870,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1887,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123650526</v>
+        <v>123652222</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,35 +1900,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1935,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513627</v>
+        <v>513612</v>
       </c>
       <c r="R12" t="n">
-        <v>6733250</v>
+        <v>6733260</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1970,7 +1967,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,12 +1977,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,6 +1991,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2012,7 +2010,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652190</v>
+        <v>123652168</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -2056,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513627</v>
+        <v>513593</v>
       </c>
       <c r="R13" t="n">
-        <v>6733227</v>
+        <v>6733228</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2091,7 +2089,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,7 +2099,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2134,7 +2132,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123652176</v>
+        <v>123652225</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2178,10 +2176,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513605</v>
+        <v>513617</v>
       </c>
       <c r="R14" t="n">
-        <v>6733249</v>
+        <v>6733234</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2213,7 +2211,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2223,12 +2221,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,7 +2254,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652200</v>
+        <v>123652180</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2300,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513638</v>
+        <v>513623</v>
       </c>
       <c r="R15" t="n">
-        <v>6733248</v>
+        <v>6733239</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2335,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,12 +2343,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2378,7 +2376,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652185</v>
+        <v>123652216</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2422,10 +2420,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513619</v>
+        <v>513614</v>
       </c>
       <c r="R16" t="n">
-        <v>6733240</v>
+        <v>6733272</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2457,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2465,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,7 +2498,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652164</v>
+        <v>123652226</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2544,10 +2542,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513617</v>
+        <v>513622</v>
       </c>
       <c r="R17" t="n">
-        <v>6733240</v>
+        <v>6733236</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2579,7 +2577,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2589,12 +2587,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,10 +2620,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123656505</v>
+        <v>123652179</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2634,35 +2632,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2670,10 +2664,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513624</v>
+        <v>513611</v>
       </c>
       <c r="R18" t="n">
-        <v>6733235</v>
+        <v>6733236</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2705,7 +2699,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2715,12 +2709,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,6 +2723,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2747,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123656502</v>
+        <v>123652195</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2759,35 +2754,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2795,10 +2786,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513623</v>
+        <v>513645</v>
       </c>
       <c r="R19" t="n">
-        <v>6733240</v>
+        <v>6733241</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2830,7 +2821,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2840,12 +2831,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,6 +2845,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2872,7 +2864,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652186</v>
+        <v>123652223</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2916,10 +2908,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513623</v>
+        <v>513611</v>
       </c>
       <c r="R20" t="n">
-        <v>6733238</v>
+        <v>6733249</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2951,7 +2943,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2961,12 +2953,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2994,7 +2986,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652182</v>
+        <v>123652184</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3038,10 +3030,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513620</v>
+        <v>513618</v>
       </c>
       <c r="R21" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3073,7 +3065,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3083,7 +3075,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3116,7 +3108,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652162</v>
+        <v>123652173</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3160,10 +3152,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513604</v>
+        <v>513600</v>
       </c>
       <c r="R22" t="n">
-        <v>6733250</v>
+        <v>6733258</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3195,7 +3187,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3205,7 +3197,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3238,10 +3230,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652197</v>
+        <v>123656502</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3250,31 +3242,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3282,10 +3278,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513644</v>
+        <v>513623</v>
       </c>
       <c r="R23" t="n">
-        <v>6733242</v>
+        <v>6733240</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3317,7 +3313,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3327,12 +3323,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,7 +3337,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3360,10 +3355,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652213</v>
+        <v>123656503</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3372,31 +3367,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3404,10 +3403,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513617</v>
+        <v>513619</v>
       </c>
       <c r="R24" t="n">
-        <v>6733269</v>
+        <v>6733230</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3439,7 +3438,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3449,12 +3448,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3463,7 +3462,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3482,7 +3480,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123652225</v>
+        <v>123652204</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3526,10 +3524,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513617</v>
+        <v>513632</v>
       </c>
       <c r="R25" t="n">
-        <v>6733234</v>
+        <v>6733247</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3561,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3571,7 +3569,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3604,7 +3602,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123652208</v>
+        <v>123652181</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3648,10 +3646,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513626</v>
+        <v>513619</v>
       </c>
       <c r="R26" t="n">
-        <v>6733254</v>
+        <v>6733234</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3683,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3693,12 +3691,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3726,10 +3724,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652187</v>
+        <v>123656505</v>
       </c>
       <c r="B27" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3738,31 +3736,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3770,10 +3772,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513627</v>
+        <v>513624</v>
       </c>
       <c r="R27" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3805,7 +3807,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3815,12 +3817,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,7 +3831,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3848,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652212</v>
+        <v>123656504</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3860,31 +3861,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3892,10 +3897,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513623</v>
+        <v>513643</v>
       </c>
       <c r="R28" t="n">
-        <v>6733260</v>
+        <v>6733240</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3927,7 +3932,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3937,12 +3942,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,7 +3956,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3970,7 +3974,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652216</v>
+        <v>123652187</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -4014,10 +4018,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513614</v>
+        <v>513627</v>
       </c>
       <c r="R29" t="n">
-        <v>6733272</v>
+        <v>6733241</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4049,7 +4053,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4059,12 +4063,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4092,7 +4096,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652173</v>
+        <v>123652220</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4136,10 +4140,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513600</v>
+        <v>513609</v>
       </c>
       <c r="R30" t="n">
-        <v>6733258</v>
+        <v>6733266</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4171,7 +4175,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4181,12 +4185,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4214,7 +4218,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123652204</v>
+        <v>123652218</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4258,10 +4262,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513632</v>
+        <v>513613</v>
       </c>
       <c r="R31" t="n">
-        <v>6733247</v>
+        <v>6733273</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4293,7 +4297,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4336,10 +4340,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123656503</v>
+        <v>123652191</v>
       </c>
       <c r="B32" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4348,35 +4352,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513619</v>
+        <v>513628</v>
       </c>
       <c r="R32" t="n">
-        <v>6733230</v>
+        <v>6733228</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4443,6 +4443,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4461,10 +4462,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123652189</v>
+        <v>123656499</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4473,25 +4474,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4505,13 +4506,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513629</v>
+        <v>513625</v>
       </c>
       <c r="R33" t="n">
-        <v>6733228</v>
+        <v>6733311</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4540,7 +4541,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4550,12 +4551,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4583,7 +4579,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652178</v>
+        <v>123652205</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4627,10 +4623,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513605</v>
+        <v>513635</v>
       </c>
       <c r="R34" t="n">
-        <v>6733242</v>
+        <v>6733245</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4662,7 +4658,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4672,12 +4668,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4705,7 +4701,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652205</v>
+        <v>123652186</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4749,10 +4745,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513635</v>
+        <v>513623</v>
       </c>
       <c r="R35" t="n">
-        <v>6733245</v>
+        <v>6733238</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4784,7 +4780,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4794,12 +4790,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4827,7 +4823,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123652223</v>
+        <v>123652169</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4871,10 +4867,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513611</v>
+        <v>513603</v>
       </c>
       <c r="R36" t="n">
-        <v>6733249</v>
+        <v>6733229</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4906,7 +4902,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4916,12 +4912,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4949,10 +4945,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652199</v>
+        <v>123650523</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4961,31 +4957,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4993,10 +4997,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513642</v>
+        <v>513585</v>
       </c>
       <c r="R37" t="n">
-        <v>6733246</v>
+        <v>6733249</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5038,12 +5042,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5052,7 +5056,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5071,7 +5074,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652201</v>
+        <v>123652209</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5115,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513640</v>
+        <v>513620</v>
       </c>
       <c r="R38" t="n">
-        <v>6733246</v>
+        <v>6733253</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5150,7 +5153,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5160,7 +5163,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5193,7 +5196,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652192</v>
+        <v>123652207</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5237,10 +5240,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513630</v>
+        <v>513629</v>
       </c>
       <c r="R39" t="n">
-        <v>6733221</v>
+        <v>6733245</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5272,7 +5275,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5282,12 +5285,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5315,7 +5318,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652220</v>
+        <v>123652189</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5359,10 +5362,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513609</v>
+        <v>513629</v>
       </c>
       <c r="R40" t="n">
-        <v>6733266</v>
+        <v>6733228</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5394,7 +5397,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5404,12 +5407,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5437,7 +5440,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652209</v>
+        <v>123652201</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5481,10 +5484,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513620</v>
+        <v>513640</v>
       </c>
       <c r="R41" t="n">
-        <v>6733253</v>
+        <v>6733246</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5516,7 +5519,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5526,7 +5529,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5559,7 +5562,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652180</v>
+        <v>123652213</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5603,10 +5606,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513623</v>
+        <v>513617</v>
       </c>
       <c r="R42" t="n">
-        <v>6733239</v>
+        <v>6733269</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5638,7 +5641,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5648,12 +5651,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5681,7 +5684,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652194</v>
+        <v>123652200</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5725,10 +5728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513642</v>
+        <v>513638</v>
       </c>
       <c r="R43" t="n">
-        <v>6733220</v>
+        <v>6733248</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5760,7 +5763,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5770,12 +5773,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5803,10 +5806,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123650528</v>
+        <v>123652160</v>
       </c>
       <c r="B44" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5815,35 +5818,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5851,10 +5850,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513632</v>
+        <v>513608</v>
       </c>
       <c r="R44" t="n">
-        <v>6733214</v>
+        <v>6733246</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5886,7 +5885,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5896,7 +5895,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5905,6 +5909,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5916,14 +5921,14 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652202</v>
+        <v>123652163</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5967,13 +5972,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513640</v>
+        <v>513621</v>
       </c>
       <c r="R45" t="n">
-        <v>6733250</v>
+        <v>6733235</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6002,7 +6007,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6012,12 +6017,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6045,7 +6050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652179</v>
+        <v>123652177</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6089,10 +6094,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513611</v>
+        <v>513615</v>
       </c>
       <c r="R46" t="n">
-        <v>6733236</v>
+        <v>6733245</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6124,7 +6129,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6134,12 +6139,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6167,7 +6172,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123652203</v>
+        <v>123652192</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6211,10 +6216,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513639</v>
+        <v>513630</v>
       </c>
       <c r="R47" t="n">
-        <v>6733252</v>
+        <v>6733221</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6246,7 +6251,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6256,12 +6261,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,7 +6294,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652191</v>
+        <v>123652194</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6333,10 +6338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513628</v>
+        <v>513642</v>
       </c>
       <c r="R48" t="n">
-        <v>6733228</v>
+        <v>6733220</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6368,7 +6373,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,7 +6383,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6411,7 +6416,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652222</v>
+        <v>123652221</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6455,10 +6460,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513612</v>
+        <v>513613</v>
       </c>
       <c r="R49" t="n">
-        <v>6733260</v>
+        <v>6733269</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6490,7 +6495,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,7 +6505,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6533,7 +6538,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652210</v>
+        <v>123652206</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6577,10 +6582,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513625</v>
+        <v>513623</v>
       </c>
       <c r="R50" t="n">
-        <v>6733251</v>
+        <v>6733237</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6612,7 +6617,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6622,12 +6627,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6655,7 +6660,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652211</v>
+        <v>123652224</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6699,10 +6704,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513625</v>
+        <v>513610</v>
       </c>
       <c r="R51" t="n">
-        <v>6733258</v>
+        <v>6733242</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6734,7 +6739,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6744,12 +6749,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6777,7 +6782,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652175</v>
+        <v>123652219</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -6821,10 +6826,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513606</v>
+        <v>513609</v>
       </c>
       <c r="R52" t="n">
-        <v>6733254</v>
+        <v>6733267</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6856,7 +6861,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6866,12 +6871,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6899,10 +6904,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123656504</v>
+        <v>123652193</v>
       </c>
       <c r="B53" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6911,35 +6916,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6947,10 +6948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513643</v>
+        <v>513631</v>
       </c>
       <c r="R53" t="n">
-        <v>6733240</v>
+        <v>6733221</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6982,7 +6983,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6992,12 +6993,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7006,6 +7007,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7024,10 +7026,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123656499</v>
+        <v>123652217</v>
       </c>
       <c r="B54" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7036,25 +7038,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7068,13 +7070,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513625</v>
+        <v>513612</v>
       </c>
       <c r="R54" t="n">
-        <v>6733311</v>
+        <v>6733277</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7103,7 +7105,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7113,7 +7115,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7141,7 +7148,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652163</v>
+        <v>123652214</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -7185,13 +7192,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513621</v>
+        <v>513615</v>
       </c>
       <c r="R55" t="n">
-        <v>6733235</v>
+        <v>6733271</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7220,7 +7227,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7230,12 +7237,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7263,7 +7270,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652169</v>
+        <v>123652171</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -7307,10 +7314,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513603</v>
+        <v>513608</v>
       </c>
       <c r="R56" t="n">
-        <v>6733229</v>
+        <v>6733238</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7342,7 +7349,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7352,7 +7359,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7385,10 +7392,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652161</v>
+        <v>123650528</v>
       </c>
       <c r="B57" t="n">
-        <v>98079</v>
+        <v>56692</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7397,31 +7404,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7429,10 +7440,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513597</v>
+        <v>513632</v>
       </c>
       <c r="R57" t="n">
-        <v>6733265</v>
+        <v>6733214</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7464,7 +7475,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7474,12 +7485,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:07</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7488,7 +7494,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7507,7 +7512,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123652170</v>
+        <v>123652197</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513607</v>
+        <v>513644</v>
       </c>
       <c r="R58" t="n">
-        <v>6733239</v>
+        <v>6733242</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7586,7 +7591,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7596,12 +7601,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7629,7 +7634,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652160</v>
+        <v>123652185</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7673,10 +7678,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513608</v>
+        <v>513619</v>
       </c>
       <c r="R59" t="n">
-        <v>6733246</v>
+        <v>6733240</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7708,7 +7713,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7718,7 +7723,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7751,10 +7756,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123656500</v>
+        <v>123652175</v>
       </c>
       <c r="B60" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7763,32 +7768,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7796,13 +7800,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513668</v>
+        <v>513606</v>
       </c>
       <c r="R60" t="n">
-        <v>6733244</v>
+        <v>6733254</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7826,22 +7830,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7862,17 +7871,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123650523</v>
+        <v>123652174</v>
       </c>
       <c r="B61" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7881,39 +7890,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7921,10 +7922,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513585</v>
+        <v>513606</v>
       </c>
       <c r="R61" t="n">
-        <v>6733249</v>
+        <v>6733257</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7956,7 +7957,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7966,12 +7967,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7980,6 +7981,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7998,7 +8000,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652219</v>
+        <v>123652170</v>
       </c>
       <c r="B62" t="n">
         <v>98079</v>
@@ -8042,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513609</v>
+        <v>513607</v>
       </c>
       <c r="R62" t="n">
-        <v>6733267</v>
+        <v>6733239</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8077,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8087,12 +8089,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8120,7 +8122,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652195</v>
+        <v>123652212</v>
       </c>
       <c r="B63" t="n">
         <v>98079</v>
@@ -8164,10 +8166,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513645</v>
+        <v>513623</v>
       </c>
       <c r="R63" t="n">
-        <v>6733241</v>
+        <v>6733260</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8199,7 +8201,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8209,12 +8211,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8242,7 +8244,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652171</v>
+        <v>123652203</v>
       </c>
       <c r="B64" t="n">
         <v>98079</v>
@@ -8286,10 +8288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513608</v>
+        <v>513639</v>
       </c>
       <c r="R64" t="n">
-        <v>6733238</v>
+        <v>6733252</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8321,7 +8323,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8331,12 +8333,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,10 +8366,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123650524</v>
+        <v>123652182</v>
       </c>
       <c r="B65" t="n">
-        <v>56692</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,39 +8378,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8416,10 +8410,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513595</v>
+        <v>513620</v>
       </c>
       <c r="R65" t="n">
-        <v>6733257</v>
+        <v>6733241</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8451,7 +8445,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8461,7 +8455,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8470,6 +8469,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8488,7 +8488,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652207</v>
+        <v>123652210</v>
       </c>
       <c r="B66" t="n">
         <v>98079</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513629</v>
+        <v>513625</v>
       </c>
       <c r="R66" t="n">
-        <v>6733245</v>
+        <v>6733251</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8610,7 +8610,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652214</v>
+        <v>123652211</v>
       </c>
       <c r="B67" t="n">
         <v>98079</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513615</v>
+        <v>513625</v>
       </c>
       <c r="R67" t="n">
-        <v>6733271</v>
+        <v>6733258</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8699,12 +8699,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8732,7 +8732,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652224</v>
+        <v>123652161</v>
       </c>
       <c r="B68" t="n">
         <v>98079</v>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513610</v>
+        <v>513597</v>
       </c>
       <c r="R68" t="n">
-        <v>6733242</v>
+        <v>6733265</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652188</v>
+        <v>123652178</v>
       </c>
       <c r="B69" t="n">
         <v>98079</v>
@@ -8898,10 +8898,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513629</v>
+        <v>513605</v>
       </c>
       <c r="R69" t="n">
-        <v>6733239</v>
+        <v>6733242</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8976,7 +8976,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652184</v>
+        <v>123652190</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513618</v>
+        <v>513627</v>
       </c>
       <c r="R70" t="n">
-        <v>6733235</v>
+        <v>6733227</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -9098,7 +9098,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652206</v>
+        <v>123652199</v>
       </c>
       <c r="B71" t="n">
         <v>98079</v>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513623</v>
+        <v>513642</v>
       </c>
       <c r="R71" t="n">
-        <v>6733237</v>
+        <v>6733246</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -9220,7 +9220,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652193</v>
+        <v>123652164</v>
       </c>
       <c r="B72" t="n">
         <v>98079</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513631</v>
+        <v>513617</v>
       </c>
       <c r="R72" t="n">
-        <v>6733221</v>
+        <v>6733240</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9342,7 +9342,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652181</v>
+        <v>123652176</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513619</v>
+        <v>513605</v>
       </c>
       <c r="R73" t="n">
-        <v>6733234</v>
+        <v>6733249</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -9464,7 +9464,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652218</v>
+        <v>123652208</v>
       </c>
       <c r="B74" t="n">
         <v>98079</v>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513613</v>
+        <v>513626</v>
       </c>
       <c r="R74" t="n">
-        <v>6733273</v>
+        <v>6733254</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123253272</v>
+        <v>123656502</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>513623</v>
       </c>
       <c r="R2" t="n">
-        <v>6733230</v>
+        <v>6733240</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,74 +783,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252664</v>
+        <v>123656503</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513616</v>
+        <v>513619</v>
       </c>
       <c r="R3" t="n">
-        <v>6733249</v>
+        <v>6733230</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,74 +903,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123253165</v>
+        <v>123656504</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513623</v>
+        <v>513643</v>
       </c>
       <c r="R4" t="n">
-        <v>6733230</v>
+        <v>6733240</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +988,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,74 +1023,68 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123252821</v>
+        <v>123656505</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513598</v>
+        <v>513624</v>
       </c>
       <c r="R5" t="n">
-        <v>6733234</v>
+        <v>6733235</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1108,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,73 +1143,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123656505</v>
+        <v>123253272</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513624</v>
+        <v>513623</v>
       </c>
       <c r="R6" t="n">
-        <v>6733235</v>
+        <v>6733230</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,27 +1225,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt.</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,55 +1255,51 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123652213</v>
+        <v>123656500</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513617</v>
+        <v>513668</v>
       </c>
       <c r="R7" t="n">
-        <v>6733269</v>
+        <v>6733244</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,27 +1337,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,50 +1373,53 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123652162</v>
+        <v>123650523</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513604</v>
+        <v>513585</v>
       </c>
       <c r="R8" t="n">
-        <v>6733250</v>
+        <v>6733249</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1481,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,7 +1486,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1524,43 +1504,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123652164</v>
+        <v>123650524</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1568,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513617</v>
+        <v>513595</v>
       </c>
       <c r="R9" t="n">
-        <v>6733240</v>
+        <v>6733257</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1603,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,7 +1605,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1646,43 +1623,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123652206</v>
+        <v>123650526</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1690,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513623</v>
+        <v>513627</v>
       </c>
       <c r="R10" t="n">
-        <v>6733237</v>
+        <v>6733250</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1725,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,12 +1711,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,7 +1725,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1768,19 +1743,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123650524</v>
+        <v>123650527</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1803,14 +1773,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1820,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513595</v>
+        <v>513634</v>
       </c>
       <c r="R11" t="n">
-        <v>6733257</v>
+        <v>6733215</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1853,19 +1819,14 @@
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:52</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,43 +1853,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123652188</v>
+        <v>123650528</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1936,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513629</v>
+        <v>513632</v>
       </c>
       <c r="R12" t="n">
-        <v>6733239</v>
+        <v>6733214</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1971,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1981,12 +1941,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,7 +1950,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2007,22 +1961,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123652216</v>
+        <v>123252664</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,24 +1996,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513614</v>
+        <v>513616</v>
       </c>
       <c r="R13" t="n">
-        <v>6733272</v>
+        <v>6733249</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2088,27 +2042,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,80 +2066,75 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123656502</v>
+        <v>123252821</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513623</v>
+        <v>513598</v>
       </c>
       <c r="R14" t="n">
-        <v>6733240</v>
+        <v>6733234</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2214,27 +2158,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,27 +2188,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123652208</v>
+        <v>123253165</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,24 +2228,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bjurtjärnsån, Dlr</t>
+          <t>Bjurtjärnsån, Bjurtjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513626</v>
+        <v>513623</v>
       </c>
       <c r="R15" t="n">
-        <v>6733254</v>
+        <v>6733230</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2335,27 +2274,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,34 +2298,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123652177</v>
+        <v>123652160</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,10 +2355,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513615</v>
+        <v>513608</v>
       </c>
       <c r="R16" t="n">
-        <v>6733245</v>
+        <v>6733246</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2462,7 +2390,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2400,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2505,15 +2433,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123652185</v>
+        <v>123652161</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,10 +2472,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513619</v>
+        <v>513597</v>
       </c>
       <c r="R17" t="n">
-        <v>6733240</v>
+        <v>6733265</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2584,7 +2507,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2594,12 +2517,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,22 +2543,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123652219</v>
+        <v>123652162</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2671,10 +2589,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513609</v>
+        <v>513604</v>
       </c>
       <c r="R18" t="n">
-        <v>6733267</v>
+        <v>6733250</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2706,7 +2624,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2716,12 +2634,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,15 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123652226</v>
+        <v>123652163</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2793,13 +2706,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513622</v>
+        <v>513621</v>
       </c>
       <c r="R19" t="n">
-        <v>6733236</v>
+        <v>6733235</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2828,7 +2741,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2838,12 +2751,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2871,15 +2784,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123652171</v>
+        <v>123652164</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2915,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513608</v>
+        <v>513617</v>
       </c>
       <c r="R20" t="n">
-        <v>6733238</v>
+        <v>6733240</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2950,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2960,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2993,15 +2901,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123652212</v>
+        <v>123652168</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3037,10 +2940,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513623</v>
+        <v>513593</v>
       </c>
       <c r="R21" t="n">
-        <v>6733260</v>
+        <v>6733228</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3072,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3082,12 +2985,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3115,15 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123652163</v>
+        <v>123652169</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3159,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513621</v>
+        <v>513603</v>
       </c>
       <c r="R22" t="n">
-        <v>6733235</v>
+        <v>6733229</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3194,7 +3092,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3204,7 +3102,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3237,15 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123652181</v>
+        <v>123652170</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513619</v>
+        <v>513607</v>
       </c>
       <c r="R23" t="n">
-        <v>6733234</v>
+        <v>6733239</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3316,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3326,7 +3219,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3359,15 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123652201</v>
+        <v>123652171</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3403,10 +3291,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513640</v>
+        <v>513608</v>
       </c>
       <c r="R24" t="n">
-        <v>6733246</v>
+        <v>6733238</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3438,7 +3326,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3448,12 +3336,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,47 +3369,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123650528</v>
+        <v>123652173</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3529,10 +3408,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513632</v>
+        <v>513600</v>
       </c>
       <c r="R25" t="n">
-        <v>6733214</v>
+        <v>6733258</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3564,7 +3443,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3574,7 +3453,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3583,6 +3467,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3594,58 +3479,45 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123650523</v>
+        <v>123652174</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3653,10 +3525,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513585</v>
+        <v>513606</v>
       </c>
       <c r="R26" t="n">
-        <v>6733249</v>
+        <v>6733257</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3688,7 +3560,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3698,12 +3570,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Jag tog fjäder/dun med mig hem och har fått artbestämt av kunnig.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3712,6 +3584,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3730,15 +3603,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123652173</v>
+        <v>123652175</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,10 +3642,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513600</v>
+        <v>513606</v>
       </c>
       <c r="R27" t="n">
-        <v>6733258</v>
+        <v>6733254</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3809,7 +3677,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3819,7 +3687,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3852,15 +3720,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123652199</v>
+        <v>123652176</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3896,10 +3759,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513642</v>
+        <v>513605</v>
       </c>
       <c r="R28" t="n">
-        <v>6733246</v>
+        <v>6733249</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3931,7 +3794,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3941,12 +3804,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3974,15 +3837,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123652223</v>
+        <v>123652177</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4018,10 +3876,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513611</v>
+        <v>513615</v>
       </c>
       <c r="R29" t="n">
-        <v>6733249</v>
+        <v>6733245</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4053,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4063,12 +3921,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4096,15 +3954,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123652168</v>
+        <v>123652178</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4140,10 +3993,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513593</v>
+        <v>513605</v>
       </c>
       <c r="R30" t="n">
-        <v>6733228</v>
+        <v>6733242</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4175,7 +4028,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4185,7 +4038,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4218,37 +4071,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123656499</v>
+        <v>123652179</v>
       </c>
       <c r="B31" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4262,13 +4110,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513625</v>
+        <v>513611</v>
       </c>
       <c r="R31" t="n">
-        <v>6733311</v>
+        <v>6733236</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4297,7 +4145,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4307,7 +4155,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,15 +4188,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123652187</v>
+        <v>123652180</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4379,10 +4227,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513627</v>
+        <v>513623</v>
       </c>
       <c r="R32" t="n">
-        <v>6733241</v>
+        <v>6733239</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4414,7 +4262,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4424,7 +4272,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4457,47 +4305,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123650526</v>
+        <v>123652181</v>
       </c>
       <c r="B33" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4505,10 +4344,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513627</v>
+        <v>513619</v>
       </c>
       <c r="R33" t="n">
-        <v>6733250</v>
+        <v>6733234</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4540,7 +4379,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4550,12 +4389,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Under roten på ett vindfälle. Fornfynd i Fornsök! Kol d.v.s. rester från kolning.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4564,6 +4403,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4582,15 +4422,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123652211</v>
+        <v>123652182</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4626,10 +4461,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513625</v>
+        <v>513620</v>
       </c>
       <c r="R34" t="n">
-        <v>6733258</v>
+        <v>6733241</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4661,7 +4496,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4671,12 +4506,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4704,15 +4539,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123652195</v>
+        <v>123652184</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4748,10 +4578,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513645</v>
+        <v>513618</v>
       </c>
       <c r="R35" t="n">
-        <v>6733241</v>
+        <v>6733235</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4783,7 +4613,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,12 +4623,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4826,47 +4656,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123656504</v>
+        <v>123652185</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4874,7 +4695,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513643</v>
+        <v>513619</v>
       </c>
       <c r="R36" t="n">
         <v>6733240</v>
@@ -4909,7 +4730,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4919,12 +4740,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4933,6 +4754,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4951,15 +4773,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123652170</v>
+        <v>123652186</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4995,10 +4812,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513607</v>
+        <v>513623</v>
       </c>
       <c r="R37" t="n">
-        <v>6733239</v>
+        <v>6733238</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5030,7 +4847,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5040,7 +4857,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5073,15 +4890,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123652190</v>
+        <v>123652187</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5120,7 +4932,7 @@
         <v>513627</v>
       </c>
       <c r="R38" t="n">
-        <v>6733227</v>
+        <v>6733241</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5152,7 +4964,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5162,7 +4974,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5195,15 +5007,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123652205</v>
+        <v>123652188</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5239,10 +5046,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513635</v>
+        <v>513629</v>
       </c>
       <c r="R39" t="n">
-        <v>6733245</v>
+        <v>6733239</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5274,7 +5081,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5284,12 +5091,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5317,15 +5124,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123652207</v>
+        <v>123652189</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5364,7 +5166,7 @@
         <v>513629</v>
       </c>
       <c r="R40" t="n">
-        <v>6733245</v>
+        <v>6733228</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5396,7 +5198,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5406,12 +5208,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5439,15 +5241,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123652182</v>
+        <v>123652190</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5483,10 +5280,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513620</v>
+        <v>513627</v>
       </c>
       <c r="R41" t="n">
-        <v>6733241</v>
+        <v>6733227</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5518,7 +5315,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5528,7 +5325,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5561,15 +5358,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123652200</v>
+        <v>123652191</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5605,10 +5397,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513638</v>
+        <v>513628</v>
       </c>
       <c r="R42" t="n">
-        <v>6733248</v>
+        <v>6733228</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5640,7 +5432,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5650,12 +5442,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5683,15 +5475,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123652175</v>
+        <v>123652192</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5727,10 +5514,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513606</v>
+        <v>513630</v>
       </c>
       <c r="R43" t="n">
-        <v>6733254</v>
+        <v>6733221</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5762,7 +5549,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5772,7 +5559,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5805,15 +5592,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123652218</v>
+        <v>123652193</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5849,10 +5631,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513613</v>
+        <v>513631</v>
       </c>
       <c r="R44" t="n">
-        <v>6733273</v>
+        <v>6733221</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5884,7 +5666,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5894,12 +5676,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5927,15 +5709,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123652161</v>
+        <v>123652194</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5971,10 +5748,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513597</v>
+        <v>513642</v>
       </c>
       <c r="R45" t="n">
-        <v>6733265</v>
+        <v>6733220</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6006,7 +5783,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6016,12 +5793,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>18:07 Varje fynd består av mellan 10 och 100 plantor.  2872</t>
+          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6042,22 +5819,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123652179</v>
+        <v>123652195</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6093,10 +5865,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513611</v>
+        <v>513645</v>
       </c>
       <c r="R46" t="n">
-        <v>6733236</v>
+        <v>6733241</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6128,7 +5900,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,12 +5910,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Många fjolårsstänglar.</t>
+          <t>15:36 Varje fynd består av mellan 10 och 100 plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6171,44 +5943,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123656500</v>
+        <v>123652197</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6216,13 +5982,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513668</v>
+        <v>513644</v>
       </c>
       <c r="R47" t="n">
-        <v>6733244</v>
+        <v>6733242</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6246,22 +6012,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2001-01-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6282,22 +6053,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123652217</v>
+        <v>123652199</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6333,10 +6099,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513612</v>
+        <v>513642</v>
       </c>
       <c r="R48" t="n">
-        <v>6733277</v>
+        <v>6733246</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6368,7 +6134,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,12 +6144,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6411,15 +6177,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123652169</v>
+        <v>123652200</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6455,10 +6216,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513603</v>
+        <v>513638</v>
       </c>
       <c r="R49" t="n">
-        <v>6733229</v>
+        <v>6733248</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6490,7 +6251,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,12 +6261,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6533,15 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123652225</v>
+        <v>123652201</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6577,10 +6333,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513617</v>
+        <v>513640</v>
       </c>
       <c r="R50" t="n">
-        <v>6733234</v>
+        <v>6733246</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6612,7 +6368,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6622,7 +6378,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6655,15 +6411,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123652209</v>
+        <v>123652202</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6699,10 +6450,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513620</v>
+        <v>513640</v>
       </c>
       <c r="R51" t="n">
-        <v>6733253</v>
+        <v>6733250</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6734,7 +6485,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6744,7 +6495,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6777,15 +6528,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123652221</v>
+        <v>123652203</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6821,10 +6567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513613</v>
+        <v>513639</v>
       </c>
       <c r="R52" t="n">
-        <v>6733269</v>
+        <v>6733252</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6856,7 +6602,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6866,12 +6612,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6899,15 +6645,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123652203</v>
+        <v>123652204</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6943,10 +6684,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513639</v>
+        <v>513632</v>
       </c>
       <c r="R53" t="n">
-        <v>6733252</v>
+        <v>6733247</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6978,7 +6719,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6988,12 +6729,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7021,15 +6762,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123652174</v>
+        <v>123652205</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7065,10 +6801,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513606</v>
+        <v>513635</v>
       </c>
       <c r="R54" t="n">
-        <v>6733257</v>
+        <v>6733245</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7100,7 +6836,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7110,12 +6846,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7143,15 +6879,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123652192</v>
+        <v>123652206</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7187,10 +6918,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513630</v>
+        <v>513623</v>
       </c>
       <c r="R55" t="n">
-        <v>6733221</v>
+        <v>6733237</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -7222,7 +6953,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7232,12 +6963,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7265,15 +6996,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123652176</v>
+        <v>123652207</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7309,10 +7035,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513605</v>
+        <v>513629</v>
       </c>
       <c r="R56" t="n">
-        <v>6733249</v>
+        <v>6733245</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7344,7 +7070,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7354,12 +7080,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7387,15 +7113,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123652204</v>
+        <v>123652208</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7431,10 +7152,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513632</v>
+        <v>513626</v>
       </c>
       <c r="R57" t="n">
-        <v>6733247</v>
+        <v>6733254</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7466,7 +7187,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7476,7 +7197,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7509,47 +7230,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123656503</v>
+        <v>123652209</v>
       </c>
       <c r="B58" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7557,10 +7269,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513619</v>
+        <v>513620</v>
       </c>
       <c r="R58" t="n">
-        <v>6733230</v>
+        <v>6733253</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7592,7 +7304,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7602,12 +7314,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Vi hörde spillkråkans lockläte flera gånger i avverkningsanmälan men jag noterade inga koordinater specifikt. FÖDOSÖK!</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7616,6 +7328,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7634,15 +7347,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123652224</v>
+        <v>123652210</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7678,10 +7386,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513610</v>
+        <v>513625</v>
       </c>
       <c r="R59" t="n">
-        <v>6733242</v>
+        <v>6733251</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7713,7 +7421,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7723,12 +7431,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7756,15 +7464,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123652210</v>
+        <v>123652211</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7803,7 +7506,7 @@
         <v>513625</v>
       </c>
       <c r="R60" t="n">
-        <v>6733251</v>
+        <v>6733258</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7835,7 +7538,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7845,12 +7548,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>15:19  Jag att jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag  har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7878,15 +7581,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123652184</v>
+        <v>123652212</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7922,10 +7620,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513618</v>
+        <v>513623</v>
       </c>
       <c r="R61" t="n">
-        <v>6733235</v>
+        <v>6733260</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7957,7 +7655,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7967,12 +7665,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,15 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123652160</v>
+        <v>123652213</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8044,10 +7737,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>513608</v>
+        <v>513617</v>
       </c>
       <c r="R62" t="n">
-        <v>6733246</v>
+        <v>6733269</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -8079,7 +7772,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,12 +7782,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8122,15 +7815,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123652222</v>
+        <v>123652214</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8166,10 +7854,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>513612</v>
+        <v>513615</v>
       </c>
       <c r="R63" t="n">
-        <v>6733260</v>
+        <v>6733271</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8201,7 +7889,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8211,12 +7899,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,15 +7932,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123652220</v>
+        <v>123652216</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8288,10 +7971,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>513609</v>
+        <v>513614</v>
       </c>
       <c r="R64" t="n">
-        <v>6733266</v>
+        <v>6733272</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -8323,7 +8006,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8333,12 +8016,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8366,15 +8049,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123652180</v>
+        <v>123652217</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8410,10 +8088,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>513623</v>
+        <v>513612</v>
       </c>
       <c r="R65" t="n">
-        <v>6733239</v>
+        <v>6733277</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8445,7 +8123,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8455,12 +8133,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8488,15 +8166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123652202</v>
+        <v>123652218</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8532,10 +8205,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>513640</v>
+        <v>513613</v>
       </c>
       <c r="R66" t="n">
-        <v>6733250</v>
+        <v>6733273</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -8567,7 +8240,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,12 +8250,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8610,15 +8283,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123652197</v>
+        <v>123652219</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8654,10 +8322,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>513644</v>
+        <v>513609</v>
       </c>
       <c r="R67" t="n">
-        <v>6733242</v>
+        <v>6733267</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8689,7 +8357,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8699,12 +8367,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8732,15 +8400,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123652193</v>
+        <v>123652220</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8776,10 +8439,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>513631</v>
+        <v>513609</v>
       </c>
       <c r="R68" t="n">
-        <v>6733221</v>
+        <v>6733266</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8811,7 +8474,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,12 +8484,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>15:59 Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8854,15 +8517,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123652186</v>
+        <v>123652221</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8898,10 +8556,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>513623</v>
+        <v>513613</v>
       </c>
       <c r="R69" t="n">
-        <v>6733238</v>
+        <v>6733269</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8933,7 +8591,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8943,12 +8601,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8976,15 +8634,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123652178</v>
+        <v>123652222</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9020,10 +8673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>513605</v>
+        <v>513612</v>
       </c>
       <c r="R70" t="n">
-        <v>6733242</v>
+        <v>6733260</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -9055,7 +8708,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9065,12 +8718,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9098,15 +8751,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123652214</v>
+        <v>123652223</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9142,10 +8790,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>513615</v>
+        <v>513611</v>
       </c>
       <c r="R71" t="n">
-        <v>6733271</v>
+        <v>6733249</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -9177,7 +8825,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9187,12 +8835,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>jag har jag aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
+          <t>Jag aldrig har sett så många knärot på en och samma plats eller avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9220,15 +8868,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123652189</v>
+        <v>123652224</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9264,10 +8907,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>513629</v>
+        <v>513610</v>
       </c>
       <c r="R72" t="n">
-        <v>6733228</v>
+        <v>6733242</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9299,7 +8942,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9309,12 +8952,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor. Somliga med fjolårets fröställningar som denna.</t>
+          <t>14:49  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9342,15 +8985,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123652191</v>
+        <v>123652225</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,10 +9024,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>513628</v>
+        <v>513617</v>
       </c>
       <c r="R73" t="n">
-        <v>6733228</v>
+        <v>6733234</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -9421,7 +9059,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9431,12 +9069,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9464,15 +9102,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123652194</v>
+        <v>123652226</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9508,10 +9141,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>513642</v>
+        <v>513622</v>
       </c>
       <c r="R74" t="n">
-        <v>6733220</v>
+        <v>6733236</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9543,7 +9176,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9553,12 +9186,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Varje fynd består av mellan 10 och 100 plantor.</t>
+          <t>14:46  Jag har aldrig har sett så många knärot på en avverkningsanmälan tidigare. Det kan finnas ändå fler.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9586,47 +9219,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123650527</v>
+        <v>123656499</v>
       </c>
       <c r="B75" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9634,13 +9258,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>513634</v>
+        <v>513625</v>
       </c>
       <c r="R75" t="n">
-        <v>6733215</v>
+        <v>6733311</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9667,14 +9291,19 @@
           <t>2025-03-18</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-03-18</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>16:07</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9683,6 +9312,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9501-2025 artfynd.xlsx
+++ b/artfynd/A 9501-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656502</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656504</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656505</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123253272</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656500</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123650523</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1620,6 +1660,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123650524</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123650526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123650527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1965,6 +2020,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123650528</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2081,6 +2141,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123252664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2197,6 +2262,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123252821</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2313,6 +2383,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123253165</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2430,6 +2505,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652160</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2547,6 +2627,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652161</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2664,6 +2749,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652162</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2781,6 +2871,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652163</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2898,6 +2993,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652164</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3015,6 +3115,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652168</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3132,6 +3237,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652169</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3249,6 +3359,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652170</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3366,6 +3481,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652171</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3483,6 +3603,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652173</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3600,6 +3725,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652174</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3717,6 +3847,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652175</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3834,6 +3969,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652176</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3951,6 +4091,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652177</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4068,6 +4213,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652178</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4185,6 +4335,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652179</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4302,6 +4457,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652180</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4419,6 +4579,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652181</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4536,6 +4701,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652182</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4653,6 +4823,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652184</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4770,6 +4945,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652185</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4887,6 +5067,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652186</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5004,6 +5189,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652187</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5121,6 +5311,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652188</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5238,6 +5433,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652189</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5355,6 +5555,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652190</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5472,6 +5677,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652191</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5589,6 +5799,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652192</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5706,6 +5921,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652193</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5823,6 +6043,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652194</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5940,6 +6165,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652195</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6057,6 +6287,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652197</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6174,6 +6409,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652199</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6291,6 +6531,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652200</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6408,6 +6653,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652201</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6525,6 +6775,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652202</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6642,6 +6897,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652203</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6759,6 +7019,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652204</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6876,6 +7141,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652205</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6993,6 +7263,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652206</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7110,6 +7385,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652207</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7227,6 +7507,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652208</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7344,6 +7629,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652209</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7461,6 +7751,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652210</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7578,6 +7873,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652211</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7695,6 +7995,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652212</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7812,6 +8117,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652213</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7929,6 +8239,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652214</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8046,6 +8361,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652216</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8163,6 +8483,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652217</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8280,6 +8605,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652218</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8397,6 +8727,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652219</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8514,6 +8849,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652220</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8631,6 +8971,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652221</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8748,6 +9093,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652222</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8865,6 +9215,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652223</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8982,6 +9337,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652224</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9099,6 +9459,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652225</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9216,6 +9581,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123652226</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9328,8 +9698,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123656499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>